--- a/PL_3シナリオ比較.xlsx
+++ b/PL_3シナリオ比較.xlsx
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>7793</v>
+        <v>7307</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>4843</v>
+        <v>4586</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>515</v>
+        <v>479</v>
       </c>
       <c r="E9" s="2" t="n"/>
     </row>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>52</v>
+        <v>48.7</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>54.1</v>
+        <v>51.2</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>44</v>
+        <v>40.9</v>
       </c>
       <c r="E10" s="2" t="n"/>
     </row>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>2744</v>
+        <v>2258</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>872</v>
+        <v>615</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>-2373</v>
+        <v>-2409</v>
       </c>
       <c r="E13" s="2" t="n"/>
     </row>
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>18.3</v>
+        <v>15.1</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>9.699999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>-202.6</v>
+        <v>-205.7</v>
       </c>
       <c r="E14" s="2" t="n"/>
     </row>
@@ -1406,13 +1406,13 @@
         </is>
       </c>
       <c r="B29" s="30" t="n">
-        <v>2744</v>
+        <v>2258</v>
       </c>
       <c r="C29" s="30" t="n">
-        <v>872</v>
+        <v>615</v>
       </c>
       <c r="D29" s="31" t="n">
-        <v>-2373</v>
+        <v>-2409</v>
       </c>
       <c r="E29" s="27" t="inlineStr"/>
     </row>
@@ -1900,7 +1900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1929,7 +1929,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="47" t="inlineStr">
         <is>
-          <t>Year1で売上1.5億・営業利益2,744万・M6損益分岐　単位：万円</t>
+          <t>Year1で売上1.5億・営業利益2,258万・M6損益分岐　単位：万円</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TikTok Shop手数料（×6%）</t>
+          <t xml:space="preserve">  TikTok Shop手数料（M1-3:3%→M4-:7%）</t>
         </is>
       </c>
       <c r="B37" s="59" t="n">
@@ -3406,37 +3406,37 @@
         <v>0</v>
       </c>
       <c r="D37" s="59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G37" s="59" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H37" s="59" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I37" s="59" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J37" s="59" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K37" s="59" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="L37" s="59" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="M37" s="59" t="n">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="N37" s="55" t="n">
-        <v>487</v>
+        <v>566</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3486,718 +3486,810 @@
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="64" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  物流・梱包費（×4%）</t>
+        </is>
+      </c>
+      <c r="B39" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" s="59" t="n">
+        <v>12</v>
+      </c>
+      <c r="H39" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="I39" s="59" t="n">
+        <v>29</v>
+      </c>
+      <c r="J39" s="59" t="n">
+        <v>39</v>
+      </c>
+      <c r="K39" s="59" t="n">
+        <v>53</v>
+      </c>
+      <c r="L39" s="59" t="n">
+        <v>70</v>
+      </c>
+      <c r="M39" s="59" t="n">
+        <v>92</v>
+      </c>
+      <c r="N39" s="55" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  在庫損失引当（×1%）</t>
+        </is>
+      </c>
+      <c r="B40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" s="59" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="K40" s="59" t="n">
+        <v>13</v>
+      </c>
+      <c r="L40" s="59" t="n">
+        <v>18</v>
+      </c>
+      <c r="M40" s="59" t="n">
+        <v>23</v>
+      </c>
+      <c r="N40" s="55" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">  EC原価合計</t>
         </is>
       </c>
-      <c r="B39" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="65" t="n">
+      <c r="B41" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="65" t="n">
         <v>17</v>
       </c>
-      <c r="E39" s="65" t="n">
-        <v>44</v>
-      </c>
-      <c r="F39" s="65" t="n">
-        <v>99</v>
-      </c>
-      <c r="G39" s="65" t="n">
-        <v>193</v>
-      </c>
-      <c r="H39" s="65" t="n">
-        <v>323</v>
-      </c>
-      <c r="I39" s="65" t="n">
-        <v>475</v>
-      </c>
-      <c r="J39" s="65" t="n">
+      <c r="E41" s="65" t="n">
+        <v>49</v>
+      </c>
+      <c r="F41" s="65" t="n">
+        <v>109</v>
+      </c>
+      <c r="G41" s="65" t="n">
+        <v>210</v>
+      </c>
+      <c r="H41" s="65" t="n">
+        <v>353</v>
+      </c>
+      <c r="I41" s="65" t="n">
+        <v>518</v>
+      </c>
+      <c r="J41" s="65" t="n">
+        <v>702</v>
+      </c>
+      <c r="K41" s="65" t="n">
+        <v>955</v>
+      </c>
+      <c r="L41" s="65" t="n">
+        <v>1267</v>
+      </c>
+      <c r="M41" s="65" t="n">
+        <v>1653</v>
+      </c>
+      <c r="N41" s="65" t="n">
+        <v>5833</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TikTok Shop 粗利</t>
+        </is>
+      </c>
+      <c r="B42" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="74" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" s="74" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" s="74" t="n">
+        <v>41</v>
+      </c>
+      <c r="G42" s="74" t="n">
+        <v>82</v>
+      </c>
+      <c r="H42" s="74" t="n">
+        <v>137</v>
+      </c>
+      <c r="I42" s="74" t="n">
+        <v>202</v>
+      </c>
+      <c r="J42" s="74" t="n">
+        <v>273</v>
+      </c>
+      <c r="K42" s="74" t="n">
+        <v>371</v>
+      </c>
+      <c r="L42" s="74" t="n">
+        <v>493</v>
+      </c>
+      <c r="M42" s="74" t="n">
         <v>643</v>
       </c>
-      <c r="K39" s="65" t="n">
-        <v>876</v>
-      </c>
-      <c r="L39" s="65" t="n">
-        <v>1162</v>
-      </c>
-      <c r="M39" s="65" t="n">
-        <v>1515</v>
-      </c>
-      <c r="N39" s="65" t="n">
-        <v>5347</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TikTok Shop 粗利</t>
-        </is>
-      </c>
-      <c r="B40" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="74" t="n">
-        <v>8</v>
-      </c>
-      <c r="E40" s="74" t="n">
-        <v>22</v>
-      </c>
-      <c r="F40" s="74" t="n">
-        <v>51</v>
-      </c>
-      <c r="G40" s="74" t="n">
-        <v>99</v>
-      </c>
-      <c r="H40" s="74" t="n">
-        <v>167</v>
-      </c>
-      <c r="I40" s="74" t="n">
-        <v>245</v>
-      </c>
-      <c r="J40" s="74" t="n">
-        <v>332</v>
-      </c>
-      <c r="K40" s="74" t="n">
-        <v>450</v>
-      </c>
-      <c r="L40" s="74" t="n">
-        <v>598</v>
-      </c>
-      <c r="M40" s="74" t="n">
-        <v>781</v>
-      </c>
-      <c r="N40" s="74" t="n">
-        <v>2753</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="70" t="inlineStr">
+      <c r="N42" s="74" t="n">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  TikTok Shop 粗利率</t>
         </is>
       </c>
-      <c r="B41" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="71" t="n">
+      <c r="B43" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="71" t="n">
         <v>32</v>
       </c>
-      <c r="E41" s="71" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="G41" s="71" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="H41" s="71" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="I41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="J41" s="71" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="K41" s="71" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="L41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="M41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="N41" s="72" t="n">
-        <v>33.7</v>
-      </c>
-    </row>
-    <row r="42" ht="6" customHeight="1">
-      <c r="A42" s="67" t="inlineStr"/>
-      <c r="B42" s="68" t="n"/>
-      <c r="C42" s="68" t="n"/>
-      <c r="D42" s="68" t="n"/>
-      <c r="E42" s="68" t="n"/>
-      <c r="F42" s="68" t="n"/>
-      <c r="G42" s="68" t="n"/>
-      <c r="H42" s="68" t="n"/>
-      <c r="I42" s="68" t="n"/>
-      <c r="J42" s="68" t="n"/>
-      <c r="K42" s="68" t="n"/>
-      <c r="L42" s="68" t="n"/>
-      <c r="M42" s="68" t="n"/>
-      <c r="N42" s="68" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="75" t="inlineStr">
+      <c r="E43" s="71" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F43" s="71" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G43" s="71" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="H43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="I43" s="71" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="K43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="L43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="M43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="N43" s="72" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="44" ht="6" customHeight="1">
+      <c r="A44" s="67" t="inlineStr"/>
+      <c r="B44" s="68" t="n"/>
+      <c r="C44" s="68" t="n"/>
+      <c r="D44" s="68" t="n"/>
+      <c r="E44" s="68" t="n"/>
+      <c r="F44" s="68" t="n"/>
+      <c r="G44" s="68" t="n"/>
+      <c r="H44" s="68" t="n"/>
+      <c r="I44" s="68" t="n"/>
+      <c r="J44" s="68" t="n"/>
+      <c r="K44" s="68" t="n"/>
+      <c r="L44" s="68" t="n"/>
+      <c r="M44" s="68" t="n"/>
+      <c r="N44" s="68" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="75" t="inlineStr">
         <is>
           <t>売上原価合計</t>
         </is>
       </c>
-      <c r="B43" s="76" t="n">
+      <c r="B45" s="76" t="n">
         <v>10</v>
       </c>
-      <c r="C43" s="76" t="n">
+      <c r="C45" s="76" t="n">
         <v>10</v>
       </c>
-      <c r="D43" s="76" t="n">
+      <c r="D45" s="76" t="n">
         <v>57</v>
       </c>
-      <c r="E43" s="76" t="n">
-        <v>124</v>
-      </c>
-      <c r="F43" s="76" t="n">
-        <v>219</v>
-      </c>
-      <c r="G43" s="76" t="n">
-        <v>313</v>
-      </c>
-      <c r="H43" s="76" t="n">
-        <v>483</v>
-      </c>
-      <c r="I43" s="76" t="n">
-        <v>675</v>
-      </c>
-      <c r="J43" s="76" t="n">
-        <v>883</v>
-      </c>
-      <c r="K43" s="76" t="n">
-        <v>1116</v>
-      </c>
-      <c r="L43" s="76" t="n">
-        <v>1442</v>
-      </c>
-      <c r="M43" s="76" t="n">
-        <v>1875</v>
-      </c>
-      <c r="N43" s="76" t="n">
-        <v>7207</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="77" t="inlineStr">
+      <c r="E45" s="76" t="n">
+        <v>129</v>
+      </c>
+      <c r="F45" s="76" t="n">
+        <v>229</v>
+      </c>
+      <c r="G45" s="76" t="n">
+        <v>330</v>
+      </c>
+      <c r="H45" s="76" t="n">
+        <v>513</v>
+      </c>
+      <c r="I45" s="76" t="n">
+        <v>718</v>
+      </c>
+      <c r="J45" s="76" t="n">
+        <v>942</v>
+      </c>
+      <c r="K45" s="76" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L45" s="76" t="n">
+        <v>1547</v>
+      </c>
+      <c r="M45" s="76" t="n">
+        <v>2013</v>
+      </c>
+      <c r="N45" s="76" t="n">
+        <v>7693</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="77" t="inlineStr">
         <is>
           <t>粗利益合計</t>
         </is>
       </c>
-      <c r="B44" s="78" t="n">
+      <c r="B46" s="78" t="n">
         <v>-10</v>
       </c>
-      <c r="C44" s="78" t="n">
+      <c r="C46" s="78" t="n">
         <v>-10</v>
       </c>
-      <c r="D44" s="79" t="n">
+      <c r="D46" s="79" t="n">
         <v>118</v>
       </c>
-      <c r="E44" s="79" t="n">
-        <v>242</v>
-      </c>
-      <c r="F44" s="79" t="n">
-        <v>381</v>
-      </c>
-      <c r="G44" s="79" t="n">
-        <v>429</v>
-      </c>
-      <c r="H44" s="79" t="n">
-        <v>607</v>
-      </c>
-      <c r="I44" s="79" t="n">
-        <v>795</v>
-      </c>
-      <c r="J44" s="79" t="n">
-        <v>992</v>
-      </c>
-      <c r="K44" s="79" t="n">
-        <v>1110</v>
-      </c>
-      <c r="L44" s="79" t="n">
-        <v>1368</v>
-      </c>
-      <c r="M44" s="79" t="n">
-        <v>1771</v>
-      </c>
-      <c r="N44" s="79" t="n">
-        <v>7793</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="70" t="inlineStr">
+      <c r="E46" s="79" t="n">
+        <v>237</v>
+      </c>
+      <c r="F46" s="79" t="n">
+        <v>371</v>
+      </c>
+      <c r="G46" s="79" t="n">
+        <v>412</v>
+      </c>
+      <c r="H46" s="79" t="n">
+        <v>577</v>
+      </c>
+      <c r="I46" s="79" t="n">
+        <v>752</v>
+      </c>
+      <c r="J46" s="79" t="n">
+        <v>933</v>
+      </c>
+      <c r="K46" s="79" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L46" s="79" t="n">
+        <v>1263</v>
+      </c>
+      <c r="M46" s="79" t="n">
+        <v>1633</v>
+      </c>
+      <c r="N46" s="79" t="n">
+        <v>7307</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="70" t="inlineStr">
         <is>
           <t>粗利率（合計）</t>
         </is>
       </c>
-      <c r="B45" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="71" t="n">
+      <c r="B47" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="71" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="E45" s="71" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="F45" s="71" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="G45" s="71" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="H45" s="71" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="I45" s="71" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="J45" s="71" t="n">
+      <c r="E47" s="71" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="F47" s="71" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G47" s="71" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="H47" s="71" t="n">
         <v>52.9</v>
       </c>
-      <c r="K45" s="71" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="L45" s="71" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="M45" s="71" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="N45" s="72" t="n">
-        <v>56.5</v>
-      </c>
-    </row>
-    <row r="46" ht="6" customHeight="1">
-      <c r="A46" s="67" t="inlineStr"/>
-      <c r="B46" s="68" t="n"/>
-      <c r="C46" s="68" t="n"/>
-      <c r="D46" s="68" t="n"/>
-      <c r="E46" s="68" t="n"/>
-      <c r="F46" s="68" t="n"/>
-      <c r="G46" s="68" t="n"/>
-      <c r="H46" s="68" t="n"/>
-      <c r="I46" s="68" t="n"/>
-      <c r="J46" s="68" t="n"/>
-      <c r="K46" s="68" t="n"/>
-      <c r="L46" s="68" t="n"/>
-      <c r="M46" s="68" t="n"/>
-      <c r="N46" s="68" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="57" t="inlineStr">
+      <c r="I47" s="71" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J47" s="71" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="K47" s="71" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="L47" s="71" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="M47" s="71" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="N47" s="72" t="n">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="48" ht="6" customHeight="1">
+      <c r="A48" s="67" t="inlineStr"/>
+      <c r="B48" s="68" t="n"/>
+      <c r="C48" s="68" t="n"/>
+      <c r="D48" s="68" t="n"/>
+      <c r="E48" s="68" t="n"/>
+      <c r="F48" s="68" t="n"/>
+      <c r="G48" s="68" t="n"/>
+      <c r="H48" s="68" t="n"/>
+      <c r="I48" s="68" t="n"/>
+      <c r="J48" s="68" t="n"/>
+      <c r="K48" s="68" t="n"/>
+      <c r="L48" s="68" t="n"/>
+      <c r="M48" s="68" t="n"/>
+      <c r="N48" s="68" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="57" t="inlineStr">
         <is>
           <t>【販売管理費】</t>
         </is>
       </c>
-      <c r="B47" s="58" t="n"/>
-      <c r="C47" s="58" t="n"/>
-      <c r="D47" s="58" t="n"/>
-      <c r="E47" s="58" t="n"/>
-      <c r="F47" s="58" t="n"/>
-      <c r="G47" s="58" t="n"/>
-      <c r="H47" s="58" t="n"/>
-      <c r="I47" s="58" t="n"/>
-      <c r="J47" s="58" t="n"/>
-      <c r="K47" s="58" t="n"/>
-      <c r="L47" s="58" t="n"/>
-      <c r="M47" s="58" t="n"/>
-      <c r="N47" s="58" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
-        </is>
-      </c>
-      <c r="B48" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="C48" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="D48" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="E48" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="F48" s="59" t="n">
-        <v>200</v>
-      </c>
-      <c r="G48" s="59" t="n">
-        <v>200</v>
-      </c>
-      <c r="H48" s="59" t="n">
-        <v>250</v>
-      </c>
-      <c r="I48" s="59" t="n">
-        <v>250</v>
-      </c>
-      <c r="J48" s="59" t="n">
-        <v>250</v>
-      </c>
-      <c r="K48" s="59" t="n">
-        <v>250</v>
-      </c>
-      <c r="L48" s="59" t="n">
-        <v>250</v>
-      </c>
-      <c r="M48" s="59" t="n">
-        <v>250</v>
-      </c>
-      <c r="N48" s="55" t="n">
-        <v>2450</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  人件費（バズ社員）</t>
-        </is>
-      </c>
-      <c r="B49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="C49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="D49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="E49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="F49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="G49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="H49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="I49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="J49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="K49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="L49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="M49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="N49" s="55" t="n">
-        <v>1200</v>
-      </c>
+      <c r="B49" s="58" t="n"/>
+      <c r="C49" s="58" t="n"/>
+      <c r="D49" s="58" t="n"/>
+      <c r="E49" s="58" t="n"/>
+      <c r="F49" s="58" t="n"/>
+      <c r="G49" s="58" t="n"/>
+      <c r="H49" s="58" t="n"/>
+      <c r="I49" s="58" t="n"/>
+      <c r="J49" s="58" t="n"/>
+      <c r="K49" s="58" t="n"/>
+      <c r="L49" s="58" t="n"/>
+      <c r="M49" s="58" t="n"/>
+      <c r="N49" s="58" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  その他販管費</t>
+          <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
         </is>
       </c>
       <c r="B50" s="59" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C50" s="59" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D50" s="59" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E50" s="59" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F50" s="59" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="G50" s="59" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="H50" s="59" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="I50" s="59" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="J50" s="59" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="K50" s="59" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="L50" s="59" t="n">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="M50" s="59" t="n">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="N50" s="55" t="n">
-        <v>810</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="36" t="inlineStr">
         <is>
+          <t xml:space="preserve">  人件費（バズ社員）</t>
+        </is>
+      </c>
+      <c r="B51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="C51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="D51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="F51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="H51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="I51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="K51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="L51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="M51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="N51" s="55" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  その他販管費</t>
+        </is>
+      </c>
+      <c r="B52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="E52" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F52" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G52" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="H52" s="59" t="n">
+        <v>70</v>
+      </c>
+      <c r="I52" s="59" t="n">
+        <v>70</v>
+      </c>
+      <c r="J52" s="59" t="n">
+        <v>80</v>
+      </c>
+      <c r="K52" s="59" t="n">
+        <v>80</v>
+      </c>
+      <c r="L52" s="59" t="n">
+        <v>90</v>
+      </c>
+      <c r="M52" s="59" t="n">
+        <v>90</v>
+      </c>
+      <c r="N52" s="55" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ENTIAL業務委託費（TIE×5%＋EC×3%）</t>
         </is>
       </c>
-      <c r="B51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="59" t="n">
+      <c r="B53" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="E51" s="59" t="n">
+      <c r="E53" s="59" t="n">
         <v>17</v>
       </c>
-      <c r="F51" s="59" t="n">
+      <c r="F53" s="59" t="n">
         <v>26</v>
       </c>
-      <c r="G51" s="59" t="n">
+      <c r="G53" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="H51" s="59" t="n">
+      <c r="H53" s="59" t="n">
         <v>45</v>
       </c>
-      <c r="I51" s="59" t="n">
+      <c r="I53" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="J51" s="59" t="n">
+      <c r="J53" s="59" t="n">
         <v>74</v>
       </c>
-      <c r="K51" s="59" t="n">
+      <c r="K53" s="59" t="n">
         <v>85</v>
       </c>
-      <c r="L51" s="59" t="n">
+      <c r="L53" s="59" t="n">
         <v>105</v>
       </c>
-      <c r="M51" s="59" t="n">
+      <c r="M53" s="59" t="n">
         <v>137</v>
       </c>
-      <c r="N51" s="55" t="n">
+      <c r="N53" s="55" t="n">
         <v>589</v>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="75" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="75" t="inlineStr">
         <is>
           <t>販売管理費合計</t>
         </is>
       </c>
-      <c r="B52" s="76" t="n">
+      <c r="B54" s="76" t="n">
         <v>250</v>
       </c>
-      <c r="C52" s="76" t="n">
+      <c r="C54" s="76" t="n">
         <v>300</v>
       </c>
-      <c r="D52" s="76" t="n">
+      <c r="D54" s="76" t="n">
         <v>309</v>
       </c>
-      <c r="E52" s="76" t="n">
+      <c r="E54" s="76" t="n">
         <v>327</v>
       </c>
-      <c r="F52" s="76" t="n">
+      <c r="F54" s="76" t="n">
         <v>386</v>
       </c>
-      <c r="G52" s="76" t="n">
+      <c r="G54" s="76" t="n">
         <v>391</v>
       </c>
-      <c r="H52" s="76" t="n">
+      <c r="H54" s="76" t="n">
         <v>465</v>
       </c>
-      <c r="I52" s="76" t="n">
+      <c r="I54" s="76" t="n">
         <v>480</v>
       </c>
-      <c r="J52" s="76" t="n">
+      <c r="J54" s="76" t="n">
         <v>504</v>
       </c>
-      <c r="K52" s="76" t="n">
+      <c r="K54" s="76" t="n">
         <v>515</v>
       </c>
-      <c r="L52" s="76" t="n">
+      <c r="L54" s="76" t="n">
         <v>545</v>
       </c>
-      <c r="M52" s="76" t="n">
+      <c r="M54" s="76" t="n">
         <v>577</v>
       </c>
-      <c r="N52" s="76" t="n">
+      <c r="N54" s="76" t="n">
         <v>5049</v>
       </c>
     </row>
-    <row r="53" ht="6" customHeight="1">
-      <c r="A53" s="67" t="inlineStr"/>
-      <c r="B53" s="68" t="n"/>
-      <c r="C53" s="68" t="n"/>
-      <c r="D53" s="68" t="n"/>
-      <c r="E53" s="68" t="n"/>
-      <c r="F53" s="68" t="n"/>
-      <c r="G53" s="68" t="n"/>
-      <c r="H53" s="68" t="n"/>
-      <c r="I53" s="68" t="n"/>
-      <c r="J53" s="68" t="n"/>
-      <c r="K53" s="68" t="n"/>
-      <c r="L53" s="68" t="n"/>
-      <c r="M53" s="68" t="n"/>
-      <c r="N53" s="68" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="56" t="inlineStr">
+    <row r="55" ht="6" customHeight="1">
+      <c r="A55" s="67" t="inlineStr"/>
+      <c r="B55" s="68" t="n"/>
+      <c r="C55" s="68" t="n"/>
+      <c r="D55" s="68" t="n"/>
+      <c r="E55" s="68" t="n"/>
+      <c r="F55" s="68" t="n"/>
+      <c r="G55" s="68" t="n"/>
+      <c r="H55" s="68" t="n"/>
+      <c r="I55" s="68" t="n"/>
+      <c r="J55" s="68" t="n"/>
+      <c r="K55" s="68" t="n"/>
+      <c r="L55" s="68" t="n"/>
+      <c r="M55" s="68" t="n"/>
+      <c r="N55" s="68" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="B54" s="80" t="n">
+      <c r="B56" s="80" t="n">
         <v>-260</v>
       </c>
-      <c r="C54" s="80" t="n">
+      <c r="C56" s="80" t="n">
         <v>-310</v>
       </c>
-      <c r="D54" s="80" t="n">
+      <c r="D56" s="80" t="n">
         <v>-191</v>
       </c>
-      <c r="E54" s="80" t="n">
-        <v>-85</v>
-      </c>
-      <c r="F54" s="80" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G54" s="81" t="n">
-        <v>38</v>
-      </c>
-      <c r="H54" s="82" t="n">
-        <v>142</v>
-      </c>
-      <c r="I54" s="82" t="n">
-        <v>315</v>
-      </c>
-      <c r="J54" s="82" t="n">
-        <v>488</v>
-      </c>
-      <c r="K54" s="82" t="n">
-        <v>595</v>
-      </c>
-      <c r="L54" s="82" t="n">
-        <v>823</v>
-      </c>
-      <c r="M54" s="82" t="n">
-        <v>1194</v>
-      </c>
-      <c r="N54" s="81" t="n">
-        <v>2744</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="70" t="inlineStr">
+      <c r="E56" s="80" t="n">
+        <v>-90</v>
+      </c>
+      <c r="F56" s="80" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G56" s="81" t="n">
+        <v>21</v>
+      </c>
+      <c r="H56" s="82" t="n">
+        <v>112</v>
+      </c>
+      <c r="I56" s="82" t="n">
+        <v>272</v>
+      </c>
+      <c r="J56" s="82" t="n">
+        <v>429</v>
+      </c>
+      <c r="K56" s="82" t="n">
+        <v>516</v>
+      </c>
+      <c r="L56" s="82" t="n">
+        <v>718</v>
+      </c>
+      <c r="M56" s="82" t="n">
+        <v>1056</v>
+      </c>
+      <c r="N56" s="81" t="n">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="70" t="inlineStr">
         <is>
           <t>営業利益率</t>
         </is>
       </c>
-      <c r="B55" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="71" t="n">
+      <c r="B57" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="71" t="n">
         <v>-109.1</v>
       </c>
-      <c r="E55" s="71" t="n">
-        <v>-23.2</v>
-      </c>
-      <c r="F55" s="71" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="G55" s="71" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H55" s="71" t="n">
-        <v>13</v>
-      </c>
-      <c r="I55" s="71" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="J55" s="71" t="n">
-        <v>26</v>
-      </c>
-      <c r="K55" s="71" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="L55" s="71" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="M55" s="71" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="N55" s="72" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="83" t="inlineStr">
-        <is>
-          <t>★ 損益分岐：M6　／　Year1通期営業利益：2,744万円　／　Year1売上：15,000万円</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="84" t="inlineStr">
-        <is>
-          <t>【注記】単位：万円 ／ ギャル協会：出演・監修料=件数×25万（月最低保証10万）＋EC RS 15% ／ 制作費：TIE売上×10% ／ EC原価率66%（仕入45%＋TK手数料6%＋ギャル協会RS15%）／ ENTIAL：完全成功報酬（TIE×5%＋EC×3%、固定費ゼロ）</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="n"/>
-      <c r="N57" s="2" t="n"/>
+      <c r="E57" s="71" t="n">
+        <v>-24.6</v>
+      </c>
+      <c r="F57" s="71" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G57" s="71" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H57" s="71" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I57" s="71" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J57" s="71" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K57" s="71" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L57" s="71" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="M57" s="71" t="n">
+        <v>29</v>
+      </c>
+      <c r="N57" s="72" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="83" t="inlineStr">
+        <is>
+          <t>★ 損益分岐：M6　／　Year1通期営業利益：2,258万円　／　Year1売上：15,000万円</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="84" t="inlineStr">
+        <is>
+          <t>【注記】単位：万円 ／ ギャル協会：出演・監修料=件数×25万（月最低保証10万）＋EC RS 15% ／ 制作費：TIE売上×10% ／ EC原価合計72%（仕入45%＋TK手数料M1-3:3%/M4-:7%＋RS15%＋物流4%＋在庫損失1%）／ ENTIAL：完全成功報酬（TIE×5%＋EC×3%、固定費ゼロ）</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A56:N56"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A57:N57"/>
+    <mergeCell ref="A59:N59"/>
     <mergeCell ref="A13:N13"/>
+    <mergeCell ref="A58:N58"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4210,7 +4302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4239,7 +4331,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="47" t="inlineStr">
         <is>
-          <t>Year1で売上8,951万・営業利益872万・M7損益分岐　単位：万円</t>
+          <t>Year1で売上8,951万・営業利益615万・M7損益分岐　単位：万円</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5816,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TikTok Shop手数料（×6%）</t>
+          <t xml:space="preserve">  TikTok Shop手数料（M1-3:3%→M4-:7%）</t>
         </is>
       </c>
       <c r="B37" s="59" t="n">
@@ -5734,37 +5826,37 @@
         <v>0</v>
       </c>
       <c r="D37" s="59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="59" t="n">
         <v>2</v>
       </c>
       <c r="F37" s="59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" s="59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H37" s="59" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I37" s="59" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J37" s="59" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K37" s="59" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L37" s="59" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="M37" s="59" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N37" s="55" t="n">
-        <v>258</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -5814,718 +5906,810 @@
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="64" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  物流・梱包費（×4%）</t>
+        </is>
+      </c>
+      <c r="B39" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" s="59" t="n">
+        <v>14</v>
+      </c>
+      <c r="J39" s="59" t="n">
+        <v>21</v>
+      </c>
+      <c r="K39" s="59" t="n">
+        <v>27</v>
+      </c>
+      <c r="L39" s="59" t="n">
+        <v>39</v>
+      </c>
+      <c r="M39" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="N39" s="55" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  在庫損失引当（×1%）</t>
+        </is>
+      </c>
+      <c r="B40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="59" t="n">
+        <v>7</v>
+      </c>
+      <c r="L40" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="M40" s="59" t="n">
+        <v>13</v>
+      </c>
+      <c r="N40" s="55" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">  EC原価合計</t>
         </is>
       </c>
-      <c r="B39" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="65" t="n">
+      <c r="B41" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="65" t="n">
         <v>9</v>
       </c>
-      <c r="E39" s="65" t="n">
-        <v>23</v>
-      </c>
-      <c r="F39" s="65" t="n">
-        <v>47</v>
-      </c>
-      <c r="G39" s="65" t="n">
-        <v>91</v>
-      </c>
-      <c r="H39" s="65" t="n">
-        <v>158</v>
-      </c>
-      <c r="I39" s="65" t="n">
-        <v>238</v>
-      </c>
-      <c r="J39" s="65" t="n">
-        <v>343</v>
-      </c>
-      <c r="K39" s="65" t="n">
-        <v>450</v>
-      </c>
-      <c r="L39" s="65" t="n">
-        <v>647</v>
-      </c>
-      <c r="M39" s="65" t="n">
-        <v>832</v>
-      </c>
-      <c r="N39" s="65" t="n">
-        <v>2838</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="73" t="inlineStr">
+      <c r="E41" s="65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" s="65" t="n">
+        <v>52</v>
+      </c>
+      <c r="G41" s="65" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="65" t="n">
+        <v>173</v>
+      </c>
+      <c r="I41" s="65" t="n">
+        <v>259</v>
+      </c>
+      <c r="J41" s="65" t="n">
+        <v>374</v>
+      </c>
+      <c r="K41" s="65" t="n">
+        <v>491</v>
+      </c>
+      <c r="L41" s="65" t="n">
+        <v>706</v>
+      </c>
+      <c r="M41" s="65" t="n">
+        <v>907</v>
+      </c>
+      <c r="N41" s="65" t="n">
+        <v>3095</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">  TikTok Shop 粗利</t>
         </is>
       </c>
-      <c r="B40" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="74" t="n">
+      <c r="B42" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="E40" s="74" t="n">
-        <v>12</v>
-      </c>
-      <c r="F40" s="74" t="n">
-        <v>25</v>
-      </c>
-      <c r="G40" s="74" t="n">
-        <v>47</v>
-      </c>
-      <c r="H40" s="74" t="n">
-        <v>82</v>
-      </c>
-      <c r="I40" s="74" t="n">
-        <v>122</v>
-      </c>
-      <c r="J40" s="74" t="n">
-        <v>177</v>
-      </c>
-      <c r="K40" s="74" t="n">
-        <v>232</v>
-      </c>
-      <c r="L40" s="74" t="n">
-        <v>333</v>
-      </c>
-      <c r="M40" s="74" t="n">
-        <v>428</v>
-      </c>
-      <c r="N40" s="74" t="n">
-        <v>1463</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="70" t="inlineStr">
+      <c r="E42" s="74" t="n">
+        <v>11</v>
+      </c>
+      <c r="F42" s="74" t="n">
+        <v>20</v>
+      </c>
+      <c r="G42" s="74" t="n">
+        <v>38</v>
+      </c>
+      <c r="H42" s="74" t="n">
+        <v>67</v>
+      </c>
+      <c r="I42" s="74" t="n">
+        <v>101</v>
+      </c>
+      <c r="J42" s="74" t="n">
+        <v>146</v>
+      </c>
+      <c r="K42" s="74" t="n">
+        <v>191</v>
+      </c>
+      <c r="L42" s="74" t="n">
+        <v>274</v>
+      </c>
+      <c r="M42" s="74" t="n">
+        <v>353</v>
+      </c>
+      <c r="N42" s="74" t="n">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  TikTok Shop 粗利率</t>
         </is>
       </c>
-      <c r="B41" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="71" t="n">
+      <c r="B43" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="71" t="n">
         <v>35.7</v>
       </c>
-      <c r="E41" s="71" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="F41" s="71" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="G41" s="71" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="H41" s="71" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="I41" s="71" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="J41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="K41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="L41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="M41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="N41" s="72" t="n">
-        <v>34.3</v>
-      </c>
-    </row>
-    <row r="42" ht="6" customHeight="1">
-      <c r="A42" s="67" t="inlineStr"/>
-      <c r="B42" s="68" t="n"/>
-      <c r="C42" s="68" t="n"/>
-      <c r="D42" s="68" t="n"/>
-      <c r="E42" s="68" t="n"/>
-      <c r="F42" s="68" t="n"/>
-      <c r="G42" s="68" t="n"/>
-      <c r="H42" s="68" t="n"/>
-      <c r="I42" s="68" t="n"/>
-      <c r="J42" s="68" t="n"/>
-      <c r="K42" s="68" t="n"/>
-      <c r="L42" s="68" t="n"/>
-      <c r="M42" s="68" t="n"/>
-      <c r="N42" s="68" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="75" t="inlineStr">
+      <c r="E43" s="71" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F43" s="71" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G43" s="71" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H43" s="71" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="I43" s="71" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J43" s="71" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="K43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="L43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="M43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="N43" s="72" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="44" ht="6" customHeight="1">
+      <c r="A44" s="67" t="inlineStr"/>
+      <c r="B44" s="68" t="n"/>
+      <c r="C44" s="68" t="n"/>
+      <c r="D44" s="68" t="n"/>
+      <c r="E44" s="68" t="n"/>
+      <c r="F44" s="68" t="n"/>
+      <c r="G44" s="68" t="n"/>
+      <c r="H44" s="68" t="n"/>
+      <c r="I44" s="68" t="n"/>
+      <c r="J44" s="68" t="n"/>
+      <c r="K44" s="68" t="n"/>
+      <c r="L44" s="68" t="n"/>
+      <c r="M44" s="68" t="n"/>
+      <c r="N44" s="68" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="75" t="inlineStr">
         <is>
           <t>売上原価合計</t>
         </is>
       </c>
-      <c r="B43" s="76" t="n">
+      <c r="B45" s="76" t="n">
         <v>10</v>
       </c>
-      <c r="C43" s="76" t="n">
+      <c r="C45" s="76" t="n">
         <v>10</v>
       </c>
-      <c r="D43" s="76" t="n">
+      <c r="D45" s="76" t="n">
         <v>19</v>
       </c>
-      <c r="E43" s="76" t="n">
-        <v>63</v>
-      </c>
-      <c r="F43" s="76" t="n">
-        <v>127</v>
-      </c>
-      <c r="G43" s="76" t="n">
-        <v>171</v>
-      </c>
-      <c r="H43" s="76" t="n">
-        <v>278</v>
-      </c>
-      <c r="I43" s="76" t="n">
-        <v>398</v>
-      </c>
-      <c r="J43" s="76" t="n">
-        <v>503</v>
-      </c>
-      <c r="K43" s="76" t="n">
-        <v>610</v>
-      </c>
-      <c r="L43" s="76" t="n">
-        <v>847</v>
-      </c>
-      <c r="M43" s="76" t="n">
-        <v>1072</v>
-      </c>
-      <c r="N43" s="76" t="n">
-        <v>4108</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="77" t="inlineStr">
+      <c r="E45" s="76" t="n">
+        <v>64</v>
+      </c>
+      <c r="F45" s="76" t="n">
+        <v>132</v>
+      </c>
+      <c r="G45" s="76" t="n">
+        <v>180</v>
+      </c>
+      <c r="H45" s="76" t="n">
+        <v>293</v>
+      </c>
+      <c r="I45" s="76" t="n">
+        <v>419</v>
+      </c>
+      <c r="J45" s="76" t="n">
+        <v>534</v>
+      </c>
+      <c r="K45" s="76" t="n">
+        <v>651</v>
+      </c>
+      <c r="L45" s="76" t="n">
+        <v>906</v>
+      </c>
+      <c r="M45" s="76" t="n">
+        <v>1147</v>
+      </c>
+      <c r="N45" s="76" t="n">
+        <v>4365</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="77" t="inlineStr">
         <is>
           <t>粗利益合計</t>
         </is>
       </c>
-      <c r="B44" s="78" t="n">
+      <c r="B46" s="78" t="n">
         <v>-10</v>
       </c>
-      <c r="C44" s="78" t="n">
+      <c r="C46" s="78" t="n">
         <v>-10</v>
       </c>
-      <c r="D44" s="78" t="n">
+      <c r="D46" s="78" t="n">
         <v>-5</v>
       </c>
-      <c r="E44" s="79" t="n">
-        <v>122</v>
-      </c>
-      <c r="F44" s="79" t="n">
-        <v>245</v>
-      </c>
-      <c r="G44" s="79" t="n">
-        <v>267</v>
-      </c>
-      <c r="H44" s="79" t="n">
-        <v>412</v>
-      </c>
-      <c r="I44" s="79" t="n">
-        <v>562</v>
-      </c>
-      <c r="J44" s="79" t="n">
-        <v>617</v>
-      </c>
-      <c r="K44" s="79" t="n">
-        <v>672</v>
-      </c>
-      <c r="L44" s="79" t="n">
-        <v>883</v>
-      </c>
-      <c r="M44" s="79" t="n">
-        <v>1088</v>
-      </c>
-      <c r="N44" s="79" t="n">
-        <v>4843</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="70" t="inlineStr">
+      <c r="E46" s="79" t="n">
+        <v>121</v>
+      </c>
+      <c r="F46" s="79" t="n">
+        <v>240</v>
+      </c>
+      <c r="G46" s="79" t="n">
+        <v>258</v>
+      </c>
+      <c r="H46" s="79" t="n">
+        <v>397</v>
+      </c>
+      <c r="I46" s="79" t="n">
+        <v>541</v>
+      </c>
+      <c r="J46" s="79" t="n">
+        <v>586</v>
+      </c>
+      <c r="K46" s="79" t="n">
+        <v>631</v>
+      </c>
+      <c r="L46" s="79" t="n">
+        <v>824</v>
+      </c>
+      <c r="M46" s="79" t="n">
+        <v>1013</v>
+      </c>
+      <c r="N46" s="79" t="n">
+        <v>4586</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="70" t="inlineStr">
         <is>
           <t>粗利率（合計）</t>
         </is>
       </c>
-      <c r="B45" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="71" t="n">
+      <c r="B47" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="71" t="n">
         <v>-35.7</v>
       </c>
-      <c r="E45" s="71" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="F45" s="71" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="G45" s="71" t="n">
-        <v>61</v>
-      </c>
-      <c r="H45" s="71" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="I45" s="71" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="J45" s="71" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="K45" s="71" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="L45" s="71" t="n">
-        <v>51</v>
-      </c>
-      <c r="M45" s="71" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="N45" s="72" t="n">
-        <v>48.4</v>
-      </c>
-    </row>
-    <row r="46" ht="6" customHeight="1">
-      <c r="A46" s="67" t="inlineStr"/>
-      <c r="B46" s="68" t="n"/>
-      <c r="C46" s="68" t="n"/>
-      <c r="D46" s="68" t="n"/>
-      <c r="E46" s="68" t="n"/>
-      <c r="F46" s="68" t="n"/>
-      <c r="G46" s="68" t="n"/>
-      <c r="H46" s="68" t="n"/>
-      <c r="I46" s="68" t="n"/>
-      <c r="J46" s="68" t="n"/>
-      <c r="K46" s="68" t="n"/>
-      <c r="L46" s="68" t="n"/>
-      <c r="M46" s="68" t="n"/>
-      <c r="N46" s="68" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="57" t="inlineStr">
+      <c r="E47" s="71" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="F47" s="71" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G47" s="71" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="H47" s="71" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="I47" s="71" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="J47" s="71" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="K47" s="71" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="L47" s="71" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="M47" s="71" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="N47" s="72" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="48" ht="6" customHeight="1">
+      <c r="A48" s="67" t="inlineStr"/>
+      <c r="B48" s="68" t="n"/>
+      <c r="C48" s="68" t="n"/>
+      <c r="D48" s="68" t="n"/>
+      <c r="E48" s="68" t="n"/>
+      <c r="F48" s="68" t="n"/>
+      <c r="G48" s="68" t="n"/>
+      <c r="H48" s="68" t="n"/>
+      <c r="I48" s="68" t="n"/>
+      <c r="J48" s="68" t="n"/>
+      <c r="K48" s="68" t="n"/>
+      <c r="L48" s="68" t="n"/>
+      <c r="M48" s="68" t="n"/>
+      <c r="N48" s="68" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="57" t="inlineStr">
         <is>
           <t>【販売管理費】</t>
         </is>
       </c>
-      <c r="B47" s="58" t="n"/>
-      <c r="C47" s="58" t="n"/>
-      <c r="D47" s="58" t="n"/>
-      <c r="E47" s="58" t="n"/>
-      <c r="F47" s="58" t="n"/>
-      <c r="G47" s="58" t="n"/>
-      <c r="H47" s="58" t="n"/>
-      <c r="I47" s="58" t="n"/>
-      <c r="J47" s="58" t="n"/>
-      <c r="K47" s="58" t="n"/>
-      <c r="L47" s="58" t="n"/>
-      <c r="M47" s="58" t="n"/>
-      <c r="N47" s="58" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
-        </is>
-      </c>
-      <c r="B48" s="59" t="n">
-        <v>80</v>
-      </c>
-      <c r="C48" s="59" t="n">
-        <v>80</v>
-      </c>
-      <c r="D48" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="E48" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="F48" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="G48" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="H48" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="I48" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="J48" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="K48" s="59" t="n">
-        <v>200</v>
-      </c>
-      <c r="L48" s="59" t="n">
-        <v>200</v>
-      </c>
-      <c r="M48" s="59" t="n">
-        <v>200</v>
-      </c>
-      <c r="N48" s="55" t="n">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  人件費（バズ社員）</t>
-        </is>
-      </c>
-      <c r="B49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="C49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="D49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="E49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="F49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="G49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="H49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="I49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="J49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="K49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="L49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="M49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="N49" s="55" t="n">
-        <v>1200</v>
-      </c>
+      <c r="B49" s="58" t="n"/>
+      <c r="C49" s="58" t="n"/>
+      <c r="D49" s="58" t="n"/>
+      <c r="E49" s="58" t="n"/>
+      <c r="F49" s="58" t="n"/>
+      <c r="G49" s="58" t="n"/>
+      <c r="H49" s="58" t="n"/>
+      <c r="I49" s="58" t="n"/>
+      <c r="J49" s="58" t="n"/>
+      <c r="K49" s="58" t="n"/>
+      <c r="L49" s="58" t="n"/>
+      <c r="M49" s="58" t="n"/>
+      <c r="N49" s="58" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  その他販管費</t>
+          <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
         </is>
       </c>
       <c r="B50" s="59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C50" s="59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D50" s="59" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E50" s="59" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F50" s="59" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G50" s="59" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H50" s="59" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I50" s="59" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="J50" s="59" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="K50" s="59" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="L50" s="59" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="M50" s="59" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="N50" s="55" t="n">
-        <v>760</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="36" t="inlineStr">
         <is>
+          <t xml:space="preserve">  人件費（バズ社員）</t>
+        </is>
+      </c>
+      <c r="B51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="C51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="D51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="F51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="H51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="I51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="K51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="L51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="M51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="N51" s="55" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  その他販管費</t>
+        </is>
+      </c>
+      <c r="B52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="E52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G52" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="H52" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="I52" s="59" t="n">
+        <v>70</v>
+      </c>
+      <c r="J52" s="59" t="n">
+        <v>70</v>
+      </c>
+      <c r="K52" s="59" t="n">
+        <v>80</v>
+      </c>
+      <c r="L52" s="59" t="n">
+        <v>80</v>
+      </c>
+      <c r="M52" s="59" t="n">
+        <v>80</v>
+      </c>
+      <c r="N52" s="55" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ENTIAL業務委託費（TIE×5%＋EC×3%）</t>
         </is>
       </c>
-      <c r="B51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="59" t="n">
+      <c r="B53" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="F51" s="59" t="n">
+      <c r="F53" s="59" t="n">
         <v>17</v>
       </c>
-      <c r="G51" s="59" t="n">
+      <c r="G53" s="59" t="n">
         <v>19</v>
       </c>
-      <c r="H51" s="59" t="n">
+      <c r="H53" s="59" t="n">
         <v>29</v>
       </c>
-      <c r="I51" s="59" t="n">
+      <c r="I53" s="59" t="n">
         <v>41</v>
       </c>
-      <c r="J51" s="59" t="n">
+      <c r="J53" s="59" t="n">
         <v>46</v>
       </c>
-      <c r="K51" s="59" t="n">
+      <c r="K53" s="59" t="n">
         <v>50</v>
       </c>
-      <c r="L51" s="59" t="n">
+      <c r="L53" s="59" t="n">
         <v>67</v>
       </c>
-      <c r="M51" s="59" t="n">
+      <c r="M53" s="59" t="n">
         <v>83</v>
       </c>
-      <c r="N51" s="55" t="n">
+      <c r="N53" s="55" t="n">
         <v>361</v>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="75" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="75" t="inlineStr">
         <is>
           <t>販売管理費合計</t>
         </is>
       </c>
-      <c r="B52" s="76" t="n">
+      <c r="B54" s="76" t="n">
         <v>230</v>
       </c>
-      <c r="C52" s="76" t="n">
+      <c r="C54" s="76" t="n">
         <v>230</v>
       </c>
-      <c r="D52" s="76" t="n">
+      <c r="D54" s="76" t="n">
         <v>250</v>
       </c>
-      <c r="E52" s="76" t="n">
+      <c r="E54" s="76" t="n">
         <v>259</v>
       </c>
-      <c r="F52" s="76" t="n">
+      <c r="F54" s="76" t="n">
         <v>297</v>
       </c>
-      <c r="G52" s="76" t="n">
+      <c r="G54" s="76" t="n">
         <v>299</v>
       </c>
-      <c r="H52" s="76" t="n">
+      <c r="H54" s="76" t="n">
         <v>339</v>
       </c>
-      <c r="I52" s="76" t="n">
+      <c r="I54" s="76" t="n">
         <v>361</v>
       </c>
-      <c r="J52" s="76" t="n">
+      <c r="J54" s="76" t="n">
         <v>366</v>
       </c>
-      <c r="K52" s="76" t="n">
+      <c r="K54" s="76" t="n">
         <v>430</v>
       </c>
-      <c r="L52" s="76" t="n">
+      <c r="L54" s="76" t="n">
         <v>447</v>
       </c>
-      <c r="M52" s="76" t="n">
+      <c r="M54" s="76" t="n">
         <v>463</v>
       </c>
-      <c r="N52" s="76" t="n">
+      <c r="N54" s="76" t="n">
         <v>3971</v>
       </c>
     </row>
-    <row r="53" ht="6" customHeight="1">
-      <c r="A53" s="67" t="inlineStr"/>
-      <c r="B53" s="68" t="n"/>
-      <c r="C53" s="68" t="n"/>
-      <c r="D53" s="68" t="n"/>
-      <c r="E53" s="68" t="n"/>
-      <c r="F53" s="68" t="n"/>
-      <c r="G53" s="68" t="n"/>
-      <c r="H53" s="68" t="n"/>
-      <c r="I53" s="68" t="n"/>
-      <c r="J53" s="68" t="n"/>
-      <c r="K53" s="68" t="n"/>
-      <c r="L53" s="68" t="n"/>
-      <c r="M53" s="68" t="n"/>
-      <c r="N53" s="68" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="56" t="inlineStr">
+    <row r="55" ht="6" customHeight="1">
+      <c r="A55" s="67" t="inlineStr"/>
+      <c r="B55" s="68" t="n"/>
+      <c r="C55" s="68" t="n"/>
+      <c r="D55" s="68" t="n"/>
+      <c r="E55" s="68" t="n"/>
+      <c r="F55" s="68" t="n"/>
+      <c r="G55" s="68" t="n"/>
+      <c r="H55" s="68" t="n"/>
+      <c r="I55" s="68" t="n"/>
+      <c r="J55" s="68" t="n"/>
+      <c r="K55" s="68" t="n"/>
+      <c r="L55" s="68" t="n"/>
+      <c r="M55" s="68" t="n"/>
+      <c r="N55" s="68" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="B54" s="80" t="n">
+      <c r="B56" s="80" t="n">
         <v>-240</v>
       </c>
-      <c r="C54" s="80" t="n">
+      <c r="C56" s="80" t="n">
         <v>-240</v>
       </c>
-      <c r="D54" s="80" t="n">
+      <c r="D56" s="80" t="n">
         <v>-255</v>
       </c>
-      <c r="E54" s="80" t="n">
-        <v>-137</v>
-      </c>
-      <c r="F54" s="80" t="n">
-        <v>-52</v>
-      </c>
-      <c r="G54" s="80" t="n">
-        <v>-32</v>
-      </c>
-      <c r="H54" s="81" t="n">
-        <v>73</v>
-      </c>
-      <c r="I54" s="82" t="n">
+      <c r="E56" s="80" t="n">
+        <v>-138</v>
+      </c>
+      <c r="F56" s="80" t="n">
+        <v>-57</v>
+      </c>
+      <c r="G56" s="80" t="n">
+        <v>-41</v>
+      </c>
+      <c r="H56" s="81" t="n">
+        <v>58</v>
+      </c>
+      <c r="I56" s="82" t="n">
+        <v>180</v>
+      </c>
+      <c r="J56" s="82" t="n">
+        <v>220</v>
+      </c>
+      <c r="K56" s="82" t="n">
         <v>201</v>
       </c>
-      <c r="J54" s="82" t="n">
-        <v>251</v>
-      </c>
-      <c r="K54" s="82" t="n">
-        <v>242</v>
-      </c>
-      <c r="L54" s="82" t="n">
-        <v>436</v>
-      </c>
-      <c r="M54" s="82" t="n">
-        <v>625</v>
-      </c>
-      <c r="N54" s="81" t="n">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="70" t="inlineStr">
+      <c r="L56" s="82" t="n">
+        <v>377</v>
+      </c>
+      <c r="M56" s="82" t="n">
+        <v>550</v>
+      </c>
+      <c r="N56" s="81" t="n">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="70" t="inlineStr">
         <is>
           <t>営業利益率</t>
         </is>
       </c>
-      <c r="B55" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="71" t="n">
+      <c r="B57" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="71" t="n">
         <v>-1821.4</v>
       </c>
-      <c r="E55" s="71" t="n">
-        <v>-74.09999999999999</v>
-      </c>
-      <c r="F55" s="71" t="n">
-        <v>-14</v>
-      </c>
-      <c r="G55" s="71" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="H55" s="71" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I55" s="71" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J55" s="71" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="K55" s="71" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="L55" s="71" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="M55" s="71" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="N55" s="72" t="n">
-        <v>-179</v>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="83" t="inlineStr">
-        <is>
-          <t>★ 損益分岐：M7　／　Year1通期営業利益：872万円　／　Year1売上：8,951万円</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="84" t="inlineStr">
-        <is>
-          <t>【注記】単位：万円 ／ ギャル協会：出演・監修料=件数×25万（月最低保証10万）＋EC RS 15% ／ 制作費：TIE売上×10% ／ EC原価率66%（仕入45%＋TK手数料6%＋ギャル協会RS15%）／ ENTIAL：完全成功報酬（TIE×5%＋EC×3%、固定費ゼロ）</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="n"/>
-      <c r="N57" s="2" t="n"/>
+      <c r="E57" s="71" t="n">
+        <v>-74.59999999999999</v>
+      </c>
+      <c r="F57" s="71" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="G57" s="71" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="H57" s="71" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I57" s="71" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J57" s="71" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="K57" s="71" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L57" s="71" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="M57" s="71" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="N57" s="72" t="n">
+        <v>-181.1</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="83" t="inlineStr">
+        <is>
+          <t>★ 損益分岐：M7　／　Year1通期営業利益：615万円　／　Year1売上：8,951万円</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="84" t="inlineStr">
+        <is>
+          <t>【注記】単位：万円 ／ ギャル協会：出演・監修料=件数×25万（月最低保証10万）＋EC RS 15% ／ 制作費：TIE売上×10% ／ EC原価合計72%（仕入45%＋TK手数料M1-3:3%/M4-:7%＋RS15%＋物流4%＋在庫損失1%）／ ENTIAL：完全成功報酬（TIE×5%＋EC×3%、固定費ゼロ）</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A56:N56"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A57:N57"/>
+    <mergeCell ref="A59:N59"/>
     <mergeCell ref="A13:N13"/>
+    <mergeCell ref="A58:N58"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6538,7 +6722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6567,7 +6751,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="47" t="inlineStr">
         <is>
-          <t>Year1で売上1,171万・営業損失2,373万・M9末で撤退決定　単位：万円</t>
+          <t>Year1で売上1,171万・営業損失2,409万・M9末で撤退決定　単位：万円</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8332,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TikTok Shop手数料（×6%）</t>
+          <t xml:space="preserve">  TikTok Shop手数料（M1-3:3%→M4-:7%）</t>
         </is>
       </c>
       <c r="B37" s="59" t="n">
@@ -8161,34 +8345,34 @@
         <v>0</v>
       </c>
       <c r="E37" s="59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J37" s="59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K37" s="59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L37" s="59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M37" s="59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N37" s="55" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -8238,460 +8422,460 @@
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="64" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  物流・梱包費（×4%）</t>
+        </is>
+      </c>
+      <c r="B39" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="M39" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" s="55" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  在庫損失引当（×1%）</t>
+        </is>
+      </c>
+      <c r="B40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">  EC原価合計</t>
         </is>
       </c>
-      <c r="B39" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="65" t="n">
+      <c r="B41" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="E39" s="65" t="n">
+      <c r="E41" s="65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" s="65" t="n">
+        <v>13</v>
+      </c>
+      <c r="G41" s="65" t="n">
+        <v>25</v>
+      </c>
+      <c r="H41" s="65" t="n">
+        <v>36</v>
+      </c>
+      <c r="I41" s="65" t="n">
+        <v>48</v>
+      </c>
+      <c r="J41" s="65" t="n">
+        <v>54</v>
+      </c>
+      <c r="K41" s="65" t="n">
+        <v>65</v>
+      </c>
+      <c r="L41" s="65" t="n">
+        <v>72</v>
+      </c>
+      <c r="M41" s="65" t="n">
+        <v>90</v>
+      </c>
+      <c r="N41" s="65" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TikTok Shop 粗利</t>
+        </is>
+      </c>
+      <c r="B42" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="74" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="F39" s="65" t="n">
-        <v>12</v>
-      </c>
-      <c r="G39" s="65" t="n">
-        <v>23</v>
-      </c>
-      <c r="H39" s="65" t="n">
-        <v>33</v>
-      </c>
-      <c r="I39" s="65" t="n">
-        <v>43</v>
-      </c>
-      <c r="J39" s="65" t="n">
-        <v>49</v>
-      </c>
-      <c r="K39" s="65" t="n">
-        <v>59</v>
-      </c>
-      <c r="L39" s="65" t="n">
-        <v>66</v>
-      </c>
-      <c r="M39" s="65" t="n">
-        <v>83</v>
-      </c>
-      <c r="N39" s="65" t="n">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TikTok Shop 粗利</t>
-        </is>
-      </c>
-      <c r="B40" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="74" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="74" t="n">
-        <v>6</v>
-      </c>
-      <c r="G40" s="74" t="n">
+      <c r="G42" s="74" t="n">
+        <v>11</v>
+      </c>
+      <c r="H42" s="74" t="n">
+        <v>14</v>
+      </c>
+      <c r="I42" s="74" t="n">
+        <v>17</v>
+      </c>
+      <c r="J42" s="74" t="n">
+        <v>21</v>
+      </c>
+      <c r="K42" s="74" t="n">
+        <v>25</v>
+      </c>
+      <c r="L42" s="74" t="n">
+        <v>28</v>
+      </c>
+      <c r="M42" s="74" t="n">
+        <v>35</v>
+      </c>
+      <c r="N42" s="74" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TikTok Shop 粗利率</t>
+        </is>
+      </c>
+      <c r="B43" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="71" t="n">
+        <v>25</v>
+      </c>
+      <c r="E43" s="71" t="n">
+        <v>25</v>
+      </c>
+      <c r="F43" s="71" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G43" s="71" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="H43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="I43" s="71" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="J43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="K43" s="71" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="L43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="M43" s="71" t="n">
+        <v>28</v>
+      </c>
+      <c r="N43" s="72" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="44" ht="6" customHeight="1">
+      <c r="A44" s="67" t="inlineStr"/>
+      <c r="B44" s="68" t="n"/>
+      <c r="C44" s="68" t="n"/>
+      <c r="D44" s="68" t="n"/>
+      <c r="E44" s="68" t="n"/>
+      <c r="F44" s="68" t="n"/>
+      <c r="G44" s="68" t="n"/>
+      <c r="H44" s="68" t="n"/>
+      <c r="I44" s="68" t="n"/>
+      <c r="J44" s="68" t="n"/>
+      <c r="K44" s="68" t="n"/>
+      <c r="L44" s="68" t="n"/>
+      <c r="M44" s="68" t="n"/>
+      <c r="N44" s="68" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="75" t="inlineStr">
+        <is>
+          <t>売上原価合計</t>
+        </is>
+      </c>
+      <c r="B45" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="C45" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="76" t="n">
         <v>13</v>
       </c>
-      <c r="H40" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="I40" s="74" t="n">
-        <v>22</v>
-      </c>
-      <c r="J40" s="74" t="n">
-        <v>26</v>
-      </c>
-      <c r="K40" s="74" t="n">
-        <v>31</v>
-      </c>
-      <c r="L40" s="74" t="n">
-        <v>34</v>
-      </c>
-      <c r="M40" s="74" t="n">
-        <v>42</v>
-      </c>
-      <c r="N40" s="74" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TikTok Shop 粗利率</t>
-        </is>
-      </c>
-      <c r="B41" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="71" t="n">
+      <c r="E45" s="76" t="n">
+        <v>16</v>
+      </c>
+      <c r="F45" s="76" t="n">
+        <v>48</v>
+      </c>
+      <c r="G45" s="76" t="n">
+        <v>60</v>
+      </c>
+      <c r="H45" s="76" t="n">
+        <v>71</v>
+      </c>
+      <c r="I45" s="76" t="n">
+        <v>58</v>
+      </c>
+      <c r="J45" s="76" t="n">
+        <v>124</v>
+      </c>
+      <c r="K45" s="76" t="n">
+        <v>100</v>
+      </c>
+      <c r="L45" s="76" t="n">
+        <v>82</v>
+      </c>
+      <c r="M45" s="76" t="n">
+        <v>100</v>
+      </c>
+      <c r="N45" s="76" t="n">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="77" t="inlineStr">
+        <is>
+          <t>粗利益合計</t>
+        </is>
+      </c>
+      <c r="B46" s="78" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C46" s="78" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D46" s="78" t="n">
+        <v>-9</v>
+      </c>
+      <c r="E46" s="78" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F46" s="79" t="n">
+        <v>70</v>
+      </c>
+      <c r="G46" s="79" t="n">
+        <v>76</v>
+      </c>
+      <c r="H46" s="79" t="n">
+        <v>79</v>
+      </c>
+      <c r="I46" s="79" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" s="79" t="n">
+        <v>151</v>
+      </c>
+      <c r="K46" s="79" t="n">
+        <v>90</v>
+      </c>
+      <c r="L46" s="79" t="n">
+        <v>18</v>
+      </c>
+      <c r="M46" s="79" t="n">
         <v>25</v>
       </c>
-      <c r="E41" s="71" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F41" s="71" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G41" s="71" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="H41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="I41" s="71" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="J41" s="71" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="K41" s="71" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="L41" s="71" t="n">
-        <v>34</v>
-      </c>
-      <c r="M41" s="71" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="N41" s="72" t="n">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="42" ht="6" customHeight="1">
-      <c r="A42" s="67" t="inlineStr"/>
-      <c r="B42" s="68" t="n"/>
-      <c r="C42" s="68" t="n"/>
-      <c r="D42" s="68" t="n"/>
-      <c r="E42" s="68" t="n"/>
-      <c r="F42" s="68" t="n"/>
-      <c r="G42" s="68" t="n"/>
-      <c r="H42" s="68" t="n"/>
-      <c r="I42" s="68" t="n"/>
-      <c r="J42" s="68" t="n"/>
-      <c r="K42" s="68" t="n"/>
-      <c r="L42" s="68" t="n"/>
-      <c r="M42" s="68" t="n"/>
-      <c r="N42" s="68" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="75" t="inlineStr">
-        <is>
-          <t>売上原価合計</t>
-        </is>
-      </c>
-      <c r="B43" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="C43" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="D43" s="76" t="n">
-        <v>13</v>
-      </c>
-      <c r="E43" s="76" t="n">
-        <v>15</v>
-      </c>
-      <c r="F43" s="76" t="n">
-        <v>47</v>
-      </c>
-      <c r="G43" s="76" t="n">
-        <v>58</v>
-      </c>
-      <c r="H43" s="76" t="n">
-        <v>68</v>
-      </c>
-      <c r="I43" s="76" t="n">
-        <v>53</v>
-      </c>
-      <c r="J43" s="76" t="n">
-        <v>119</v>
-      </c>
-      <c r="K43" s="76" t="n">
-        <v>94</v>
-      </c>
-      <c r="L43" s="76" t="n">
-        <v>76</v>
-      </c>
-      <c r="M43" s="76" t="n">
-        <v>93</v>
-      </c>
-      <c r="N43" s="76" t="n">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="77" t="inlineStr">
-        <is>
-          <t>粗利益合計</t>
-        </is>
-      </c>
-      <c r="B44" s="78" t="n">
-        <v>-10</v>
-      </c>
-      <c r="C44" s="78" t="n">
-        <v>-10</v>
-      </c>
-      <c r="D44" s="78" t="n">
-        <v>-9</v>
-      </c>
-      <c r="E44" s="78" t="n">
-        <v>-7</v>
-      </c>
-      <c r="F44" s="79" t="n">
-        <v>71</v>
-      </c>
-      <c r="G44" s="79" t="n">
-        <v>78</v>
-      </c>
-      <c r="H44" s="79" t="n">
-        <v>82</v>
-      </c>
-      <c r="I44" s="79" t="n">
-        <v>12</v>
-      </c>
-      <c r="J44" s="79" t="n">
-        <v>156</v>
-      </c>
-      <c r="K44" s="79" t="n">
-        <v>96</v>
-      </c>
-      <c r="L44" s="79" t="n">
-        <v>24</v>
-      </c>
-      <c r="M44" s="79" t="n">
-        <v>32</v>
-      </c>
-      <c r="N44" s="79" t="n">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="70" t="inlineStr">
+      <c r="N46" s="79" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="70" t="inlineStr">
         <is>
           <t>粗利率（合計）</t>
         </is>
       </c>
-      <c r="B45" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="71" t="n">
+      <c r="B47" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="71" t="n">
         <v>-225</v>
       </c>
-      <c r="E45" s="71" t="n">
-        <v>-87.5</v>
-      </c>
-      <c r="F45" s="71" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="G45" s="71" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="H45" s="71" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I45" s="71" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J45" s="71" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="K45" s="71" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="L45" s="71" t="n">
-        <v>24</v>
-      </c>
-      <c r="M45" s="71" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="N45" s="72" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="46" ht="6" customHeight="1">
-      <c r="A46" s="67" t="inlineStr"/>
-      <c r="B46" s="68" t="n"/>
-      <c r="C46" s="68" t="n"/>
-      <c r="D46" s="68" t="n"/>
-      <c r="E46" s="68" t="n"/>
-      <c r="F46" s="68" t="n"/>
-      <c r="G46" s="68" t="n"/>
-      <c r="H46" s="68" t="n"/>
-      <c r="I46" s="68" t="n"/>
-      <c r="J46" s="68" t="n"/>
-      <c r="K46" s="68" t="n"/>
-      <c r="L46" s="68" t="n"/>
-      <c r="M46" s="68" t="n"/>
-      <c r="N46" s="68" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="57" t="inlineStr">
+      <c r="E47" s="71" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F47" s="71" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G47" s="71" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="H47" s="71" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="I47" s="71" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J47" s="71" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="K47" s="71" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="L47" s="71" t="n">
+        <v>18</v>
+      </c>
+      <c r="M47" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="N47" s="72" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="48" ht="6" customHeight="1">
+      <c r="A48" s="67" t="inlineStr"/>
+      <c r="B48" s="68" t="n"/>
+      <c r="C48" s="68" t="n"/>
+      <c r="D48" s="68" t="n"/>
+      <c r="E48" s="68" t="n"/>
+      <c r="F48" s="68" t="n"/>
+      <c r="G48" s="68" t="n"/>
+      <c r="H48" s="68" t="n"/>
+      <c r="I48" s="68" t="n"/>
+      <c r="J48" s="68" t="n"/>
+      <c r="K48" s="68" t="n"/>
+      <c r="L48" s="68" t="n"/>
+      <c r="M48" s="68" t="n"/>
+      <c r="N48" s="68" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="57" t="inlineStr">
         <is>
           <t>【販売管理費】</t>
         </is>
       </c>
-      <c r="B47" s="58" t="n"/>
-      <c r="C47" s="58" t="n"/>
-      <c r="D47" s="58" t="n"/>
-      <c r="E47" s="58" t="n"/>
-      <c r="F47" s="58" t="n"/>
-      <c r="G47" s="58" t="n"/>
-      <c r="H47" s="58" t="n"/>
-      <c r="I47" s="58" t="n"/>
-      <c r="J47" s="58" t="n"/>
-      <c r="K47" s="58" t="n"/>
-      <c r="L47" s="58" t="n"/>
-      <c r="M47" s="58" t="n"/>
-      <c r="N47" s="58" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
-        </is>
-      </c>
-      <c r="B48" s="59" t="n">
-        <v>80</v>
-      </c>
-      <c r="C48" s="59" t="n">
-        <v>80</v>
-      </c>
-      <c r="D48" s="59" t="n">
-        <v>80</v>
-      </c>
-      <c r="E48" s="59" t="n">
-        <v>80</v>
-      </c>
-      <c r="F48" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="G48" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="H48" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="I48" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="J48" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="K48" s="59" t="n">
-        <v>80</v>
-      </c>
-      <c r="L48" s="59" t="n">
-        <v>50</v>
-      </c>
-      <c r="M48" s="59" t="n">
-        <v>50</v>
-      </c>
-      <c r="N48" s="55" t="n">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  人件費（バズ社員）</t>
-        </is>
-      </c>
-      <c r="B49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="C49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="D49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="E49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="F49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="G49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="H49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="I49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="J49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="K49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="L49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="M49" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="N49" s="55" t="n">
-        <v>1200</v>
-      </c>
+      <c r="B49" s="58" t="n"/>
+      <c r="C49" s="58" t="n"/>
+      <c r="D49" s="58" t="n"/>
+      <c r="E49" s="58" t="n"/>
+      <c r="F49" s="58" t="n"/>
+      <c r="G49" s="58" t="n"/>
+      <c r="H49" s="58" t="n"/>
+      <c r="I49" s="58" t="n"/>
+      <c r="J49" s="58" t="n"/>
+      <c r="K49" s="58" t="n"/>
+      <c r="L49" s="58" t="n"/>
+      <c r="M49" s="58" t="n"/>
+      <c r="N49" s="58" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  その他販管費</t>
+          <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
         </is>
       </c>
       <c r="B50" s="59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C50" s="59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D50" s="59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E50" s="59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F50" s="59" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G50" s="59" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H50" s="59" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="I50" s="59" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="J50" s="59" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K50" s="59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L50" s="59" t="n">
         <v>50</v>
@@ -8700,256 +8884,348 @@
         <v>50</v>
       </c>
       <c r="N50" s="55" t="n">
-        <v>600</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="36" t="inlineStr">
         <is>
+          <t xml:space="preserve">  人件費（バズ社員）</t>
+        </is>
+      </c>
+      <c r="B51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="C51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="D51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="F51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="H51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="I51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="K51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="L51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="M51" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="N51" s="55" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  その他販管費</t>
+        </is>
+      </c>
+      <c r="B52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="E52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="G52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="H52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="J52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="K52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="L52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="M52" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="N52" s="55" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ENTIAL業務委託費（TIE×5%＋EC×3%）</t>
         </is>
       </c>
-      <c r="B51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="59" t="n">
+      <c r="B53" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="G51" s="59" t="n">
+      <c r="G53" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="H51" s="59" t="n">
+      <c r="H53" s="59" t="n">
         <v>7</v>
       </c>
-      <c r="I51" s="59" t="n">
+      <c r="I53" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="J51" s="59" t="n">
+      <c r="J53" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="K51" s="59" t="n">
+      <c r="K53" s="59" t="n">
         <v>8</v>
       </c>
-      <c r="L51" s="59" t="n">
+      <c r="L53" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="M51" s="59" t="n">
+      <c r="M53" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="N51" s="55" t="n">
+      <c r="N53" s="55" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="75" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="75" t="inlineStr">
         <is>
           <t>販売管理費合計</t>
         </is>
       </c>
-      <c r="B52" s="76" t="n">
+      <c r="B54" s="76" t="n">
         <v>230</v>
       </c>
-      <c r="C52" s="76" t="n">
+      <c r="C54" s="76" t="n">
         <v>230</v>
       </c>
-      <c r="D52" s="76" t="n">
+      <c r="D54" s="76" t="n">
         <v>230</v>
       </c>
-      <c r="E52" s="76" t="n">
+      <c r="E54" s="76" t="n">
         <v>230</v>
       </c>
-      <c r="F52" s="76" t="n">
+      <c r="F54" s="76" t="n">
         <v>256</v>
       </c>
-      <c r="G52" s="76" t="n">
+      <c r="G54" s="76" t="n">
         <v>256</v>
       </c>
-      <c r="H52" s="76" t="n">
+      <c r="H54" s="76" t="n">
         <v>277</v>
       </c>
-      <c r="I52" s="76" t="n">
+      <c r="I54" s="76" t="n">
         <v>272</v>
       </c>
-      <c r="J52" s="76" t="n">
+      <c r="J54" s="76" t="n">
         <v>262</v>
       </c>
-      <c r="K52" s="76" t="n">
+      <c r="K54" s="76" t="n">
         <v>238</v>
       </c>
-      <c r="L52" s="76" t="n">
+      <c r="L54" s="76" t="n">
         <v>203</v>
       </c>
-      <c r="M52" s="76" t="n">
+      <c r="M54" s="76" t="n">
         <v>204</v>
       </c>
-      <c r="N52" s="76" t="n">
+      <c r="N54" s="76" t="n">
         <v>2888</v>
       </c>
     </row>
-    <row r="53" ht="6" customHeight="1">
-      <c r="A53" s="67" t="inlineStr"/>
-      <c r="B53" s="68" t="n"/>
-      <c r="C53" s="68" t="n"/>
-      <c r="D53" s="68" t="n"/>
-      <c r="E53" s="68" t="n"/>
-      <c r="F53" s="68" t="n"/>
-      <c r="G53" s="68" t="n"/>
-      <c r="H53" s="68" t="n"/>
-      <c r="I53" s="68" t="n"/>
-      <c r="J53" s="68" t="n"/>
-      <c r="K53" s="68" t="n"/>
-      <c r="L53" s="68" t="n"/>
-      <c r="M53" s="68" t="n"/>
-      <c r="N53" s="68" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="56" t="inlineStr">
+    <row r="55" ht="6" customHeight="1">
+      <c r="A55" s="67" t="inlineStr"/>
+      <c r="B55" s="68" t="n"/>
+      <c r="C55" s="68" t="n"/>
+      <c r="D55" s="68" t="n"/>
+      <c r="E55" s="68" t="n"/>
+      <c r="F55" s="68" t="n"/>
+      <c r="G55" s="68" t="n"/>
+      <c r="H55" s="68" t="n"/>
+      <c r="I55" s="68" t="n"/>
+      <c r="J55" s="68" t="n"/>
+      <c r="K55" s="68" t="n"/>
+      <c r="L55" s="68" t="n"/>
+      <c r="M55" s="68" t="n"/>
+      <c r="N55" s="68" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="B54" s="80" t="n">
+      <c r="B56" s="80" t="n">
         <v>-240</v>
       </c>
-      <c r="C54" s="80" t="n">
+      <c r="C56" s="80" t="n">
         <v>-240</v>
       </c>
-      <c r="D54" s="80" t="n">
+      <c r="D56" s="80" t="n">
         <v>-239</v>
       </c>
-      <c r="E54" s="80" t="n">
-        <v>-237</v>
-      </c>
-      <c r="F54" s="80" t="n">
+      <c r="E56" s="80" t="n">
+        <v>-238</v>
+      </c>
+      <c r="F56" s="80" t="n">
+        <v>-186</v>
+      </c>
+      <c r="G56" s="80" t="n">
+        <v>-180</v>
+      </c>
+      <c r="H56" s="80" t="n">
+        <v>-198</v>
+      </c>
+      <c r="I56" s="80" t="n">
+        <v>-265</v>
+      </c>
+      <c r="J56" s="80" t="n">
+        <v>-111</v>
+      </c>
+      <c r="K56" s="80" t="n">
+        <v>-148</v>
+      </c>
+      <c r="L56" s="80" t="n">
         <v>-185</v>
       </c>
-      <c r="G54" s="80" t="n">
-        <v>-178</v>
-      </c>
-      <c r="H54" s="80" t="n">
-        <v>-195</v>
-      </c>
-      <c r="I54" s="80" t="n">
-        <v>-260</v>
-      </c>
-      <c r="J54" s="80" t="n">
-        <v>-106</v>
-      </c>
-      <c r="K54" s="80" t="n">
-        <v>-142</v>
-      </c>
-      <c r="L54" s="80" t="n">
+      <c r="M56" s="80" t="n">
         <v>-179</v>
       </c>
-      <c r="M54" s="80" t="n">
-        <v>-172</v>
-      </c>
-      <c r="N54" s="87" t="n">
-        <v>-2373</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="70" t="inlineStr">
+      <c r="N56" s="87" t="n">
+        <v>-2409</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="70" t="inlineStr">
         <is>
           <t>営業利益率</t>
         </is>
       </c>
-      <c r="B55" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="71" t="n">
+      <c r="B57" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="71" t="n">
         <v>-5975</v>
       </c>
-      <c r="E55" s="71" t="n">
-        <v>-2962.5</v>
-      </c>
-      <c r="F55" s="71" t="n">
-        <v>-156.8</v>
-      </c>
-      <c r="G55" s="71" t="n">
-        <v>-130.9</v>
-      </c>
-      <c r="H55" s="71" t="n">
-        <v>-130</v>
-      </c>
-      <c r="I55" s="71" t="n">
-        <v>-400</v>
-      </c>
-      <c r="J55" s="71" t="n">
-        <v>-38.5</v>
-      </c>
-      <c r="K55" s="71" t="n">
-        <v>-74.7</v>
-      </c>
-      <c r="L55" s="71" t="n">
-        <v>-179</v>
-      </c>
-      <c r="M55" s="71" t="n">
-        <v>-137.6</v>
-      </c>
-      <c r="N55" s="72" t="n">
-        <v>-1018.5</v>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="37" t="inlineStr">
-        <is>
-          <t>★ 損益分岐：Year1内で達成せず　／　Year1通期営業利益：-2,373万円　／　Year1売上：1,171万円</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="84" t="inlineStr">
-        <is>
-          <t>【注記】単位：万円 ／ ギャル協会：出演・監修料=件数×25万（月最低保証10万）＋EC RS 15% ／ 制作費：TIE売上×10% ／ EC原価率66%（仕入45%＋TK手数料6%＋ギャル協会RS15%）／ ENTIAL：完全成功報酬（TIE×5%＋EC×3%、固定費ゼロ）</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="n"/>
-      <c r="N57" s="2" t="n"/>
+      <c r="E57" s="71" t="n">
+        <v>-2975</v>
+      </c>
+      <c r="F57" s="71" t="n">
+        <v>-157.6</v>
+      </c>
+      <c r="G57" s="71" t="n">
+        <v>-132.4</v>
+      </c>
+      <c r="H57" s="71" t="n">
+        <v>-132</v>
+      </c>
+      <c r="I57" s="71" t="n">
+        <v>-407.7</v>
+      </c>
+      <c r="J57" s="71" t="n">
+        <v>-40.4</v>
+      </c>
+      <c r="K57" s="71" t="n">
+        <v>-77.90000000000001</v>
+      </c>
+      <c r="L57" s="71" t="n">
+        <v>-185</v>
+      </c>
+      <c r="M57" s="71" t="n">
+        <v>-143.2</v>
+      </c>
+      <c r="N57" s="72" t="n">
+        <v>-1022.6</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="37" t="inlineStr">
+        <is>
+          <t>★ 損益分岐：Year1内で達成せず　／　Year1通期営業利益：-2,409万円　／　Year1売上：1,171万円</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="84" t="inlineStr">
+        <is>
+          <t>【注記】単位：万円 ／ ギャル協会：出演・監修料=件数×25万（月最低保証10万）＋EC RS 15% ／ 制作費：TIE売上×10% ／ EC原価合計72%（仕入45%＋TK手数料M1-3:3%/M4-:7%＋RS15%＋物流4%＋在庫損失1%）／ ENTIAL：完全成功報酬（TIE×5%＋EC×3%、固定費ゼロ）</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A56:N56"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A57:N57"/>
+    <mergeCell ref="A59:N59"/>
     <mergeCell ref="A13:N13"/>
+    <mergeCell ref="A58:N58"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PL_3シナリオ比較.xlsx
+++ b/PL_3シナリオ比較.xlsx
@@ -317,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -401,7 +401,13 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1349,16 +1355,22 @@
           <t xml:space="preserve">  ※EC物販収益はギャル協会のショップ利益（バズPL外）</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="29" t="inlineStr"/>
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
@@ -1392,7 +1404,7 @@
       <c r="D28" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="E28" s="29" t="inlineStr"/>
+      <c r="E28" s="30" t="inlineStr"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -1400,14 +1412,20 @@
           <t xml:space="preserve">  ※体験事業元締め収益は別途（バズPL外）</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>0</v>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E29" s="28" t="inlineStr"/>
     </row>
@@ -1434,13 +1452,13 @@
           <t>【バズ 営業利益（手残り）】</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="32" t="n">
         <v>1854</v>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="32" t="n">
         <v>397</v>
       </c>
-      <c r="D31" s="31" t="n">
+      <c r="D31" s="33" t="n">
         <v>-2435</v>
       </c>
       <c r="E31" s="27" t="inlineStr"/>
@@ -1453,7 +1471,7 @@
       <c r="E32" s="2" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>▌ 撤退判断のKPIゲート（3段階チェック）</t>
         </is>
@@ -1464,68 +1482,68 @@
       <c r="E33" s="2" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="33" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="B34" s="33" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>チェック項目</t>
         </is>
       </c>
-      <c r="C34" s="33" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>撤退基準</t>
         </is>
       </c>
-      <c r="D34" s="33" t="inlineStr">
+      <c r="D34" s="35" t="inlineStr">
         <is>
           <t>アクション</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr"/>
+      <c r="E34" s="36" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>M3末</t>
         </is>
       </c>
-      <c r="B35" s="35" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>TKフォロワー</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>&lt; 2,000人</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="D35" s="37" t="inlineStr">
         <is>
           <t>→ 改善施策を検討</t>
         </is>
       </c>
-      <c r="E35" s="29" t="inlineStr"/>
+      <c r="E35" s="30" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>M3末</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="38" t="inlineStr">
         <is>
           <t>IGフォロワー</t>
         </is>
       </c>
-      <c r="C36" s="36" t="inlineStr">
+      <c r="C36" s="38" t="inlineStr">
         <is>
           <t>&lt; 1,000人</t>
         </is>
       </c>
-      <c r="D36" s="36" t="inlineStr">
+      <c r="D36" s="38" t="inlineStr">
         <is>
           <t>→ 改善施策を検討</t>
         </is>
@@ -1533,45 +1551,45 @@
       <c r="E36" s="28" t="inlineStr"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>M6末</t>
         </is>
       </c>
-      <c r="B37" s="35" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>タイアップ累計受注</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>&lt; 3社</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D37" s="37" t="inlineStr">
         <is>
           <t>→ イエローカード、営業強化</t>
         </is>
       </c>
-      <c r="E37" s="29" t="inlineStr"/>
+      <c r="E37" s="30" t="inlineStr"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="36" t="inlineStr">
+      <c r="A38" s="38" t="inlineStr">
         <is>
           <t>M6末</t>
         </is>
       </c>
-      <c r="B38" s="36" t="inlineStr">
+      <c r="B38" s="38" t="inlineStr">
         <is>
           <t>EC累計注文件数</t>
         </is>
       </c>
-      <c r="C38" s="36" t="inlineStr">
+      <c r="C38" s="38" t="inlineStr">
         <is>
           <t>&lt; 200件</t>
         </is>
       </c>
-      <c r="D38" s="36" t="inlineStr">
+      <c r="D38" s="38" t="inlineStr">
         <is>
           <t>→ イエローカード、施策見直し</t>
         </is>
@@ -1579,142 +1597,142 @@
       <c r="E38" s="28" t="inlineStr"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>M6末</t>
         </is>
       </c>
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>単月営業利益</t>
         </is>
       </c>
-      <c r="C39" s="35" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>&lt; -300万円</t>
         </is>
       </c>
-      <c r="D39" s="35" t="inlineStr">
+      <c r="D39" s="37" t="inlineStr">
         <is>
           <t>→ コスト圧縮検討</t>
         </is>
       </c>
-      <c r="E39" s="29" t="inlineStr"/>
+      <c r="E39" s="30" t="inlineStr"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="37" t="inlineStr">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>M9末</t>
         </is>
       </c>
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>月次タイアップ受注</t>
         </is>
       </c>
-      <c r="C40" s="37" t="inlineStr">
+      <c r="C40" s="39" t="inlineStr">
         <is>
           <t>&lt; 2社</t>
         </is>
       </c>
-      <c r="D40" s="37" t="inlineStr">
+      <c r="D40" s="39" t="inlineStr">
         <is>
           <t>→ ★撤退決定</t>
         </is>
       </c>
-      <c r="E40" s="38" t="inlineStr"/>
+      <c r="E40" s="40" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="37" t="inlineStr">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>M9末</t>
         </is>
       </c>
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t>月次EC売上</t>
         </is>
       </c>
-      <c r="C41" s="37" t="inlineStr">
+      <c r="C41" s="39" t="inlineStr">
         <is>
           <t>&lt; 300万円</t>
         </is>
       </c>
-      <c r="D41" s="37" t="inlineStr">
+      <c r="D41" s="39" t="inlineStr">
         <is>
           <t>→ ★撤退決定</t>
         </is>
       </c>
-      <c r="E41" s="38" t="inlineStr"/>
+      <c r="E41" s="40" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="37" t="inlineStr">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>M9末</t>
         </is>
       </c>
-      <c r="B42" s="37" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>単月営業利益</t>
         </is>
       </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="C42" s="39" t="inlineStr">
         <is>
           <t>&lt; -200万円継続</t>
         </is>
       </c>
-      <c r="D42" s="37" t="inlineStr">
+      <c r="D42" s="39" t="inlineStr">
         <is>
           <t>→ ★撤退決定</t>
         </is>
       </c>
-      <c r="E42" s="38" t="inlineStr"/>
+      <c r="E42" s="40" t="inlineStr"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="39" t="inlineStr">
         <is>
           <t>M10〜</t>
         </is>
       </c>
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B43" s="39" t="inlineStr">
         <is>
           <t>撤退プロセス実行</t>
         </is>
       </c>
-      <c r="C43" s="37" t="inlineStr">
+      <c r="C43" s="39" t="inlineStr">
         <is>
           <t>新規受注停止</t>
         </is>
       </c>
-      <c r="D43" s="37" t="inlineStr">
+      <c r="D43" s="39" t="inlineStr">
         <is>
           <t>既存案件のみクロージング</t>
         </is>
       </c>
-      <c r="E43" s="38" t="inlineStr"/>
+      <c r="E43" s="40" t="inlineStr"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="37" t="inlineStr">
+      <c r="A44" s="39" t="inlineStr">
         <is>
           <t>M12末</t>
         </is>
       </c>
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>事業終了</t>
         </is>
       </c>
-      <c r="C44" s="37" t="inlineStr">
+      <c r="C44" s="39" t="inlineStr">
         <is>
           <t>完全撤退</t>
         </is>
       </c>
-      <c r="D44" s="37" t="inlineStr">
+      <c r="D44" s="39" t="inlineStr">
         <is>
           <t>Year1末で事業停止</t>
         </is>
       </c>
-      <c r="E44" s="38" t="inlineStr"/>
+      <c r="E44" s="40" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1724,7 +1742,7 @@
       <c r="E45" s="2" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="39" t="inlineStr">
+      <c r="A46" s="41" t="inlineStr">
         <is>
           <t>▌ ①大成功パターンに着地するための条件</t>
         </is>
@@ -1735,12 +1753,12 @@
       <c r="E46" s="2" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="40" t="inlineStr">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="B47" s="33" t="inlineStr">
+      <c r="B47" s="35" t="inlineStr">
         <is>
           <t>条件</t>
         </is>
@@ -1750,12 +1768,12 @@
       <c r="E47" s="2" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="41" t="inlineStr">
+      <c r="A48" s="43" t="inlineStr">
         <is>
           <t>M3時点</t>
         </is>
       </c>
-      <c r="B48" s="42" t="inlineStr">
+      <c r="B48" s="44" t="inlineStr">
         <is>
           <t>TKフォロワー 5,000人以上、IGフォロワー 3,000人以上</t>
         </is>
@@ -1765,12 +1783,12 @@
       <c r="E48" s="2" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="43" t="inlineStr">
+      <c r="A49" s="45" t="inlineStr">
         <is>
           <t>M3時点</t>
         </is>
       </c>
-      <c r="B49" s="36" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>タイアップ初回受注（1件以上）を獲得</t>
         </is>
@@ -1780,12 +1798,12 @@
       <c r="E49" s="2" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="41" t="inlineStr">
+      <c r="A50" s="43" t="inlineStr">
         <is>
           <t>M6時点</t>
         </is>
       </c>
-      <c r="B50" s="42" t="inlineStr">
+      <c r="B50" s="44" t="inlineStr">
         <is>
           <t>TKフォロワー 28,000人以上、IGフォロワー 20,000人以上</t>
         </is>
@@ -1795,12 +1813,12 @@
       <c r="E50" s="2" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="43" t="inlineStr">
+      <c r="A51" s="45" t="inlineStr">
         <is>
           <t>M6時点</t>
         </is>
       </c>
-      <c r="B51" s="36" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t>タイアップ月次受注 4件以上（TK+IG合算）</t>
         </is>
@@ -1810,12 +1828,12 @@
       <c r="E51" s="2" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="41" t="inlineStr">
+      <c r="A52" s="43" t="inlineStr">
         <is>
           <t>M6時点</t>
         </is>
       </c>
-      <c r="B52" s="42" t="inlineStr">
+      <c r="B52" s="44" t="inlineStr">
         <is>
           <t>EC月次注文 450件以上・月次売上 290万円以上</t>
         </is>
@@ -1825,12 +1843,12 @@
       <c r="E52" s="2" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="43" t="inlineStr">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>M9時点</t>
         </is>
       </c>
-      <c r="B53" s="36" t="inlineStr">
+      <c r="B53" s="38" t="inlineStr">
         <is>
           <t>タイアップ単価 150万円/社を維持</t>
         </is>
@@ -1840,12 +1858,12 @@
       <c r="E53" s="2" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="41" t="inlineStr">
+      <c r="A54" s="43" t="inlineStr">
         <is>
           <t>M9時点</t>
         </is>
       </c>
-      <c r="B54" s="42" t="inlineStr">
+      <c r="B54" s="44" t="inlineStr">
         <is>
           <t>EC月次売上 975万円以上</t>
         </is>
@@ -1855,12 +1873,12 @@
       <c r="E54" s="2" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="44" t="inlineStr">
+      <c r="A55" s="46" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="B55" s="36" t="inlineStr">
+      <c r="B55" s="38" t="inlineStr">
         <is>
           <t>ENTIALがバズ社内PMとして常駐し、営業・オペをすべて巻き取る</t>
         </is>
@@ -1870,12 +1888,12 @@
       <c r="E55" s="2" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="45" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="B56" s="42" t="inlineStr">
+      <c r="B56" s="44" t="inlineStr">
         <is>
           <t>うさたにパイセン出演コンテンツを安定供給できる</t>
         </is>
@@ -1885,12 +1903,12 @@
       <c r="E56" s="2" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="44" t="inlineStr">
+      <c r="A57" s="46" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="B57" s="36" t="inlineStr">
+      <c r="B57" s="38" t="inlineStr">
         <is>
           <t>WESELL（TikTok Shop）が安定運用できるインフラ整備</t>
         </is>
@@ -1949,86 +1967,86 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>❶ 大成功パターン  ／  Year1 月次事業計画（バズ社PL）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>Year1でバズ売上8,519万・営業利益1,854万・M6損益分岐　単位：万円</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="F3" s="33" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="G3" s="33" t="inlineStr">
+      <c r="G3" s="35" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="H3" s="33" t="inlineStr">
+      <c r="H3" s="35" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="I3" s="33" t="inlineStr">
+      <c r="I3" s="35" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="J3" s="33" t="inlineStr">
+      <c r="J3" s="35" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="K3" s="33" t="inlineStr">
+      <c r="K3" s="35" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="L3" s="33" t="inlineStr">
+      <c r="L3" s="35" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="M3" s="33" t="inlineStr">
+      <c r="M3" s="35" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="N3" s="33" t="inlineStr">
+      <c r="N3" s="35" t="inlineStr">
         <is>
           <t>Year1合計</t>
         </is>
@@ -2055,403 +2073,403 @@
       <c r="N4" s="2" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>TikTokフォロワー数（累計）</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="51" t="n">
         <v>2000</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="51" t="n">
         <v>18000</v>
       </c>
-      <c r="G5" s="49" t="n">
+      <c r="G5" s="51" t="n">
         <v>28000</v>
       </c>
-      <c r="H5" s="49" t="n">
+      <c r="H5" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="I5" s="49" t="n">
+      <c r="I5" s="51" t="n">
         <v>55000</v>
       </c>
-      <c r="J5" s="49" t="n">
+      <c r="J5" s="51" t="n">
         <v>72000</v>
       </c>
-      <c r="K5" s="49" t="n">
+      <c r="K5" s="51" t="n">
         <v>92000</v>
       </c>
-      <c r="L5" s="49" t="n">
+      <c r="L5" s="51" t="n">
         <v>115000</v>
       </c>
-      <c r="M5" s="49" t="n">
+      <c r="M5" s="51" t="n">
         <v>140000</v>
       </c>
-      <c r="N5" s="49" t="n">
+      <c r="N5" s="51" t="n">
         <v>140000</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>IGフォロワー数（累計）</t>
         </is>
       </c>
-      <c r="B6" s="51" t="n">
+      <c r="B6" s="53" t="n">
         <v>300</v>
       </c>
-      <c r="C6" s="51" t="n">
+      <c r="C6" s="53" t="n">
         <v>1200</v>
       </c>
-      <c r="D6" s="51" t="n">
+      <c r="D6" s="53" t="n">
         <v>3000</v>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="53" t="n">
         <v>6000</v>
       </c>
-      <c r="F6" s="51" t="n">
+      <c r="F6" s="53" t="n">
         <v>12000</v>
       </c>
-      <c r="G6" s="51" t="n">
+      <c r="G6" s="53" t="n">
         <v>20000</v>
       </c>
-      <c r="H6" s="51" t="n">
+      <c r="H6" s="53" t="n">
         <v>30000</v>
       </c>
-      <c r="I6" s="51" t="n">
+      <c r="I6" s="53" t="n">
         <v>43000</v>
       </c>
-      <c r="J6" s="51" t="n">
+      <c r="J6" s="53" t="n">
         <v>58000</v>
       </c>
-      <c r="K6" s="51" t="n">
+      <c r="K6" s="53" t="n">
         <v>75000</v>
       </c>
-      <c r="L6" s="51" t="n">
+      <c r="L6" s="53" t="n">
         <v>95000</v>
       </c>
-      <c r="M6" s="51" t="n">
+      <c r="M6" s="53" t="n">
         <v>120000</v>
       </c>
-      <c r="N6" s="51" t="n">
+      <c r="N6" s="53" t="n">
         <v>120000</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>TKタイアップ受注社数（月次）</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="49" t="n">
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="49" t="n">
+      <c r="E7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="49" t="n">
+      <c r="G7" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="49" t="n">
+      <c r="H7" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="49" t="n">
+      <c r="I7" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="49" t="n">
+      <c r="J7" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="49" t="n">
+      <c r="L7" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="M7" s="49" t="n">
+      <c r="M7" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="49" t="n">
+      <c r="N7" s="51" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>TKタイアップ平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="E8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="F8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="G8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="H8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="I8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="J8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="K8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="L8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="M8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="N8" s="55" t="n">
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="F8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="G8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="H8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="I8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="J8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="K8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="L8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="M8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="N8" s="57" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>IGタイアップ受注社数（月次）</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="49" t="n">
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="49" t="n">
+      <c r="G9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="49" t="n">
+      <c r="H9" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="49" t="n">
+      <c r="I9" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="49" t="n">
+      <c r="J9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="49" t="n">
+      <c r="K9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="49" t="n">
+      <c r="L9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="49" t="n">
+      <c r="M9" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="N9" s="49" t="n">
+      <c r="N9" s="51" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>IGタイアップ平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="F10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="G10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="H10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="I10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="J10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="K10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="L10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="M10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="N10" s="55" t="n">
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="F10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="G10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="H10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="I10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="J10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="K10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="L10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="M10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="N10" s="57" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>EC注文件数（TikTok Shop）</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="49" t="n">
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="n">
         <v>50</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="51" t="n">
         <v>120</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="51" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="51" t="n">
         <v>450</v>
       </c>
-      <c r="H11" s="49" t="n">
+      <c r="H11" s="51" t="n">
         <v>700</v>
       </c>
-      <c r="I11" s="49" t="n">
+      <c r="I11" s="51" t="n">
         <v>1000</v>
       </c>
-      <c r="J11" s="49" t="n">
+      <c r="J11" s="51" t="n">
         <v>1300</v>
       </c>
-      <c r="K11" s="49" t="n">
+      <c r="K11" s="51" t="n">
         <v>1700</v>
       </c>
-      <c r="L11" s="49" t="n">
+      <c r="L11" s="51" t="n">
         <v>2200</v>
       </c>
-      <c r="M11" s="49" t="n">
+      <c r="M11" s="51" t="n">
         <v>2800</v>
       </c>
-      <c r="N11" s="49" t="n">
+      <c r="N11" s="51" t="n">
         <v>10570</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>EC平均注文単価（円）</t>
         </is>
       </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="54" t="n">
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="56" t="n">
         <v>5500</v>
       </c>
-      <c r="F12" s="54" t="n">
+      <c r="F12" s="56" t="n">
         <v>6000</v>
       </c>
-      <c r="G12" s="54" t="n">
+      <c r="G12" s="56" t="n">
         <v>6500</v>
       </c>
-      <c r="H12" s="54" t="n">
+      <c r="H12" s="56" t="n">
         <v>7000</v>
       </c>
-      <c r="I12" s="54" t="n">
+      <c r="I12" s="56" t="n">
         <v>7200</v>
       </c>
-      <c r="J12" s="54" t="n">
+      <c r="J12" s="56" t="n">
         <v>7500</v>
       </c>
-      <c r="K12" s="54" t="n">
+      <c r="K12" s="56" t="n">
         <v>7800</v>
       </c>
-      <c r="L12" s="54" t="n">
+      <c r="L12" s="56" t="n">
         <v>8000</v>
       </c>
-      <c r="M12" s="54" t="n">
+      <c r="M12" s="56" t="n">
         <v>8200</v>
       </c>
-      <c r="N12" s="55" t="n">
+      <c r="N12" s="57" t="n">
         <v>6870</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="56" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>▌ 損益計算書（P/L）　単位：万円</t>
         </is>
@@ -2471,560 +2489,560 @@
       <c r="N13" s="2" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>【売上高】</t>
         </is>
       </c>
-      <c r="B14" s="58" t="n"/>
-      <c r="C14" s="58" t="n"/>
-      <c r="D14" s="58" t="n"/>
-      <c r="E14" s="58" t="n"/>
-      <c r="F14" s="58" t="n"/>
-      <c r="G14" s="58" t="n"/>
-      <c r="H14" s="58" t="n"/>
-      <c r="I14" s="58" t="n"/>
-      <c r="J14" s="58" t="n"/>
-      <c r="K14" s="58" t="n"/>
-      <c r="L14" s="58" t="n"/>
-      <c r="M14" s="58" t="n"/>
-      <c r="N14" s="58" t="n"/>
+      <c r="B14" s="60" t="n"/>
+      <c r="C14" s="60" t="n"/>
+      <c r="D14" s="60" t="n"/>
+      <c r="E14" s="60" t="n"/>
+      <c r="F14" s="60" t="n"/>
+      <c r="G14" s="60" t="n"/>
+      <c r="H14" s="60" t="n"/>
+      <c r="I14" s="60" t="n"/>
+      <c r="J14" s="60" t="n"/>
+      <c r="K14" s="60" t="n"/>
+      <c r="L14" s="60" t="n"/>
+      <c r="M14" s="60" t="n"/>
+      <c r="N14" s="60" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ① TikTokメディアタイアップ</t>
         </is>
       </c>
-      <c r="B15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="E15" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="F15" s="59" t="n">
+      <c r="B15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="E15" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="F15" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="G15" s="59" t="n">
+      <c r="G15" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="H15" s="59" t="n">
+      <c r="H15" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="I15" s="59" t="n">
+      <c r="I15" s="61" t="n">
         <v>450</v>
       </c>
-      <c r="J15" s="59" t="n">
+      <c r="J15" s="61" t="n">
         <v>450</v>
       </c>
-      <c r="K15" s="59" t="n">
+      <c r="K15" s="61" t="n">
         <v>450</v>
       </c>
-      <c r="L15" s="59" t="n">
+      <c r="L15" s="61" t="n">
         <v>600</v>
       </c>
-      <c r="M15" s="59" t="n">
+      <c r="M15" s="61" t="n">
         <v>750</v>
       </c>
-      <c r="N15" s="55" t="n">
+      <c r="N15" s="57" t="n">
         <v>3900</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     受注社数（社）</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="62" t="n">
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="62" t="n">
+      <c r="F16" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="62" t="n">
+      <c r="G16" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="62" t="n">
+      <c r="H16" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="62" t="n">
+      <c r="I16" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="62" t="n">
+      <c r="J16" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="K16" s="62" t="n">
+      <c r="K16" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="L16" s="62" t="n">
+      <c r="L16" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="M16" s="62" t="n">
+      <c r="M16" s="64" t="n">
         <v>5</v>
       </c>
-      <c r="N16" s="63" t="n">
+      <c r="N16" s="65" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="E17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="F17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="G17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="H17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="I17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="J17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="K17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="L17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="M17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="N17" s="63" t="n">
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="E17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="F17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="I17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="J17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="K17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="L17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="M17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="N17" s="65" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ② IGメディアタイアップ</t>
         </is>
       </c>
-      <c r="B18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="F18" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="G18" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="H18" s="59" t="n">
+      <c r="B18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="F18" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="G18" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="H18" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="I18" s="59" t="n">
+      <c r="I18" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="J18" s="59" t="n">
+      <c r="J18" s="61" t="n">
         <v>450</v>
       </c>
-      <c r="K18" s="59" t="n">
+      <c r="K18" s="61" t="n">
         <v>450</v>
       </c>
-      <c r="L18" s="59" t="n">
+      <c r="L18" s="61" t="n">
         <v>450</v>
       </c>
-      <c r="M18" s="59" t="n">
+      <c r="M18" s="61" t="n">
         <v>600</v>
       </c>
-      <c r="N18" s="55" t="n">
+      <c r="N18" s="57" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     受注社数（社）</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" s="62" t="n">
+      <c r="B19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="62" t="n">
+      <c r="F19" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="62" t="n">
+      <c r="G19" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="62" t="n">
+      <c r="H19" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="62" t="n">
+      <c r="I19" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="62" t="n">
+      <c r="J19" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="62" t="n">
+      <c r="K19" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="L19" s="62" t="n">
+      <c r="L19" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="M19" s="62" t="n">
+      <c r="M19" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="N19" s="63" t="n">
+      <c r="N19" s="65" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="F20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="G20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="H20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="I20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="J20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="K20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="L20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="M20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="N20" s="63" t="n">
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="F20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="G20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="H20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="I20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="J20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="K20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="L20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="M20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="N20" s="65" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="64" t="inlineStr">
+      <c r="A21" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">  タイアップ売上合計</t>
         </is>
       </c>
-      <c r="B21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="65" t="n">
-        <v>150</v>
-      </c>
-      <c r="E21" s="65" t="n">
+      <c r="B21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="67" t="n">
+        <v>150</v>
+      </c>
+      <c r="E21" s="67" t="n">
         <v>300</v>
       </c>
-      <c r="F21" s="65" t="n">
+      <c r="F21" s="67" t="n">
         <v>450</v>
       </c>
-      <c r="G21" s="65" t="n">
+      <c r="G21" s="67" t="n">
         <v>450</v>
       </c>
-      <c r="H21" s="65" t="n">
+      <c r="H21" s="67" t="n">
         <v>600</v>
       </c>
-      <c r="I21" s="65" t="n">
+      <c r="I21" s="67" t="n">
         <v>750</v>
       </c>
-      <c r="J21" s="65" t="n">
+      <c r="J21" s="67" t="n">
         <v>900</v>
       </c>
-      <c r="K21" s="65" t="n">
+      <c r="K21" s="67" t="n">
         <v>900</v>
       </c>
-      <c r="L21" s="65" t="n">
+      <c r="L21" s="67" t="n">
         <v>1050</v>
       </c>
-      <c r="M21" s="65" t="n">
+      <c r="M21" s="67" t="n">
         <v>1350</v>
       </c>
-      <c r="N21" s="65" t="n">
+      <c r="N21" s="67" t="n">
         <v>6900</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ③ ECアフィリエイトコミッション（×20%）</t>
         </is>
       </c>
-      <c r="B22" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="59" t="n">
+      <c r="B22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="E22" s="59" t="n">
+      <c r="E22" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="F22" s="59" t="n">
+      <c r="F22" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="G22" s="59" t="n">
+      <c r="G22" s="61" t="n">
         <v>58</v>
       </c>
-      <c r="H22" s="59" t="n">
+      <c r="H22" s="61" t="n">
         <v>98</v>
       </c>
-      <c r="I22" s="59" t="n">
+      <c r="I22" s="61" t="n">
         <v>144</v>
       </c>
-      <c r="J22" s="59" t="n">
+      <c r="J22" s="61" t="n">
         <v>195</v>
       </c>
-      <c r="K22" s="59" t="n">
+      <c r="K22" s="61" t="n">
         <v>265</v>
       </c>
-      <c r="L22" s="59" t="n">
+      <c r="L22" s="61" t="n">
         <v>352</v>
       </c>
-      <c r="M22" s="59" t="n">
+      <c r="M22" s="61" t="n">
         <v>459</v>
       </c>
-      <c r="N22" s="55" t="n">
+      <c r="N22" s="57" t="n">
         <v>1619</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     EC実売上（ギャル協会側・参考値）</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="62" t="n">
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="64" t="n">
         <v>25</v>
       </c>
-      <c r="E23" s="62" t="n">
+      <c r="E23" s="64" t="n">
         <v>66</v>
       </c>
-      <c r="F23" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="G23" s="62" t="n">
+      <c r="F23" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="G23" s="64" t="n">
         <v>292</v>
       </c>
-      <c r="H23" s="62" t="n">
+      <c r="H23" s="64" t="n">
         <v>490</v>
       </c>
-      <c r="I23" s="62" t="n">
+      <c r="I23" s="64" t="n">
         <v>720</v>
       </c>
-      <c r="J23" s="62" t="n">
+      <c r="J23" s="64" t="n">
         <v>975</v>
       </c>
-      <c r="K23" s="62" t="n">
+      <c r="K23" s="64" t="n">
         <v>1326</v>
       </c>
-      <c r="L23" s="62" t="n">
+      <c r="L23" s="64" t="n">
         <v>1760</v>
       </c>
-      <c r="M23" s="62" t="n">
+      <c r="M23" s="64" t="n">
         <v>2296</v>
       </c>
-      <c r="N23" s="63" t="n">
+      <c r="N23" s="65" t="n">
         <v>8100</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     注文件数（件）</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="62" t="n">
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="64" t="n">
         <v>50</v>
       </c>
-      <c r="E24" s="62" t="n">
+      <c r="E24" s="64" t="n">
         <v>120</v>
       </c>
-      <c r="F24" s="62" t="n">
+      <c r="F24" s="64" t="n">
         <v>250</v>
       </c>
-      <c r="G24" s="62" t="n">
+      <c r="G24" s="64" t="n">
         <v>450</v>
       </c>
-      <c r="H24" s="62" t="n">
+      <c r="H24" s="64" t="n">
         <v>700</v>
       </c>
-      <c r="I24" s="62" t="n">
+      <c r="I24" s="64" t="n">
         <v>1000</v>
       </c>
-      <c r="J24" s="62" t="n">
+      <c r="J24" s="64" t="n">
         <v>1300</v>
       </c>
-      <c r="K24" s="62" t="n">
+      <c r="K24" s="64" t="n">
         <v>1700</v>
       </c>
-      <c r="L24" s="62" t="n">
+      <c r="L24" s="64" t="n">
         <v>2200</v>
       </c>
-      <c r="M24" s="62" t="n">
+      <c r="M24" s="64" t="n">
         <v>2800</v>
       </c>
-      <c r="N24" s="63" t="n">
+      <c r="N24" s="65" t="n">
         <v>10570</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="60" t="inlineStr">
+      <c r="A25" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     平均注文単価（円）</t>
         </is>
       </c>
-      <c r="B25" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="62" t="n">
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="E25" s="62" t="n">
+      <c r="E25" s="64" t="n">
         <v>5500</v>
       </c>
-      <c r="F25" s="62" t="n">
+      <c r="F25" s="64" t="n">
         <v>6000</v>
       </c>
-      <c r="G25" s="62" t="n">
+      <c r="G25" s="64" t="n">
         <v>6500</v>
       </c>
-      <c r="H25" s="62" t="n">
+      <c r="H25" s="64" t="n">
         <v>7000</v>
       </c>
-      <c r="I25" s="62" t="n">
+      <c r="I25" s="64" t="n">
         <v>7200</v>
       </c>
-      <c r="J25" s="62" t="n">
+      <c r="J25" s="64" t="n">
         <v>7500</v>
       </c>
-      <c r="K25" s="62" t="n">
+      <c r="K25" s="64" t="n">
         <v>7800</v>
       </c>
-      <c r="L25" s="62" t="n">
+      <c r="L25" s="64" t="n">
         <v>8000</v>
       </c>
-      <c r="M25" s="62" t="n">
+      <c r="M25" s="64" t="n">
         <v>8200</v>
       </c>
-      <c r="N25" s="63" t="n">
+      <c r="N25" s="65" t="n">
         <v>6870</v>
       </c>
     </row>
@@ -3034,267 +3052,267 @@
           <t>売上合計</t>
         </is>
       </c>
-      <c r="B26" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="66" t="n">
+      <c r="B26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="68" t="n">
         <v>155</v>
       </c>
-      <c r="E26" s="66" t="n">
+      <c r="E26" s="68" t="n">
         <v>313</v>
       </c>
-      <c r="F26" s="66" t="n">
+      <c r="F26" s="68" t="n">
         <v>480</v>
       </c>
-      <c r="G26" s="66" t="n">
+      <c r="G26" s="68" t="n">
         <v>508</v>
       </c>
-      <c r="H26" s="66" t="n">
+      <c r="H26" s="68" t="n">
         <v>698</v>
       </c>
-      <c r="I26" s="66" t="n">
+      <c r="I26" s="68" t="n">
         <v>894</v>
       </c>
-      <c r="J26" s="66" t="n">
+      <c r="J26" s="68" t="n">
         <v>1095</v>
       </c>
-      <c r="K26" s="66" t="n">
+      <c r="K26" s="68" t="n">
         <v>1165</v>
       </c>
-      <c r="L26" s="66" t="n">
+      <c r="L26" s="68" t="n">
         <v>1402</v>
       </c>
-      <c r="M26" s="66" t="n">
+      <c r="M26" s="68" t="n">
         <v>1809</v>
       </c>
-      <c r="N26" s="66" t="n">
+      <c r="N26" s="68" t="n">
         <v>8519</v>
       </c>
     </row>
     <row r="27" ht="6" customHeight="1">
-      <c r="A27" s="67" t="inlineStr"/>
-      <c r="B27" s="68" t="n"/>
-      <c r="C27" s="68" t="n"/>
-      <c r="D27" s="68" t="n"/>
-      <c r="E27" s="68" t="n"/>
-      <c r="F27" s="68" t="n"/>
-      <c r="G27" s="68" t="n"/>
-      <c r="H27" s="68" t="n"/>
-      <c r="I27" s="68" t="n"/>
-      <c r="J27" s="68" t="n"/>
-      <c r="K27" s="68" t="n"/>
-      <c r="L27" s="68" t="n"/>
-      <c r="M27" s="68" t="n"/>
-      <c r="N27" s="68" t="n"/>
+      <c r="A27" s="69" t="inlineStr"/>
+      <c r="B27" s="70" t="n"/>
+      <c r="C27" s="70" t="n"/>
+      <c r="D27" s="70" t="n"/>
+      <c r="E27" s="70" t="n"/>
+      <c r="F27" s="70" t="n"/>
+      <c r="G27" s="70" t="n"/>
+      <c r="H27" s="70" t="n"/>
+      <c r="I27" s="70" t="n"/>
+      <c r="J27" s="70" t="n"/>
+      <c r="K27" s="70" t="n"/>
+      <c r="L27" s="70" t="n"/>
+      <c r="M27" s="70" t="n"/>
+      <c r="N27" s="70" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="57" t="inlineStr">
+      <c r="A28" s="59" t="inlineStr">
         <is>
           <t>【タイアップ原価】</t>
         </is>
       </c>
-      <c r="B28" s="58" t="n"/>
-      <c r="C28" s="58" t="n"/>
-      <c r="D28" s="58" t="n"/>
-      <c r="E28" s="58" t="n"/>
-      <c r="F28" s="58" t="n"/>
-      <c r="G28" s="58" t="n"/>
-      <c r="H28" s="58" t="n"/>
-      <c r="I28" s="58" t="n"/>
-      <c r="J28" s="58" t="n"/>
-      <c r="K28" s="58" t="n"/>
-      <c r="L28" s="58" t="n"/>
-      <c r="M28" s="58" t="n"/>
-      <c r="N28" s="58" t="n"/>
+      <c r="B28" s="60" t="n"/>
+      <c r="C28" s="60" t="n"/>
+      <c r="D28" s="60" t="n"/>
+      <c r="E28" s="60" t="n"/>
+      <c r="F28" s="60" t="n"/>
+      <c r="G28" s="60" t="n"/>
+      <c r="H28" s="60" t="n"/>
+      <c r="I28" s="60" t="n"/>
+      <c r="J28" s="60" t="n"/>
+      <c r="K28" s="60" t="n"/>
+      <c r="L28" s="60" t="n"/>
+      <c r="M28" s="60" t="n"/>
+      <c r="N28" s="60" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ギャル協会出演・監修料（件数×25万・最低保証10万）</t>
         </is>
       </c>
-      <c r="B29" s="59" t="n">
+      <c r="B29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="C29" s="59" t="n">
+      <c r="C29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="59" t="n">
+      <c r="D29" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="E29" s="59" t="n">
+      <c r="E29" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="F29" s="59" t="n">
+      <c r="F29" s="61" t="n">
         <v>75</v>
       </c>
-      <c r="G29" s="59" t="n">
+      <c r="G29" s="61" t="n">
         <v>75</v>
       </c>
-      <c r="H29" s="59" t="n">
+      <c r="H29" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="I29" s="59" t="n">
+      <c r="I29" s="61" t="n">
         <v>125</v>
       </c>
-      <c r="J29" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="K29" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="L29" s="59" t="n">
+      <c r="J29" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="K29" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="L29" s="61" t="n">
         <v>175</v>
       </c>
-      <c r="M29" s="59" t="n">
+      <c r="M29" s="61" t="n">
         <v>225</v>
       </c>
-      <c r="N29" s="55" t="n">
+      <c r="N29" s="57" t="n">
         <v>1170</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     タイアップ件数（社）</t>
         </is>
       </c>
-      <c r="B30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="62" t="n">
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="62" t="n">
+      <c r="E30" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="62" t="n">
+      <c r="F30" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="62" t="n">
+      <c r="G30" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="62" t="n">
+      <c r="H30" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="I30" s="62" t="n">
+      <c r="I30" s="64" t="n">
         <v>5</v>
       </c>
-      <c r="J30" s="62" t="n">
+      <c r="J30" s="64" t="n">
         <v>6</v>
       </c>
-      <c r="K30" s="62" t="n">
+      <c r="K30" s="64" t="n">
         <v>6</v>
       </c>
-      <c r="L30" s="62" t="n">
+      <c r="L30" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="M30" s="62" t="n">
+      <c r="M30" s="64" t="n">
         <v>9</v>
       </c>
-      <c r="N30" s="63" t="n">
+      <c r="N30" s="65" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  コンテンツ制作費（×10%）</t>
         </is>
       </c>
-      <c r="B31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="59" t="n">
+      <c r="B31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="E31" s="59" t="n">
+      <c r="E31" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="F31" s="59" t="n">
+      <c r="F31" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="G31" s="59" t="n">
+      <c r="G31" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="H31" s="59" t="n">
+      <c r="H31" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="I31" s="59" t="n">
+      <c r="I31" s="61" t="n">
         <v>75</v>
       </c>
-      <c r="J31" s="59" t="n">
+      <c r="J31" s="61" t="n">
         <v>90</v>
       </c>
-      <c r="K31" s="59" t="n">
+      <c r="K31" s="61" t="n">
         <v>90</v>
       </c>
-      <c r="L31" s="59" t="n">
+      <c r="L31" s="61" t="n">
         <v>105</v>
       </c>
-      <c r="M31" s="59" t="n">
+      <c r="M31" s="61" t="n">
         <v>135</v>
       </c>
-      <c r="N31" s="55" t="n">
+      <c r="N31" s="57" t="n">
         <v>690</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="64" t="inlineStr">
+      <c r="A32" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">  タイアップ原価合計</t>
         </is>
       </c>
-      <c r="B32" s="65" t="n">
+      <c r="B32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="C32" s="65" t="n">
+      <c r="C32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="65" t="n">
+      <c r="D32" s="67" t="n">
         <v>40</v>
       </c>
-      <c r="E32" s="65" t="n">
+      <c r="E32" s="67" t="n">
         <v>80</v>
       </c>
-      <c r="F32" s="65" t="n">
+      <c r="F32" s="67" t="n">
         <v>120</v>
       </c>
-      <c r="G32" s="65" t="n">
+      <c r="G32" s="67" t="n">
         <v>120</v>
       </c>
-      <c r="H32" s="65" t="n">
+      <c r="H32" s="67" t="n">
         <v>160</v>
       </c>
-      <c r="I32" s="65" t="n">
+      <c r="I32" s="67" t="n">
         <v>200</v>
       </c>
-      <c r="J32" s="65" t="n">
+      <c r="J32" s="67" t="n">
         <v>240</v>
       </c>
-      <c r="K32" s="65" t="n">
+      <c r="K32" s="67" t="n">
         <v>240</v>
       </c>
-      <c r="L32" s="65" t="n">
+      <c r="L32" s="67" t="n">
         <v>280</v>
       </c>
-      <c r="M32" s="65" t="n">
+      <c r="M32" s="67" t="n">
         <v>360</v>
       </c>
-      <c r="N32" s="65" t="n">
+      <c r="N32" s="67" t="n">
         <v>1860</v>
       </c>
     </row>
@@ -3304,658 +3322,658 @@
           <t xml:space="preserve">  タイアップ粗利</t>
         </is>
       </c>
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="C33" s="31" t="n">
+      <c r="C33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="D33" s="69" t="n">
+      <c r="D33" s="71" t="n">
         <v>110</v>
       </c>
-      <c r="E33" s="69" t="n">
+      <c r="E33" s="71" t="n">
         <v>220</v>
       </c>
-      <c r="F33" s="69" t="n">
+      <c r="F33" s="71" t="n">
         <v>330</v>
       </c>
-      <c r="G33" s="69" t="n">
+      <c r="G33" s="71" t="n">
         <v>330</v>
       </c>
-      <c r="H33" s="69" t="n">
+      <c r="H33" s="71" t="n">
         <v>440</v>
       </c>
-      <c r="I33" s="69" t="n">
+      <c r="I33" s="71" t="n">
         <v>550</v>
       </c>
-      <c r="J33" s="69" t="n">
+      <c r="J33" s="71" t="n">
         <v>660</v>
       </c>
-      <c r="K33" s="69" t="n">
+      <c r="K33" s="71" t="n">
         <v>660</v>
       </c>
-      <c r="L33" s="69" t="n">
+      <c r="L33" s="71" t="n">
         <v>770</v>
       </c>
-      <c r="M33" s="69" t="n">
+      <c r="M33" s="71" t="n">
         <v>990</v>
       </c>
-      <c r="N33" s="69" t="n">
+      <c r="N33" s="71" t="n">
         <v>5040</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="70" t="inlineStr">
+      <c r="A34" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">  タイアップ粗利率</t>
         </is>
       </c>
-      <c r="B34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="71" t="n">
+      <c r="B34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="E34" s="71" t="n">
+      <c r="E34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="F34" s="71" t="n">
+      <c r="F34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="G34" s="71" t="n">
+      <c r="G34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="H34" s="71" t="n">
+      <c r="H34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="I34" s="71" t="n">
+      <c r="I34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="J34" s="71" t="n">
+      <c r="J34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="K34" s="71" t="n">
+      <c r="K34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="L34" s="71" t="n">
+      <c r="L34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="M34" s="71" t="n">
+      <c r="M34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="N34" s="72" t="n">
+      <c r="N34" s="74" t="n">
         <v>73.3</v>
       </c>
     </row>
     <row r="35" ht="6" customHeight="1">
-      <c r="A35" s="67" t="inlineStr"/>
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="68" t="n"/>
-      <c r="D35" s="68" t="n"/>
-      <c r="E35" s="68" t="n"/>
-      <c r="F35" s="68" t="n"/>
-      <c r="G35" s="68" t="n"/>
-      <c r="H35" s="68" t="n"/>
-      <c r="I35" s="68" t="n"/>
-      <c r="J35" s="68" t="n"/>
-      <c r="K35" s="68" t="n"/>
-      <c r="L35" s="68" t="n"/>
-      <c r="M35" s="68" t="n"/>
-      <c r="N35" s="68" t="n"/>
+      <c r="A35" s="69" t="inlineStr"/>
+      <c r="B35" s="70" t="n"/>
+      <c r="C35" s="70" t="n"/>
+      <c r="D35" s="70" t="n"/>
+      <c r="E35" s="70" t="n"/>
+      <c r="F35" s="70" t="n"/>
+      <c r="G35" s="70" t="n"/>
+      <c r="H35" s="70" t="n"/>
+      <c r="I35" s="70" t="n"/>
+      <c r="J35" s="70" t="n"/>
+      <c r="K35" s="70" t="n"/>
+      <c r="L35" s="70" t="n"/>
+      <c r="M35" s="70" t="n"/>
+      <c r="N35" s="70" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  ※ECコミッション（原価ゼロ）→ ギャル協会がショップオーナー</t>
         </is>
       </c>
-      <c r="B36" s="73" t="n"/>
-      <c r="C36" s="73" t="n"/>
-      <c r="D36" s="73" t="n"/>
-      <c r="E36" s="73" t="n"/>
-      <c r="F36" s="73" t="n"/>
-      <c r="G36" s="73" t="n"/>
-      <c r="H36" s="73" t="n"/>
-      <c r="I36" s="73" t="n"/>
-      <c r="J36" s="73" t="n"/>
-      <c r="K36" s="73" t="n"/>
-      <c r="L36" s="73" t="n"/>
-      <c r="M36" s="73" t="n"/>
-      <c r="N36" s="73" t="n"/>
+      <c r="B36" s="75" t="n"/>
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="75" t="n"/>
+      <c r="E36" s="75" t="n"/>
+      <c r="F36" s="75" t="n"/>
+      <c r="G36" s="75" t="n"/>
+      <c r="H36" s="75" t="n"/>
+      <c r="I36" s="75" t="n"/>
+      <c r="J36" s="75" t="n"/>
+      <c r="K36" s="75" t="n"/>
+      <c r="L36" s="75" t="n"/>
+      <c r="M36" s="75" t="n"/>
+      <c r="N36" s="75" t="n"/>
     </row>
     <row r="37" ht="6" customHeight="1">
-      <c r="A37" s="67" t="inlineStr"/>
-      <c r="B37" s="68" t="n"/>
-      <c r="C37" s="68" t="n"/>
-      <c r="D37" s="68" t="n"/>
-      <c r="E37" s="68" t="n"/>
-      <c r="F37" s="68" t="n"/>
-      <c r="G37" s="68" t="n"/>
-      <c r="H37" s="68" t="n"/>
-      <c r="I37" s="68" t="n"/>
-      <c r="J37" s="68" t="n"/>
-      <c r="K37" s="68" t="n"/>
-      <c r="L37" s="68" t="n"/>
-      <c r="M37" s="68" t="n"/>
-      <c r="N37" s="68" t="n"/>
+      <c r="A37" s="69" t="inlineStr"/>
+      <c r="B37" s="70" t="n"/>
+      <c r="C37" s="70" t="n"/>
+      <c r="D37" s="70" t="n"/>
+      <c r="E37" s="70" t="n"/>
+      <c r="F37" s="70" t="n"/>
+      <c r="G37" s="70" t="n"/>
+      <c r="H37" s="70" t="n"/>
+      <c r="I37" s="70" t="n"/>
+      <c r="J37" s="70" t="n"/>
+      <c r="K37" s="70" t="n"/>
+      <c r="L37" s="70" t="n"/>
+      <c r="M37" s="70" t="n"/>
+      <c r="N37" s="70" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="74" t="inlineStr">
+      <c r="A38" s="76" t="inlineStr">
         <is>
           <t>売上原価合計</t>
         </is>
       </c>
-      <c r="B38" s="75" t="n">
+      <c r="B38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="C38" s="75" t="n">
+      <c r="C38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="75" t="n">
+      <c r="D38" s="77" t="n">
         <v>40</v>
       </c>
-      <c r="E38" s="75" t="n">
+      <c r="E38" s="77" t="n">
         <v>80</v>
       </c>
-      <c r="F38" s="75" t="n">
+      <c r="F38" s="77" t="n">
         <v>120</v>
       </c>
-      <c r="G38" s="75" t="n">
+      <c r="G38" s="77" t="n">
         <v>120</v>
       </c>
-      <c r="H38" s="75" t="n">
+      <c r="H38" s="77" t="n">
         <v>160</v>
       </c>
-      <c r="I38" s="75" t="n">
+      <c r="I38" s="77" t="n">
         <v>200</v>
       </c>
-      <c r="J38" s="75" t="n">
+      <c r="J38" s="77" t="n">
         <v>240</v>
       </c>
-      <c r="K38" s="75" t="n">
+      <c r="K38" s="77" t="n">
         <v>240</v>
       </c>
-      <c r="L38" s="75" t="n">
+      <c r="L38" s="77" t="n">
         <v>280</v>
       </c>
-      <c r="M38" s="75" t="n">
+      <c r="M38" s="77" t="n">
         <v>360</v>
       </c>
-      <c r="N38" s="75" t="n">
+      <c r="N38" s="77" t="n">
         <v>1860</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="76" t="inlineStr">
+      <c r="A39" s="78" t="inlineStr">
         <is>
           <t>粗利益合計</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n">
+      <c r="B39" s="79" t="n">
         <v>-10</v>
       </c>
-      <c r="C39" s="77" t="n">
+      <c r="C39" s="79" t="n">
         <v>-10</v>
       </c>
-      <c r="D39" s="78" t="n">
+      <c r="D39" s="80" t="n">
         <v>115</v>
       </c>
-      <c r="E39" s="78" t="n">
+      <c r="E39" s="80" t="n">
         <v>233</v>
       </c>
-      <c r="F39" s="78" t="n">
+      <c r="F39" s="80" t="n">
         <v>360</v>
       </c>
-      <c r="G39" s="78" t="n">
+      <c r="G39" s="80" t="n">
         <v>388</v>
       </c>
-      <c r="H39" s="78" t="n">
+      <c r="H39" s="80" t="n">
         <v>538</v>
       </c>
-      <c r="I39" s="78" t="n">
+      <c r="I39" s="80" t="n">
         <v>694</v>
       </c>
-      <c r="J39" s="78" t="n">
+      <c r="J39" s="80" t="n">
         <v>855</v>
       </c>
-      <c r="K39" s="78" t="n">
+      <c r="K39" s="80" t="n">
         <v>925</v>
       </c>
-      <c r="L39" s="78" t="n">
+      <c r="L39" s="80" t="n">
         <v>1122</v>
       </c>
-      <c r="M39" s="78" t="n">
+      <c r="M39" s="80" t="n">
         <v>1449</v>
       </c>
-      <c r="N39" s="78" t="n">
+      <c r="N39" s="80" t="n">
         <v>6659</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="70" t="inlineStr">
+      <c r="A40" s="72" t="inlineStr">
         <is>
           <t>粗利率（合計）</t>
         </is>
       </c>
-      <c r="B40" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="71" t="n">
+      <c r="B40" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="73" t="n">
         <v>74.2</v>
       </c>
-      <c r="E40" s="71" t="n">
+      <c r="E40" s="73" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="F40" s="71" t="n">
+      <c r="F40" s="73" t="n">
         <v>75</v>
       </c>
-      <c r="G40" s="71" t="n">
+      <c r="G40" s="73" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="H40" s="71" t="n">
+      <c r="H40" s="73" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="I40" s="71" t="n">
+      <c r="I40" s="73" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="J40" s="71" t="n">
+      <c r="J40" s="73" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="K40" s="71" t="n">
+      <c r="K40" s="73" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="L40" s="71" t="n">
+      <c r="L40" s="73" t="n">
         <v>80</v>
       </c>
-      <c r="M40" s="71" t="n">
+      <c r="M40" s="73" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="N40" s="72" t="n">
+      <c r="N40" s="74" t="n">
         <v>77.2</v>
       </c>
     </row>
     <row r="41" ht="6" customHeight="1">
-      <c r="A41" s="67" t="inlineStr"/>
-      <c r="B41" s="68" t="n"/>
-      <c r="C41" s="68" t="n"/>
-      <c r="D41" s="68" t="n"/>
-      <c r="E41" s="68" t="n"/>
-      <c r="F41" s="68" t="n"/>
-      <c r="G41" s="68" t="n"/>
-      <c r="H41" s="68" t="n"/>
-      <c r="I41" s="68" t="n"/>
-      <c r="J41" s="68" t="n"/>
-      <c r="K41" s="68" t="n"/>
-      <c r="L41" s="68" t="n"/>
-      <c r="M41" s="68" t="n"/>
-      <c r="N41" s="68" t="n"/>
+      <c r="A41" s="69" t="inlineStr"/>
+      <c r="B41" s="70" t="n"/>
+      <c r="C41" s="70" t="n"/>
+      <c r="D41" s="70" t="n"/>
+      <c r="E41" s="70" t="n"/>
+      <c r="F41" s="70" t="n"/>
+      <c r="G41" s="70" t="n"/>
+      <c r="H41" s="70" t="n"/>
+      <c r="I41" s="70" t="n"/>
+      <c r="J41" s="70" t="n"/>
+      <c r="K41" s="70" t="n"/>
+      <c r="L41" s="70" t="n"/>
+      <c r="M41" s="70" t="n"/>
+      <c r="N41" s="70" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="57" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>【販売管理費】</t>
         </is>
       </c>
-      <c r="B42" s="58" t="n"/>
-      <c r="C42" s="58" t="n"/>
-      <c r="D42" s="58" t="n"/>
-      <c r="E42" s="58" t="n"/>
-      <c r="F42" s="58" t="n"/>
-      <c r="G42" s="58" t="n"/>
-      <c r="H42" s="58" t="n"/>
-      <c r="I42" s="58" t="n"/>
-      <c r="J42" s="58" t="n"/>
-      <c r="K42" s="58" t="n"/>
-      <c r="L42" s="58" t="n"/>
-      <c r="M42" s="58" t="n"/>
-      <c r="N42" s="58" t="n"/>
+      <c r="B42" s="60" t="n"/>
+      <c r="C42" s="60" t="n"/>
+      <c r="D42" s="60" t="n"/>
+      <c r="E42" s="60" t="n"/>
+      <c r="F42" s="60" t="n"/>
+      <c r="G42" s="60" t="n"/>
+      <c r="H42" s="60" t="n"/>
+      <c r="I42" s="60" t="n"/>
+      <c r="J42" s="60" t="n"/>
+      <c r="K42" s="60" t="n"/>
+      <c r="L42" s="60" t="n"/>
+      <c r="M42" s="60" t="n"/>
+      <c r="N42" s="60" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
         </is>
       </c>
-      <c r="B43" s="59" t="n">
+      <c r="B43" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="C43" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="D43" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="E43" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="F43" s="59" t="n">
+      <c r="C43" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="D43" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="E43" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="F43" s="61" t="n">
         <v>200</v>
       </c>
-      <c r="G43" s="59" t="n">
+      <c r="G43" s="61" t="n">
         <v>200</v>
       </c>
-      <c r="H43" s="59" t="n">
+      <c r="H43" s="61" t="n">
         <v>250</v>
       </c>
-      <c r="I43" s="59" t="n">
+      <c r="I43" s="61" t="n">
         <v>250</v>
       </c>
-      <c r="J43" s="59" t="n">
+      <c r="J43" s="61" t="n">
         <v>250</v>
       </c>
-      <c r="K43" s="59" t="n">
+      <c r="K43" s="61" t="n">
         <v>250</v>
       </c>
-      <c r="L43" s="59" t="n">
+      <c r="L43" s="61" t="n">
         <v>250</v>
       </c>
-      <c r="M43" s="59" t="n">
+      <c r="M43" s="61" t="n">
         <v>250</v>
       </c>
-      <c r="N43" s="55" t="n">
+      <c r="N43" s="57" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  人件費（バズ社員）</t>
         </is>
       </c>
-      <c r="B44" s="59" t="n">
+      <c r="B44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="C44" s="59" t="n">
+      <c r="C44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="D44" s="59" t="n">
+      <c r="D44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="E44" s="59" t="n">
+      <c r="E44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="F44" s="59" t="n">
+      <c r="F44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="G44" s="59" t="n">
+      <c r="G44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="H44" s="59" t="n">
+      <c r="H44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="I44" s="59" t="n">
+      <c r="I44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="59" t="n">
+      <c r="J44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="K44" s="59" t="n">
+      <c r="K44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="L44" s="59" t="n">
+      <c r="L44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="M44" s="59" t="n">
+      <c r="M44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="N44" s="55" t="n">
+      <c r="N44" s="57" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  その他販管費</t>
         </is>
       </c>
-      <c r="B45" s="59" t="n">
+      <c r="B45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="C45" s="59" t="n">
+      <c r="C45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="D45" s="59" t="n">
+      <c r="D45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="E45" s="59" t="n">
+      <c r="E45" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="F45" s="59" t="n">
+      <c r="F45" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="G45" s="59" t="n">
+      <c r="G45" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="H45" s="59" t="n">
+      <c r="H45" s="61" t="n">
         <v>70</v>
       </c>
-      <c r="I45" s="59" t="n">
+      <c r="I45" s="61" t="n">
         <v>70</v>
       </c>
-      <c r="J45" s="59" t="n">
+      <c r="J45" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="K45" s="59" t="n">
+      <c r="K45" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="L45" s="59" t="n">
+      <c r="L45" s="61" t="n">
         <v>90</v>
       </c>
-      <c r="M45" s="59" t="n">
+      <c r="M45" s="61" t="n">
         <v>90</v>
       </c>
-      <c r="N45" s="55" t="n">
+      <c r="N45" s="57" t="n">
         <v>810</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ENTIAL業務委託費（TIE×5%）</t>
         </is>
       </c>
-      <c r="B46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="59" t="n">
+      <c r="B46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="E46" s="59" t="n">
+      <c r="E46" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="F46" s="59" t="n">
+      <c r="F46" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="G46" s="59" t="n">
+      <c r="G46" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="H46" s="59" t="n">
+      <c r="H46" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="I46" s="59" t="n">
+      <c r="I46" s="61" t="n">
         <v>38</v>
       </c>
-      <c r="J46" s="59" t="n">
+      <c r="J46" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="K46" s="59" t="n">
+      <c r="K46" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="L46" s="59" t="n">
+      <c r="L46" s="61" t="n">
         <v>52</v>
       </c>
-      <c r="M46" s="59" t="n">
+      <c r="M46" s="61" t="n">
         <v>68</v>
       </c>
-      <c r="N46" s="55" t="n">
+      <c r="N46" s="57" t="n">
         <v>345</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="74" t="inlineStr">
+      <c r="A47" s="76" t="inlineStr">
         <is>
           <t>販売管理費合計</t>
         </is>
       </c>
-      <c r="B47" s="75" t="n">
+      <c r="B47" s="77" t="n">
         <v>250</v>
       </c>
-      <c r="C47" s="75" t="n">
+      <c r="C47" s="77" t="n">
         <v>300</v>
       </c>
-      <c r="D47" s="75" t="n">
+      <c r="D47" s="77" t="n">
         <v>308</v>
       </c>
-      <c r="E47" s="75" t="n">
+      <c r="E47" s="77" t="n">
         <v>325</v>
       </c>
-      <c r="F47" s="75" t="n">
+      <c r="F47" s="77" t="n">
         <v>382</v>
       </c>
-      <c r="G47" s="75" t="n">
+      <c r="G47" s="77" t="n">
         <v>382</v>
       </c>
-      <c r="H47" s="75" t="n">
+      <c r="H47" s="77" t="n">
         <v>450</v>
       </c>
-      <c r="I47" s="75" t="n">
+      <c r="I47" s="77" t="n">
         <v>458</v>
       </c>
-      <c r="J47" s="75" t="n">
+      <c r="J47" s="77" t="n">
         <v>475</v>
       </c>
-      <c r="K47" s="75" t="n">
+      <c r="K47" s="77" t="n">
         <v>475</v>
       </c>
-      <c r="L47" s="75" t="n">
+      <c r="L47" s="77" t="n">
         <v>492</v>
       </c>
-      <c r="M47" s="75" t="n">
+      <c r="M47" s="77" t="n">
         <v>508</v>
       </c>
-      <c r="N47" s="75" t="n">
+      <c r="N47" s="77" t="n">
         <v>4805</v>
       </c>
     </row>
     <row r="48" ht="6" customHeight="1">
-      <c r="A48" s="67" t="inlineStr"/>
-      <c r="B48" s="68" t="n"/>
-      <c r="C48" s="68" t="n"/>
-      <c r="D48" s="68" t="n"/>
-      <c r="E48" s="68" t="n"/>
-      <c r="F48" s="68" t="n"/>
-      <c r="G48" s="68" t="n"/>
-      <c r="H48" s="68" t="n"/>
-      <c r="I48" s="68" t="n"/>
-      <c r="J48" s="68" t="n"/>
-      <c r="K48" s="68" t="n"/>
-      <c r="L48" s="68" t="n"/>
-      <c r="M48" s="68" t="n"/>
-      <c r="N48" s="68" t="n"/>
+      <c r="A48" s="69" t="inlineStr"/>
+      <c r="B48" s="70" t="n"/>
+      <c r="C48" s="70" t="n"/>
+      <c r="D48" s="70" t="n"/>
+      <c r="E48" s="70" t="n"/>
+      <c r="F48" s="70" t="n"/>
+      <c r="G48" s="70" t="n"/>
+      <c r="H48" s="70" t="n"/>
+      <c r="I48" s="70" t="n"/>
+      <c r="J48" s="70" t="n"/>
+      <c r="K48" s="70" t="n"/>
+      <c r="L48" s="70" t="n"/>
+      <c r="M48" s="70" t="n"/>
+      <c r="N48" s="70" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="56" t="inlineStr">
+      <c r="A49" s="58" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="B49" s="79" t="n">
+      <c r="B49" s="81" t="n">
         <v>-260</v>
       </c>
-      <c r="C49" s="79" t="n">
+      <c r="C49" s="81" t="n">
         <v>-310</v>
       </c>
-      <c r="D49" s="79" t="n">
+      <c r="D49" s="81" t="n">
         <v>-193</v>
       </c>
-      <c r="E49" s="79" t="n">
+      <c r="E49" s="81" t="n">
         <v>-92</v>
       </c>
-      <c r="F49" s="79" t="n">
+      <c r="F49" s="81" t="n">
         <v>-22</v>
       </c>
-      <c r="G49" s="80" t="n">
+      <c r="G49" s="82" t="n">
         <v>6</v>
       </c>
-      <c r="H49" s="81" t="n">
+      <c r="H49" s="83" t="n">
         <v>88</v>
       </c>
-      <c r="I49" s="81" t="n">
+      <c r="I49" s="83" t="n">
         <v>236</v>
       </c>
-      <c r="J49" s="81" t="n">
+      <c r="J49" s="83" t="n">
         <v>380</v>
       </c>
-      <c r="K49" s="81" t="n">
+      <c r="K49" s="83" t="n">
         <v>450</v>
       </c>
-      <c r="L49" s="81" t="n">
+      <c r="L49" s="83" t="n">
         <v>630</v>
       </c>
-      <c r="M49" s="81" t="n">
+      <c r="M49" s="83" t="n">
         <v>941</v>
       </c>
-      <c r="N49" s="80" t="n">
+      <c r="N49" s="82" t="n">
         <v>1854</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="70" t="inlineStr">
+      <c r="A50" s="72" t="inlineStr">
         <is>
           <t>営業利益率</t>
         </is>
       </c>
-      <c r="B50" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="71" t="n">
+      <c r="B50" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="73" t="n">
         <v>-124.5</v>
       </c>
-      <c r="E50" s="71" t="n">
+      <c r="E50" s="73" t="n">
         <v>-29.4</v>
       </c>
-      <c r="F50" s="71" t="n">
+      <c r="F50" s="73" t="n">
         <v>-4.6</v>
       </c>
-      <c r="G50" s="71" t="n">
+      <c r="G50" s="73" t="n">
         <v>1.2</v>
       </c>
-      <c r="H50" s="71" t="n">
+      <c r="H50" s="73" t="n">
         <v>12.6</v>
       </c>
-      <c r="I50" s="71" t="n">
+      <c r="I50" s="73" t="n">
         <v>26.4</v>
       </c>
-      <c r="J50" s="71" t="n">
+      <c r="J50" s="73" t="n">
         <v>34.7</v>
       </c>
-      <c r="K50" s="71" t="n">
+      <c r="K50" s="73" t="n">
         <v>38.6</v>
       </c>
-      <c r="L50" s="71" t="n">
+      <c r="L50" s="73" t="n">
         <v>44.9</v>
       </c>
-      <c r="M50" s="71" t="n">
+      <c r="M50" s="73" t="n">
         <v>52</v>
       </c>
-      <c r="N50" s="72" t="n">
+      <c r="N50" s="74" t="n">
         <v>5.2</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="82" t="inlineStr">
+      <c r="A51" s="84" t="inlineStr">
         <is>
           <t>★ 損益分岐：M6　／　Year1通期営業利益：1,854万円　／　Year1売上：8,519万円</t>
         </is>
@@ -3975,7 +3993,7 @@
       <c r="N51" s="2" t="n"/>
     </row>
     <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="83" t="inlineStr">
+      <c r="A52" s="85" t="inlineStr">
         <is>
           <t>【注記】単位：万円 ／ ギャル協会：出演・監修料=件数×25万（最低保証10万）、EC物販はギャル協会がショップオーナー（バズに原価なし） ／ バズEC収益=アフィリエイトコミッション（EC実売上×20%） ／ 制作費：TIE×10% ／ ENTIAL：TIE成功報酬×5%（EC運用除外）</t>
         </is>
@@ -4033,86 +4051,86 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="84" t="inlineStr">
+      <c r="A1" s="86" t="inlineStr">
         <is>
           <t>❷ 及第点パターン  ／  Year1 月次事業計画（バズ社PL）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>Year1でバズ売上5,510万・営業利益397万・M7損益分岐　単位：万円</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="F3" s="33" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="G3" s="33" t="inlineStr">
+      <c r="G3" s="35" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="H3" s="33" t="inlineStr">
+      <c r="H3" s="35" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="I3" s="33" t="inlineStr">
+      <c r="I3" s="35" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="J3" s="33" t="inlineStr">
+      <c r="J3" s="35" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="K3" s="33" t="inlineStr">
+      <c r="K3" s="35" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="L3" s="33" t="inlineStr">
+      <c r="L3" s="35" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="M3" s="33" t="inlineStr">
+      <c r="M3" s="35" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="N3" s="33" t="inlineStr">
+      <c r="N3" s="35" t="inlineStr">
         <is>
           <t>Year1合計</t>
         </is>
@@ -4139,411 +4157,411 @@
       <c r="N4" s="2" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>TikTokフォロワー数（累計）</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="51" t="n">
         <v>300</v>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="51" t="n">
         <v>1000</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="51" t="n">
         <v>2500</v>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="51" t="n">
         <v>9000</v>
       </c>
-      <c r="G5" s="49" t="n">
+      <c r="G5" s="51" t="n">
         <v>15000</v>
       </c>
-      <c r="H5" s="49" t="n">
+      <c r="H5" s="51" t="n">
         <v>22000</v>
       </c>
-      <c r="I5" s="49" t="n">
+      <c r="I5" s="51" t="n">
         <v>30000</v>
       </c>
-      <c r="J5" s="49" t="n">
+      <c r="J5" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="K5" s="49" t="n">
+      <c r="K5" s="51" t="n">
         <v>52000</v>
       </c>
-      <c r="L5" s="49" t="n">
+      <c r="L5" s="51" t="n">
         <v>66000</v>
       </c>
-      <c r="M5" s="49" t="n">
+      <c r="M5" s="51" t="n">
         <v>82000</v>
       </c>
-      <c r="N5" s="49" t="n">
+      <c r="N5" s="51" t="n">
         <v>82000</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>IGフォロワー数（累計）</t>
         </is>
       </c>
-      <c r="B6" s="51" t="n">
+      <c r="B6" s="53" t="n">
         <v>200</v>
       </c>
-      <c r="C6" s="51" t="n">
+      <c r="C6" s="53" t="n">
         <v>600</v>
       </c>
-      <c r="D6" s="51" t="n">
+      <c r="D6" s="53" t="n">
         <v>1500</v>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="53" t="n">
         <v>3000</v>
       </c>
-      <c r="F6" s="51" t="n">
+      <c r="F6" s="53" t="n">
         <v>6000</v>
       </c>
-      <c r="G6" s="51" t="n">
+      <c r="G6" s="53" t="n">
         <v>10000</v>
       </c>
-      <c r="H6" s="51" t="n">
+      <c r="H6" s="53" t="n">
         <v>15000</v>
       </c>
-      <c r="I6" s="51" t="n">
+      <c r="I6" s="53" t="n">
         <v>21000</v>
       </c>
-      <c r="J6" s="51" t="n">
+      <c r="J6" s="53" t="n">
         <v>28000</v>
       </c>
-      <c r="K6" s="51" t="n">
+      <c r="K6" s="53" t="n">
         <v>36000</v>
       </c>
-      <c r="L6" s="51" t="n">
+      <c r="L6" s="53" t="n">
         <v>46000</v>
       </c>
-      <c r="M6" s="51" t="n">
+      <c r="M6" s="53" t="n">
         <v>58000</v>
       </c>
-      <c r="N6" s="51" t="n">
+      <c r="N6" s="53" t="n">
         <v>58000</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>TKタイアップ受注社数（月次）</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="49" t="n">
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="49" t="n">
+      <c r="G7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="49" t="n">
+      <c r="H7" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="49" t="n">
+      <c r="I7" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="49" t="n">
+      <c r="J7" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="L7" s="49" t="n">
+      <c r="L7" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="49" t="n">
+      <c r="M7" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="N7" s="49" t="n">
+      <c r="N7" s="51" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>TKタイアップ平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="F8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="G8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="H8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="I8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="J8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="K8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="L8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="M8" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="N8" s="55" t="n">
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="F8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="G8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="H8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="I8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="J8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="K8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="L8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="M8" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="N8" s="57" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>IGタイアップ受注社数（月次）</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="49" t="n">
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="49" t="n">
+      <c r="G9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="49" t="n">
+      <c r="H9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="49" t="n">
+      <c r="I9" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="49" t="n">
+      <c r="J9" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="49" t="n">
+      <c r="K9" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="49" t="n">
+      <c r="L9" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="49" t="n">
+      <c r="M9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="N9" s="49" t="n">
+      <c r="N9" s="51" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>IGタイアップ平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="G10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="H10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="I10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="J10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="K10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="L10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="M10" s="54" t="n">
-        <v>150</v>
-      </c>
-      <c r="N10" s="55" t="n">
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="G10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="H10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="I10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="J10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="K10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="L10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="M10" s="56" t="n">
+        <v>150</v>
+      </c>
+      <c r="N10" s="57" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>EC注文件数（TikTok Shop）</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="49" t="n">
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="51" t="n">
         <v>70</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="51" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="51" t="n">
         <v>250</v>
       </c>
-      <c r="H11" s="49" t="n">
+      <c r="H11" s="51" t="n">
         <v>400</v>
       </c>
-      <c r="I11" s="49" t="n">
+      <c r="I11" s="51" t="n">
         <v>600</v>
       </c>
-      <c r="J11" s="49" t="n">
+      <c r="J11" s="51" t="n">
         <v>800</v>
       </c>
-      <c r="K11" s="49" t="n">
+      <c r="K11" s="51" t="n">
         <v>1050</v>
       </c>
-      <c r="L11" s="49" t="n">
+      <c r="L11" s="51" t="n">
         <v>1400</v>
       </c>
-      <c r="M11" s="49" t="n">
+      <c r="M11" s="51" t="n">
         <v>1800</v>
       </c>
-      <c r="N11" s="49" t="n">
+      <c r="N11" s="51" t="n">
         <v>6530</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>EC平均注文単価（円）</t>
         </is>
       </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="54" t="n">
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="n">
         <v>4500</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="F12" s="54" t="n">
+      <c r="F12" s="56" t="n">
         <v>5500</v>
       </c>
-      <c r="G12" s="54" t="n">
+      <c r="G12" s="56" t="n">
         <v>5500</v>
       </c>
-      <c r="H12" s="54" t="n">
+      <c r="H12" s="56" t="n">
         <v>6000</v>
       </c>
-      <c r="I12" s="54" t="n">
+      <c r="I12" s="56" t="n">
         <v>6000</v>
       </c>
-      <c r="J12" s="54" t="n">
+      <c r="J12" s="56" t="n">
         <v>6500</v>
       </c>
-      <c r="K12" s="54" t="n">
+      <c r="K12" s="56" t="n">
         <v>6500</v>
       </c>
-      <c r="L12" s="54" t="n">
+      <c r="L12" s="56" t="n">
         <v>7000</v>
       </c>
-      <c r="M12" s="54" t="n">
+      <c r="M12" s="56" t="n">
         <v>7000</v>
       </c>
-      <c r="N12" s="55" t="n">
+      <c r="N12" s="57" t="n">
         <v>5950</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="56" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>▌ 損益計算書（P/L）　単位：万円</t>
         </is>
@@ -4563,568 +4581,568 @@
       <c r="N13" s="2" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>【売上高】</t>
         </is>
       </c>
-      <c r="B14" s="58" t="n"/>
-      <c r="C14" s="58" t="n"/>
-      <c r="D14" s="58" t="n"/>
-      <c r="E14" s="58" t="n"/>
-      <c r="F14" s="58" t="n"/>
-      <c r="G14" s="58" t="n"/>
-      <c r="H14" s="58" t="n"/>
-      <c r="I14" s="58" t="n"/>
-      <c r="J14" s="58" t="n"/>
-      <c r="K14" s="58" t="n"/>
-      <c r="L14" s="58" t="n"/>
-      <c r="M14" s="58" t="n"/>
-      <c r="N14" s="58" t="n"/>
+      <c r="B14" s="60" t="n"/>
+      <c r="C14" s="60" t="n"/>
+      <c r="D14" s="60" t="n"/>
+      <c r="E14" s="60" t="n"/>
+      <c r="F14" s="60" t="n"/>
+      <c r="G14" s="60" t="n"/>
+      <c r="H14" s="60" t="n"/>
+      <c r="I14" s="60" t="n"/>
+      <c r="J14" s="60" t="n"/>
+      <c r="K14" s="60" t="n"/>
+      <c r="L14" s="60" t="n"/>
+      <c r="M14" s="60" t="n"/>
+      <c r="N14" s="60" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ① TikTokメディアタイアップ</t>
         </is>
       </c>
-      <c r="B15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="F15" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="G15" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="H15" s="59" t="n">
+      <c r="B15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="F15" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="G15" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="I15" s="59" t="n">
+      <c r="I15" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="J15" s="59" t="n">
+      <c r="J15" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="K15" s="59" t="n">
+      <c r="K15" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="L15" s="59" t="n">
+      <c r="L15" s="61" t="n">
         <v>450</v>
       </c>
-      <c r="M15" s="59" t="n">
+      <c r="M15" s="61" t="n">
         <v>450</v>
       </c>
-      <c r="N15" s="55" t="n">
+      <c r="N15" s="57" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     受注社数（社）</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="62" t="n">
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="62" t="n">
+      <c r="F16" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="62" t="n">
+      <c r="G16" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="62" t="n">
+      <c r="H16" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="62" t="n">
+      <c r="I16" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="62" t="n">
+      <c r="J16" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="K16" s="62" t="n">
+      <c r="K16" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="L16" s="62" t="n">
+      <c r="L16" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="M16" s="62" t="n">
+      <c r="M16" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="N16" s="63" t="n">
+      <c r="N16" s="65" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="F17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="G17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="H17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="I17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="J17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="K17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="L17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="M17" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="N17" s="63" t="n">
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="F17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="I17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="J17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="K17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="L17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="M17" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="N17" s="65" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ② IGメディアタイアップ</t>
         </is>
       </c>
-      <c r="B18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="G18" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="H18" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="I18" s="59" t="n">
+      <c r="B18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="G18" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="H18" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="I18" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="J18" s="59" t="n">
+      <c r="J18" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="K18" s="59" t="n">
+      <c r="K18" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="L18" s="59" t="n">
+      <c r="L18" s="61" t="n">
         <v>300</v>
       </c>
-      <c r="M18" s="59" t="n">
+      <c r="M18" s="61" t="n">
         <v>450</v>
       </c>
-      <c r="N18" s="55" t="n">
+      <c r="N18" s="57" t="n">
         <v>2100</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     受注社数（社）</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="62" t="n">
+      <c r="B19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="62" t="n">
+      <c r="G19" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="62" t="n">
+      <c r="H19" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="62" t="n">
+      <c r="I19" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="62" t="n">
+      <c r="J19" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="K19" s="62" t="n">
+      <c r="K19" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="L19" s="62" t="n">
+      <c r="L19" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="M19" s="62" t="n">
+      <c r="M19" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="N19" s="63" t="n">
+      <c r="N19" s="65" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="G20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="H20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="I20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="J20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="K20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="L20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="M20" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="N20" s="63" t="n">
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="G20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="H20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="I20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="J20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="K20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="L20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="M20" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="N20" s="65" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="64" t="inlineStr">
+      <c r="A21" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">  タイアップ売上合計</t>
         </is>
       </c>
-      <c r="B21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="65" t="n">
-        <v>150</v>
-      </c>
-      <c r="F21" s="65" t="n">
+      <c r="B21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="67" t="n">
+        <v>150</v>
+      </c>
+      <c r="F21" s="67" t="n">
         <v>300</v>
       </c>
-      <c r="G21" s="65" t="n">
+      <c r="G21" s="67" t="n">
         <v>300</v>
       </c>
-      <c r="H21" s="65" t="n">
+      <c r="H21" s="67" t="n">
         <v>450</v>
       </c>
-      <c r="I21" s="65" t="n">
+      <c r="I21" s="67" t="n">
         <v>600</v>
       </c>
-      <c r="J21" s="65" t="n">
+      <c r="J21" s="67" t="n">
         <v>600</v>
       </c>
-      <c r="K21" s="65" t="n">
+      <c r="K21" s="67" t="n">
         <v>600</v>
       </c>
-      <c r="L21" s="65" t="n">
+      <c r="L21" s="67" t="n">
         <v>750</v>
       </c>
-      <c r="M21" s="65" t="n">
+      <c r="M21" s="67" t="n">
         <v>900</v>
       </c>
-      <c r="N21" s="65" t="n">
+      <c r="N21" s="67" t="n">
         <v>4650</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ③ ECアフィリエイトコミッション（×20%）</t>
         </is>
       </c>
-      <c r="B22" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="59" t="n">
+      <c r="B22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="59" t="n">
+      <c r="E22" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="F22" s="59" t="n">
+      <c r="F22" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="G22" s="59" t="n">
+      <c r="G22" s="61" t="n">
         <v>28</v>
       </c>
-      <c r="H22" s="59" t="n">
+      <c r="H22" s="61" t="n">
         <v>48</v>
       </c>
-      <c r="I22" s="59" t="n">
+      <c r="I22" s="61" t="n">
         <v>72</v>
       </c>
-      <c r="J22" s="59" t="n">
+      <c r="J22" s="61" t="n">
         <v>104</v>
       </c>
-      <c r="K22" s="59" t="n">
+      <c r="K22" s="61" t="n">
         <v>136</v>
       </c>
-      <c r="L22" s="59" t="n">
+      <c r="L22" s="61" t="n">
         <v>196</v>
       </c>
-      <c r="M22" s="59" t="n">
+      <c r="M22" s="61" t="n">
         <v>252</v>
       </c>
-      <c r="N22" s="55" t="n">
+      <c r="N22" s="57" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     EC実売上（ギャル協会側・参考値）</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="62" t="n">
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="64" t="n">
         <v>14</v>
       </c>
-      <c r="E23" s="62" t="n">
+      <c r="E23" s="64" t="n">
         <v>35</v>
       </c>
-      <c r="F23" s="62" t="n">
+      <c r="F23" s="64" t="n">
         <v>72</v>
       </c>
-      <c r="G23" s="62" t="n">
+      <c r="G23" s="64" t="n">
         <v>138</v>
       </c>
-      <c r="H23" s="62" t="n">
+      <c r="H23" s="64" t="n">
         <v>240</v>
       </c>
-      <c r="I23" s="62" t="n">
+      <c r="I23" s="64" t="n">
         <v>360</v>
       </c>
-      <c r="J23" s="62" t="n">
+      <c r="J23" s="64" t="n">
         <v>520</v>
       </c>
-      <c r="K23" s="62" t="n">
+      <c r="K23" s="64" t="n">
         <v>682</v>
       </c>
-      <c r="L23" s="62" t="n">
+      <c r="L23" s="64" t="n">
         <v>980</v>
       </c>
-      <c r="M23" s="62" t="n">
+      <c r="M23" s="64" t="n">
         <v>1260</v>
       </c>
-      <c r="N23" s="63" t="n">
+      <c r="N23" s="65" t="n">
         <v>4301</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     注文件数（件）</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="62" t="n">
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="64" t="n">
         <v>30</v>
       </c>
-      <c r="E24" s="62" t="n">
+      <c r="E24" s="64" t="n">
         <v>70</v>
       </c>
-      <c r="F24" s="62" t="n">
+      <c r="F24" s="64" t="n">
         <v>130</v>
       </c>
-      <c r="G24" s="62" t="n">
+      <c r="G24" s="64" t="n">
         <v>250</v>
       </c>
-      <c r="H24" s="62" t="n">
+      <c r="H24" s="64" t="n">
         <v>400</v>
       </c>
-      <c r="I24" s="62" t="n">
+      <c r="I24" s="64" t="n">
         <v>600</v>
       </c>
-      <c r="J24" s="62" t="n">
+      <c r="J24" s="64" t="n">
         <v>800</v>
       </c>
-      <c r="K24" s="62" t="n">
+      <c r="K24" s="64" t="n">
         <v>1050</v>
       </c>
-      <c r="L24" s="62" t="n">
+      <c r="L24" s="64" t="n">
         <v>1400</v>
       </c>
-      <c r="M24" s="62" t="n">
+      <c r="M24" s="64" t="n">
         <v>1800</v>
       </c>
-      <c r="N24" s="63" t="n">
+      <c r="N24" s="65" t="n">
         <v>6530</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="60" t="inlineStr">
+      <c r="A25" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     平均注文単価（円）</t>
         </is>
       </c>
-      <c r="B25" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="62" t="n">
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="64" t="n">
         <v>4500</v>
       </c>
-      <c r="E25" s="62" t="n">
+      <c r="E25" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="F25" s="62" t="n">
+      <c r="F25" s="64" t="n">
         <v>5500</v>
       </c>
-      <c r="G25" s="62" t="n">
+      <c r="G25" s="64" t="n">
         <v>5500</v>
       </c>
-      <c r="H25" s="62" t="n">
+      <c r="H25" s="64" t="n">
         <v>6000</v>
       </c>
-      <c r="I25" s="62" t="n">
+      <c r="I25" s="64" t="n">
         <v>6000</v>
       </c>
-      <c r="J25" s="62" t="n">
+      <c r="J25" s="64" t="n">
         <v>6500</v>
       </c>
-      <c r="K25" s="62" t="n">
+      <c r="K25" s="64" t="n">
         <v>6500</v>
       </c>
-      <c r="L25" s="62" t="n">
+      <c r="L25" s="64" t="n">
         <v>7000</v>
       </c>
-      <c r="M25" s="62" t="n">
+      <c r="M25" s="64" t="n">
         <v>7000</v>
       </c>
-      <c r="N25" s="63" t="n">
+      <c r="N25" s="65" t="n">
         <v>5950</v>
       </c>
     </row>
@@ -5134,269 +5152,269 @@
           <t>売上合計</t>
         </is>
       </c>
-      <c r="B26" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="66" t="n">
+      <c r="B26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="66" t="n">
+      <c r="E26" s="68" t="n">
         <v>157</v>
       </c>
-      <c r="F26" s="66" t="n">
+      <c r="F26" s="68" t="n">
         <v>314</v>
       </c>
-      <c r="G26" s="66" t="n">
+      <c r="G26" s="68" t="n">
         <v>328</v>
       </c>
-      <c r="H26" s="66" t="n">
+      <c r="H26" s="68" t="n">
         <v>498</v>
       </c>
-      <c r="I26" s="66" t="n">
+      <c r="I26" s="68" t="n">
         <v>672</v>
       </c>
-      <c r="J26" s="66" t="n">
+      <c r="J26" s="68" t="n">
         <v>704</v>
       </c>
-      <c r="K26" s="66" t="n">
+      <c r="K26" s="68" t="n">
         <v>736</v>
       </c>
-      <c r="L26" s="66" t="n">
+      <c r="L26" s="68" t="n">
         <v>946</v>
       </c>
-      <c r="M26" s="66" t="n">
+      <c r="M26" s="68" t="n">
         <v>1152</v>
       </c>
-      <c r="N26" s="66" t="n">
+      <c r="N26" s="68" t="n">
         <v>5510</v>
       </c>
     </row>
     <row r="27" ht="6" customHeight="1">
-      <c r="A27" s="67" t="inlineStr"/>
-      <c r="B27" s="68" t="n"/>
-      <c r="C27" s="68" t="n"/>
-      <c r="D27" s="68" t="n"/>
-      <c r="E27" s="68" t="n"/>
-      <c r="F27" s="68" t="n"/>
-      <c r="G27" s="68" t="n"/>
-      <c r="H27" s="68" t="n"/>
-      <c r="I27" s="68" t="n"/>
-      <c r="J27" s="68" t="n"/>
-      <c r="K27" s="68" t="n"/>
-      <c r="L27" s="68" t="n"/>
-      <c r="M27" s="68" t="n"/>
-      <c r="N27" s="68" t="n"/>
+      <c r="A27" s="69" t="inlineStr"/>
+      <c r="B27" s="70" t="n"/>
+      <c r="C27" s="70" t="n"/>
+      <c r="D27" s="70" t="n"/>
+      <c r="E27" s="70" t="n"/>
+      <c r="F27" s="70" t="n"/>
+      <c r="G27" s="70" t="n"/>
+      <c r="H27" s="70" t="n"/>
+      <c r="I27" s="70" t="n"/>
+      <c r="J27" s="70" t="n"/>
+      <c r="K27" s="70" t="n"/>
+      <c r="L27" s="70" t="n"/>
+      <c r="M27" s="70" t="n"/>
+      <c r="N27" s="70" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="57" t="inlineStr">
+      <c r="A28" s="59" t="inlineStr">
         <is>
           <t>【タイアップ原価】</t>
         </is>
       </c>
-      <c r="B28" s="58" t="n"/>
-      <c r="C28" s="58" t="n"/>
-      <c r="D28" s="58" t="n"/>
-      <c r="E28" s="58" t="n"/>
-      <c r="F28" s="58" t="n"/>
-      <c r="G28" s="58" t="n"/>
-      <c r="H28" s="58" t="n"/>
-      <c r="I28" s="58" t="n"/>
-      <c r="J28" s="58" t="n"/>
-      <c r="K28" s="58" t="n"/>
-      <c r="L28" s="58" t="n"/>
-      <c r="M28" s="58" t="n"/>
-      <c r="N28" s="58" t="n"/>
+      <c r="B28" s="60" t="n"/>
+      <c r="C28" s="60" t="n"/>
+      <c r="D28" s="60" t="n"/>
+      <c r="E28" s="60" t="n"/>
+      <c r="F28" s="60" t="n"/>
+      <c r="G28" s="60" t="n"/>
+      <c r="H28" s="60" t="n"/>
+      <c r="I28" s="60" t="n"/>
+      <c r="J28" s="60" t="n"/>
+      <c r="K28" s="60" t="n"/>
+      <c r="L28" s="60" t="n"/>
+      <c r="M28" s="60" t="n"/>
+      <c r="N28" s="60" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ギャル協会出演・監修料（件数×25万・最低保証10万）</t>
         </is>
       </c>
-      <c r="B29" s="59" t="n">
+      <c r="B29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="C29" s="59" t="n">
+      <c r="C29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="59" t="n">
+      <c r="D29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="E29" s="59" t="n">
+      <c r="E29" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="F29" s="59" t="n">
+      <c r="F29" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="G29" s="59" t="n">
+      <c r="G29" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="H29" s="59" t="n">
+      <c r="H29" s="61" t="n">
         <v>75</v>
       </c>
-      <c r="I29" s="59" t="n">
+      <c r="I29" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="J29" s="59" t="n">
+      <c r="J29" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="K29" s="59" t="n">
+      <c r="K29" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="L29" s="59" t="n">
+      <c r="L29" s="61" t="n">
         <v>125</v>
       </c>
-      <c r="M29" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="N29" s="55" t="n">
+      <c r="M29" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="N29" s="57" t="n">
         <v>805</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     タイアップ件数（社）</t>
         </is>
       </c>
-      <c r="B30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="62" t="n">
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="62" t="n">
+      <c r="F30" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="62" t="n">
+      <c r="G30" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="62" t="n">
+      <c r="H30" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="62" t="n">
+      <c r="I30" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="J30" s="62" t="n">
+      <c r="J30" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="K30" s="62" t="n">
+      <c r="K30" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="L30" s="62" t="n">
+      <c r="L30" s="64" t="n">
         <v>5</v>
       </c>
-      <c r="M30" s="62" t="n">
+      <c r="M30" s="64" t="n">
         <v>6</v>
       </c>
-      <c r="N30" s="63" t="n">
+      <c r="N30" s="65" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  コンテンツ制作費（×10%）</t>
         </is>
       </c>
-      <c r="B31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="59" t="n">
+      <c r="B31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="F31" s="59" t="n">
+      <c r="F31" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="G31" s="59" t="n">
+      <c r="G31" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="H31" s="59" t="n">
+      <c r="H31" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="I31" s="59" t="n">
+      <c r="I31" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="J31" s="59" t="n">
+      <c r="J31" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="K31" s="59" t="n">
+      <c r="K31" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="L31" s="59" t="n">
+      <c r="L31" s="61" t="n">
         <v>75</v>
       </c>
-      <c r="M31" s="59" t="n">
+      <c r="M31" s="61" t="n">
         <v>90</v>
       </c>
-      <c r="N31" s="55" t="n">
+      <c r="N31" s="57" t="n">
         <v>465</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="64" t="inlineStr">
+      <c r="A32" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">  タイアップ原価合計</t>
         </is>
       </c>
-      <c r="B32" s="65" t="n">
+      <c r="B32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="C32" s="65" t="n">
+      <c r="C32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="65" t="n">
+      <c r="D32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="E32" s="65" t="n">
+      <c r="E32" s="67" t="n">
         <v>40</v>
       </c>
-      <c r="F32" s="65" t="n">
+      <c r="F32" s="67" t="n">
         <v>80</v>
       </c>
-      <c r="G32" s="65" t="n">
+      <c r="G32" s="67" t="n">
         <v>80</v>
       </c>
-      <c r="H32" s="65" t="n">
+      <c r="H32" s="67" t="n">
         <v>120</v>
       </c>
-      <c r="I32" s="65" t="n">
+      <c r="I32" s="67" t="n">
         <v>160</v>
       </c>
-      <c r="J32" s="65" t="n">
+      <c r="J32" s="67" t="n">
         <v>160</v>
       </c>
-      <c r="K32" s="65" t="n">
+      <c r="K32" s="67" t="n">
         <v>160</v>
       </c>
-      <c r="L32" s="65" t="n">
+      <c r="L32" s="67" t="n">
         <v>200</v>
       </c>
-      <c r="M32" s="65" t="n">
+      <c r="M32" s="67" t="n">
         <v>240</v>
       </c>
-      <c r="N32" s="65" t="n">
+      <c r="N32" s="67" t="n">
         <v>1270</v>
       </c>
     </row>
@@ -5406,658 +5424,658 @@
           <t xml:space="preserve">  タイアップ粗利</t>
         </is>
       </c>
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="C33" s="31" t="n">
+      <c r="C33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="D33" s="31" t="n">
+      <c r="D33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="E33" s="69" t="n">
+      <c r="E33" s="71" t="n">
         <v>110</v>
       </c>
-      <c r="F33" s="69" t="n">
+      <c r="F33" s="71" t="n">
         <v>220</v>
       </c>
-      <c r="G33" s="69" t="n">
+      <c r="G33" s="71" t="n">
         <v>220</v>
       </c>
-      <c r="H33" s="69" t="n">
+      <c r="H33" s="71" t="n">
         <v>330</v>
       </c>
-      <c r="I33" s="69" t="n">
+      <c r="I33" s="71" t="n">
         <v>440</v>
       </c>
-      <c r="J33" s="69" t="n">
+      <c r="J33" s="71" t="n">
         <v>440</v>
       </c>
-      <c r="K33" s="69" t="n">
+      <c r="K33" s="71" t="n">
         <v>440</v>
       </c>
-      <c r="L33" s="69" t="n">
+      <c r="L33" s="71" t="n">
         <v>550</v>
       </c>
-      <c r="M33" s="69" t="n">
+      <c r="M33" s="71" t="n">
         <v>660</v>
       </c>
-      <c r="N33" s="69" t="n">
+      <c r="N33" s="71" t="n">
         <v>3380</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="70" t="inlineStr">
+      <c r="A34" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">  タイアップ粗利率</t>
         </is>
       </c>
-      <c r="B34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="71" t="n">
+      <c r="B34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="F34" s="71" t="n">
+      <c r="F34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="G34" s="71" t="n">
+      <c r="G34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="H34" s="71" t="n">
+      <c r="H34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="I34" s="71" t="n">
+      <c r="I34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="J34" s="71" t="n">
+      <c r="J34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="K34" s="71" t="n">
+      <c r="K34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="L34" s="71" t="n">
+      <c r="L34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="M34" s="71" t="n">
+      <c r="M34" s="73" t="n">
         <v>73.3</v>
       </c>
-      <c r="N34" s="72" t="n">
+      <c r="N34" s="74" t="n">
         <v>73.3</v>
       </c>
     </row>
     <row r="35" ht="6" customHeight="1">
-      <c r="A35" s="67" t="inlineStr"/>
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="68" t="n"/>
-      <c r="D35" s="68" t="n"/>
-      <c r="E35" s="68" t="n"/>
-      <c r="F35" s="68" t="n"/>
-      <c r="G35" s="68" t="n"/>
-      <c r="H35" s="68" t="n"/>
-      <c r="I35" s="68" t="n"/>
-      <c r="J35" s="68" t="n"/>
-      <c r="K35" s="68" t="n"/>
-      <c r="L35" s="68" t="n"/>
-      <c r="M35" s="68" t="n"/>
-      <c r="N35" s="68" t="n"/>
+      <c r="A35" s="69" t="inlineStr"/>
+      <c r="B35" s="70" t="n"/>
+      <c r="C35" s="70" t="n"/>
+      <c r="D35" s="70" t="n"/>
+      <c r="E35" s="70" t="n"/>
+      <c r="F35" s="70" t="n"/>
+      <c r="G35" s="70" t="n"/>
+      <c r="H35" s="70" t="n"/>
+      <c r="I35" s="70" t="n"/>
+      <c r="J35" s="70" t="n"/>
+      <c r="K35" s="70" t="n"/>
+      <c r="L35" s="70" t="n"/>
+      <c r="M35" s="70" t="n"/>
+      <c r="N35" s="70" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  ※ECコミッション（原価ゼロ）→ ギャル協会がショップオーナー</t>
         </is>
       </c>
-      <c r="B36" s="73" t="n"/>
-      <c r="C36" s="73" t="n"/>
-      <c r="D36" s="73" t="n"/>
-      <c r="E36" s="73" t="n"/>
-      <c r="F36" s="73" t="n"/>
-      <c r="G36" s="73" t="n"/>
-      <c r="H36" s="73" t="n"/>
-      <c r="I36" s="73" t="n"/>
-      <c r="J36" s="73" t="n"/>
-      <c r="K36" s="73" t="n"/>
-      <c r="L36" s="73" t="n"/>
-      <c r="M36" s="73" t="n"/>
-      <c r="N36" s="73" t="n"/>
+      <c r="B36" s="75" t="n"/>
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="75" t="n"/>
+      <c r="E36" s="75" t="n"/>
+      <c r="F36" s="75" t="n"/>
+      <c r="G36" s="75" t="n"/>
+      <c r="H36" s="75" t="n"/>
+      <c r="I36" s="75" t="n"/>
+      <c r="J36" s="75" t="n"/>
+      <c r="K36" s="75" t="n"/>
+      <c r="L36" s="75" t="n"/>
+      <c r="M36" s="75" t="n"/>
+      <c r="N36" s="75" t="n"/>
     </row>
     <row r="37" ht="6" customHeight="1">
-      <c r="A37" s="67" t="inlineStr"/>
-      <c r="B37" s="68" t="n"/>
-      <c r="C37" s="68" t="n"/>
-      <c r="D37" s="68" t="n"/>
-      <c r="E37" s="68" t="n"/>
-      <c r="F37" s="68" t="n"/>
-      <c r="G37" s="68" t="n"/>
-      <c r="H37" s="68" t="n"/>
-      <c r="I37" s="68" t="n"/>
-      <c r="J37" s="68" t="n"/>
-      <c r="K37" s="68" t="n"/>
-      <c r="L37" s="68" t="n"/>
-      <c r="M37" s="68" t="n"/>
-      <c r="N37" s="68" t="n"/>
+      <c r="A37" s="69" t="inlineStr"/>
+      <c r="B37" s="70" t="n"/>
+      <c r="C37" s="70" t="n"/>
+      <c r="D37" s="70" t="n"/>
+      <c r="E37" s="70" t="n"/>
+      <c r="F37" s="70" t="n"/>
+      <c r="G37" s="70" t="n"/>
+      <c r="H37" s="70" t="n"/>
+      <c r="I37" s="70" t="n"/>
+      <c r="J37" s="70" t="n"/>
+      <c r="K37" s="70" t="n"/>
+      <c r="L37" s="70" t="n"/>
+      <c r="M37" s="70" t="n"/>
+      <c r="N37" s="70" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="74" t="inlineStr">
+      <c r="A38" s="76" t="inlineStr">
         <is>
           <t>売上原価合計</t>
         </is>
       </c>
-      <c r="B38" s="75" t="n">
+      <c r="B38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="C38" s="75" t="n">
+      <c r="C38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="75" t="n">
+      <c r="D38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="E38" s="75" t="n">
+      <c r="E38" s="77" t="n">
         <v>40</v>
       </c>
-      <c r="F38" s="75" t="n">
+      <c r="F38" s="77" t="n">
         <v>80</v>
       </c>
-      <c r="G38" s="75" t="n">
+      <c r="G38" s="77" t="n">
         <v>80</v>
       </c>
-      <c r="H38" s="75" t="n">
+      <c r="H38" s="77" t="n">
         <v>120</v>
       </c>
-      <c r="I38" s="75" t="n">
+      <c r="I38" s="77" t="n">
         <v>160</v>
       </c>
-      <c r="J38" s="75" t="n">
+      <c r="J38" s="77" t="n">
         <v>160</v>
       </c>
-      <c r="K38" s="75" t="n">
+      <c r="K38" s="77" t="n">
         <v>160</v>
       </c>
-      <c r="L38" s="75" t="n">
+      <c r="L38" s="77" t="n">
         <v>200</v>
       </c>
-      <c r="M38" s="75" t="n">
+      <c r="M38" s="77" t="n">
         <v>240</v>
       </c>
-      <c r="N38" s="75" t="n">
+      <c r="N38" s="77" t="n">
         <v>1270</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="76" t="inlineStr">
+      <c r="A39" s="78" t="inlineStr">
         <is>
           <t>粗利益合計</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n">
+      <c r="B39" s="79" t="n">
         <v>-10</v>
       </c>
-      <c r="C39" s="77" t="n">
+      <c r="C39" s="79" t="n">
         <v>-10</v>
       </c>
-      <c r="D39" s="77" t="n">
+      <c r="D39" s="79" t="n">
         <v>-7</v>
       </c>
-      <c r="E39" s="78" t="n">
+      <c r="E39" s="80" t="n">
         <v>117</v>
       </c>
-      <c r="F39" s="78" t="n">
+      <c r="F39" s="80" t="n">
         <v>234</v>
       </c>
-      <c r="G39" s="78" t="n">
+      <c r="G39" s="80" t="n">
         <v>248</v>
       </c>
-      <c r="H39" s="78" t="n">
+      <c r="H39" s="80" t="n">
         <v>378</v>
       </c>
-      <c r="I39" s="78" t="n">
+      <c r="I39" s="80" t="n">
         <v>512</v>
       </c>
-      <c r="J39" s="78" t="n">
+      <c r="J39" s="80" t="n">
         <v>544</v>
       </c>
-      <c r="K39" s="78" t="n">
+      <c r="K39" s="80" t="n">
         <v>576</v>
       </c>
-      <c r="L39" s="78" t="n">
+      <c r="L39" s="80" t="n">
         <v>746</v>
       </c>
-      <c r="M39" s="78" t="n">
+      <c r="M39" s="80" t="n">
         <v>912</v>
       </c>
-      <c r="N39" s="78" t="n">
+      <c r="N39" s="80" t="n">
         <v>4240</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="70" t="inlineStr">
+      <c r="A40" s="72" t="inlineStr">
         <is>
           <t>粗利率（合計）</t>
         </is>
       </c>
-      <c r="B40" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="71" t="n">
+      <c r="B40" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="73" t="n">
         <v>-233.3</v>
       </c>
-      <c r="E40" s="71" t="n">
+      <c r="E40" s="73" t="n">
         <v>74.5</v>
       </c>
-      <c r="F40" s="71" t="n">
+      <c r="F40" s="73" t="n">
         <v>74.5</v>
       </c>
-      <c r="G40" s="71" t="n">
+      <c r="G40" s="73" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="H40" s="71" t="n">
+      <c r="H40" s="73" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="I40" s="71" t="n">
+      <c r="I40" s="73" t="n">
         <v>76.2</v>
       </c>
-      <c r="J40" s="71" t="n">
+      <c r="J40" s="73" t="n">
         <v>77.3</v>
       </c>
-      <c r="K40" s="71" t="n">
+      <c r="K40" s="73" t="n">
         <v>78.3</v>
       </c>
-      <c r="L40" s="71" t="n">
+      <c r="L40" s="73" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="M40" s="71" t="n">
+      <c r="M40" s="73" t="n">
         <v>79.2</v>
       </c>
-      <c r="N40" s="72" t="n">
+      <c r="N40" s="74" t="n">
         <v>45.7</v>
       </c>
     </row>
     <row r="41" ht="6" customHeight="1">
-      <c r="A41" s="67" t="inlineStr"/>
-      <c r="B41" s="68" t="n"/>
-      <c r="C41" s="68" t="n"/>
-      <c r="D41" s="68" t="n"/>
-      <c r="E41" s="68" t="n"/>
-      <c r="F41" s="68" t="n"/>
-      <c r="G41" s="68" t="n"/>
-      <c r="H41" s="68" t="n"/>
-      <c r="I41" s="68" t="n"/>
-      <c r="J41" s="68" t="n"/>
-      <c r="K41" s="68" t="n"/>
-      <c r="L41" s="68" t="n"/>
-      <c r="M41" s="68" t="n"/>
-      <c r="N41" s="68" t="n"/>
+      <c r="A41" s="69" t="inlineStr"/>
+      <c r="B41" s="70" t="n"/>
+      <c r="C41" s="70" t="n"/>
+      <c r="D41" s="70" t="n"/>
+      <c r="E41" s="70" t="n"/>
+      <c r="F41" s="70" t="n"/>
+      <c r="G41" s="70" t="n"/>
+      <c r="H41" s="70" t="n"/>
+      <c r="I41" s="70" t="n"/>
+      <c r="J41" s="70" t="n"/>
+      <c r="K41" s="70" t="n"/>
+      <c r="L41" s="70" t="n"/>
+      <c r="M41" s="70" t="n"/>
+      <c r="N41" s="70" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="57" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>【販売管理費】</t>
         </is>
       </c>
-      <c r="B42" s="58" t="n"/>
-      <c r="C42" s="58" t="n"/>
-      <c r="D42" s="58" t="n"/>
-      <c r="E42" s="58" t="n"/>
-      <c r="F42" s="58" t="n"/>
-      <c r="G42" s="58" t="n"/>
-      <c r="H42" s="58" t="n"/>
-      <c r="I42" s="58" t="n"/>
-      <c r="J42" s="58" t="n"/>
-      <c r="K42" s="58" t="n"/>
-      <c r="L42" s="58" t="n"/>
-      <c r="M42" s="58" t="n"/>
-      <c r="N42" s="58" t="n"/>
+      <c r="B42" s="60" t="n"/>
+      <c r="C42" s="60" t="n"/>
+      <c r="D42" s="60" t="n"/>
+      <c r="E42" s="60" t="n"/>
+      <c r="F42" s="60" t="n"/>
+      <c r="G42" s="60" t="n"/>
+      <c r="H42" s="60" t="n"/>
+      <c r="I42" s="60" t="n"/>
+      <c r="J42" s="60" t="n"/>
+      <c r="K42" s="60" t="n"/>
+      <c r="L42" s="60" t="n"/>
+      <c r="M42" s="60" t="n"/>
+      <c r="N42" s="60" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
         </is>
       </c>
-      <c r="B43" s="59" t="n">
+      <c r="B43" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="C43" s="59" t="n">
+      <c r="C43" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="D43" s="59" t="n">
+      <c r="D43" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="E43" s="59" t="n">
+      <c r="E43" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="F43" s="59" t="n">
+      <c r="F43" s="61" t="n">
         <v>120</v>
       </c>
-      <c r="G43" s="59" t="n">
+      <c r="G43" s="61" t="n">
         <v>120</v>
       </c>
-      <c r="H43" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="I43" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="J43" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="K43" s="59" t="n">
+      <c r="H43" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="I43" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="J43" s="61" t="n">
+        <v>150</v>
+      </c>
+      <c r="K43" s="61" t="n">
         <v>200</v>
       </c>
-      <c r="L43" s="59" t="n">
+      <c r="L43" s="61" t="n">
         <v>200</v>
       </c>
-      <c r="M43" s="59" t="n">
+      <c r="M43" s="61" t="n">
         <v>200</v>
       </c>
-      <c r="N43" s="55" t="n">
+      <c r="N43" s="57" t="n">
         <v>1650</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  人件費（バズ社員）</t>
         </is>
       </c>
-      <c r="B44" s="59" t="n">
+      <c r="B44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="C44" s="59" t="n">
+      <c r="C44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="D44" s="59" t="n">
+      <c r="D44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="E44" s="59" t="n">
+      <c r="E44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="F44" s="59" t="n">
+      <c r="F44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="G44" s="59" t="n">
+      <c r="G44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="H44" s="59" t="n">
+      <c r="H44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="I44" s="59" t="n">
+      <c r="I44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="59" t="n">
+      <c r="J44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="K44" s="59" t="n">
+      <c r="K44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="L44" s="59" t="n">
+      <c r="L44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="M44" s="59" t="n">
+      <c r="M44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="N44" s="55" t="n">
+      <c r="N44" s="57" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  その他販管費</t>
         </is>
       </c>
-      <c r="B45" s="59" t="n">
+      <c r="B45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="C45" s="59" t="n">
+      <c r="C45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="D45" s="59" t="n">
+      <c r="D45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="E45" s="59" t="n">
+      <c r="E45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="F45" s="59" t="n">
+      <c r="F45" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="G45" s="59" t="n">
+      <c r="G45" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="H45" s="59" t="n">
+      <c r="H45" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="I45" s="59" t="n">
+      <c r="I45" s="61" t="n">
         <v>70</v>
       </c>
-      <c r="J45" s="59" t="n">
+      <c r="J45" s="61" t="n">
         <v>70</v>
       </c>
-      <c r="K45" s="59" t="n">
+      <c r="K45" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="L45" s="59" t="n">
+      <c r="L45" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="M45" s="59" t="n">
+      <c r="M45" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="N45" s="55" t="n">
+      <c r="N45" s="57" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ENTIAL業務委託費（TIE×5%）</t>
         </is>
       </c>
-      <c r="B46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="59" t="n">
+      <c r="B46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="F46" s="59" t="n">
+      <c r="F46" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="G46" s="59" t="n">
+      <c r="G46" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="H46" s="59" t="n">
+      <c r="H46" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="I46" s="59" t="n">
+      <c r="I46" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="J46" s="59" t="n">
+      <c r="J46" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="K46" s="59" t="n">
+      <c r="K46" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="L46" s="59" t="n">
+      <c r="L46" s="61" t="n">
         <v>38</v>
       </c>
-      <c r="M46" s="59" t="n">
+      <c r="M46" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="N46" s="55" t="n">
+      <c r="N46" s="57" t="n">
         <v>233</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="74" t="inlineStr">
+      <c r="A47" s="76" t="inlineStr">
         <is>
           <t>販売管理費合計</t>
         </is>
       </c>
-      <c r="B47" s="75" t="n">
+      <c r="B47" s="77" t="n">
         <v>230</v>
       </c>
-      <c r="C47" s="75" t="n">
+      <c r="C47" s="77" t="n">
         <v>230</v>
       </c>
-      <c r="D47" s="75" t="n">
+      <c r="D47" s="77" t="n">
         <v>250</v>
       </c>
-      <c r="E47" s="75" t="n">
+      <c r="E47" s="77" t="n">
         <v>258</v>
       </c>
-      <c r="F47" s="75" t="n">
+      <c r="F47" s="77" t="n">
         <v>295</v>
       </c>
-      <c r="G47" s="75" t="n">
+      <c r="G47" s="77" t="n">
         <v>295</v>
       </c>
-      <c r="H47" s="75" t="n">
+      <c r="H47" s="77" t="n">
         <v>332</v>
       </c>
-      <c r="I47" s="75" t="n">
+      <c r="I47" s="77" t="n">
         <v>350</v>
       </c>
-      <c r="J47" s="75" t="n">
+      <c r="J47" s="77" t="n">
         <v>350</v>
       </c>
-      <c r="K47" s="75" t="n">
+      <c r="K47" s="77" t="n">
         <v>410</v>
       </c>
-      <c r="L47" s="75" t="n">
+      <c r="L47" s="77" t="n">
         <v>418</v>
       </c>
-      <c r="M47" s="75" t="n">
+      <c r="M47" s="77" t="n">
         <v>425</v>
       </c>
-      <c r="N47" s="75" t="n">
+      <c r="N47" s="77" t="n">
         <v>3843</v>
       </c>
     </row>
     <row r="48" ht="6" customHeight="1">
-      <c r="A48" s="67" t="inlineStr"/>
-      <c r="B48" s="68" t="n"/>
-      <c r="C48" s="68" t="n"/>
-      <c r="D48" s="68" t="n"/>
-      <c r="E48" s="68" t="n"/>
-      <c r="F48" s="68" t="n"/>
-      <c r="G48" s="68" t="n"/>
-      <c r="H48" s="68" t="n"/>
-      <c r="I48" s="68" t="n"/>
-      <c r="J48" s="68" t="n"/>
-      <c r="K48" s="68" t="n"/>
-      <c r="L48" s="68" t="n"/>
-      <c r="M48" s="68" t="n"/>
-      <c r="N48" s="68" t="n"/>
+      <c r="A48" s="69" t="inlineStr"/>
+      <c r="B48" s="70" t="n"/>
+      <c r="C48" s="70" t="n"/>
+      <c r="D48" s="70" t="n"/>
+      <c r="E48" s="70" t="n"/>
+      <c r="F48" s="70" t="n"/>
+      <c r="G48" s="70" t="n"/>
+      <c r="H48" s="70" t="n"/>
+      <c r="I48" s="70" t="n"/>
+      <c r="J48" s="70" t="n"/>
+      <c r="K48" s="70" t="n"/>
+      <c r="L48" s="70" t="n"/>
+      <c r="M48" s="70" t="n"/>
+      <c r="N48" s="70" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="56" t="inlineStr">
+      <c r="A49" s="58" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="B49" s="79" t="n">
+      <c r="B49" s="81" t="n">
         <v>-240</v>
       </c>
-      <c r="C49" s="79" t="n">
+      <c r="C49" s="81" t="n">
         <v>-240</v>
       </c>
-      <c r="D49" s="79" t="n">
+      <c r="D49" s="81" t="n">
         <v>-257</v>
       </c>
-      <c r="E49" s="79" t="n">
+      <c r="E49" s="81" t="n">
         <v>-141</v>
       </c>
-      <c r="F49" s="79" t="n">
+      <c r="F49" s="81" t="n">
         <v>-61</v>
       </c>
-      <c r="G49" s="79" t="n">
+      <c r="G49" s="81" t="n">
         <v>-47</v>
       </c>
-      <c r="H49" s="80" t="n">
+      <c r="H49" s="82" t="n">
         <v>46</v>
       </c>
-      <c r="I49" s="81" t="n">
+      <c r="I49" s="83" t="n">
         <v>162</v>
       </c>
-      <c r="J49" s="81" t="n">
+      <c r="J49" s="83" t="n">
         <v>194</v>
       </c>
-      <c r="K49" s="81" t="n">
+      <c r="K49" s="83" t="n">
         <v>166</v>
       </c>
-      <c r="L49" s="81" t="n">
+      <c r="L49" s="83" t="n">
         <v>328</v>
       </c>
-      <c r="M49" s="81" t="n">
+      <c r="M49" s="83" t="n">
         <v>487</v>
       </c>
-      <c r="N49" s="80" t="n">
+      <c r="N49" s="82" t="n">
         <v>397</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="70" t="inlineStr">
+      <c r="A50" s="72" t="inlineStr">
         <is>
           <t>営業利益率</t>
         </is>
       </c>
-      <c r="B50" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="71" t="n">
+      <c r="B50" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="73" t="n">
         <v>-8566.700000000001</v>
       </c>
-      <c r="E50" s="71" t="n">
+      <c r="E50" s="73" t="n">
         <v>-89.8</v>
       </c>
-      <c r="F50" s="71" t="n">
+      <c r="F50" s="73" t="n">
         <v>-19.4</v>
       </c>
-      <c r="G50" s="71" t="n">
+      <c r="G50" s="73" t="n">
         <v>-14.3</v>
       </c>
-      <c r="H50" s="71" t="n">
+      <c r="H50" s="73" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="I50" s="71" t="n">
+      <c r="I50" s="73" t="n">
         <v>24.1</v>
       </c>
-      <c r="J50" s="71" t="n">
+      <c r="J50" s="73" t="n">
         <v>27.6</v>
       </c>
-      <c r="K50" s="71" t="n">
+      <c r="K50" s="73" t="n">
         <v>22.6</v>
       </c>
-      <c r="L50" s="71" t="n">
+      <c r="L50" s="73" t="n">
         <v>34.7</v>
       </c>
-      <c r="M50" s="71" t="n">
+      <c r="M50" s="73" t="n">
         <v>42.3</v>
       </c>
-      <c r="N50" s="72" t="n">
+      <c r="N50" s="74" t="n">
         <v>-853</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="82" t="inlineStr">
+      <c r="A51" s="84" t="inlineStr">
         <is>
           <t>★ 損益分岐：M7　／　Year1通期営業利益：397万円　／　Year1売上：5,510万円</t>
         </is>
@@ -6077,7 +6095,7 @@
       <c r="N51" s="2" t="n"/>
     </row>
     <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="83" t="inlineStr">
+      <c r="A52" s="85" t="inlineStr">
         <is>
           <t>【注記】単位：万円 ／ ギャル協会：出演・監修料=件数×25万（最低保証10万）、EC物販はギャル協会がショップオーナー（バズに原価なし） ／ バズEC収益=アフィリエイトコミッション（EC実売上×20%） ／ 制作費：TIE×10% ／ ENTIAL：TIE成功報酬×5%（EC運用除外）</t>
         </is>
@@ -6135,86 +6153,86 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="85" t="inlineStr">
+      <c r="A1" s="87" t="inlineStr">
         <is>
           <t>❸ 撤退パターン  ／  Year1 月次事業計画（バズ社PL）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>Year1でバズ売上715万・営業損失2,435万・M9末で撤退決定　単位：万円</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="F3" s="33" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="G3" s="33" t="inlineStr">
+      <c r="G3" s="35" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="H3" s="33" t="inlineStr">
+      <c r="H3" s="35" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="I3" s="33" t="inlineStr">
+      <c r="I3" s="35" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="J3" s="33" t="inlineStr">
+      <c r="J3" s="35" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="K3" s="33" t="inlineStr">
+      <c r="K3" s="35" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="L3" s="33" t="inlineStr">
+      <c r="L3" s="35" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="M3" s="33" t="inlineStr">
+      <c r="M3" s="35" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="N3" s="33" t="inlineStr">
+      <c r="N3" s="35" t="inlineStr">
         <is>
           <t>Year1合計</t>
         </is>
@@ -6241,455 +6259,455 @@
       <c r="N4" s="2" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>TikTokフォロワー数（累計）</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="51" t="n">
         <v>200</v>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="51" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="51" t="n">
         <v>1500</v>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="51" t="n">
         <v>2000</v>
       </c>
-      <c r="G5" s="49" t="n">
+      <c r="G5" s="51" t="n">
         <v>2800</v>
       </c>
-      <c r="H5" s="49" t="n">
+      <c r="H5" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="I5" s="49" t="n">
+      <c r="I5" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="J5" s="49" t="n">
+      <c r="J5" s="51" t="n">
         <v>4500</v>
       </c>
-      <c r="K5" s="49" t="n">
+      <c r="K5" s="51" t="n">
         <v>4800</v>
       </c>
-      <c r="L5" s="49" t="n">
+      <c r="L5" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="M5" s="49" t="n">
+      <c r="M5" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="N5" s="49" t="n">
+      <c r="N5" s="51" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>IGフォロワー数（累計）</t>
         </is>
       </c>
-      <c r="B6" s="51" t="n">
+      <c r="B6" s="53" t="n">
         <v>100</v>
       </c>
-      <c r="C6" s="51" t="n">
+      <c r="C6" s="53" t="n">
         <v>300</v>
       </c>
-      <c r="D6" s="51" t="n">
+      <c r="D6" s="53" t="n">
         <v>600</v>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="53" t="n">
         <v>900</v>
       </c>
-      <c r="F6" s="51" t="n">
+      <c r="F6" s="53" t="n">
         <v>1200</v>
       </c>
-      <c r="G6" s="51" t="n">
+      <c r="G6" s="53" t="n">
         <v>1600</v>
       </c>
-      <c r="H6" s="51" t="n">
+      <c r="H6" s="53" t="n">
         <v>2000</v>
       </c>
-      <c r="I6" s="51" t="n">
+      <c r="I6" s="53" t="n">
         <v>2300</v>
       </c>
-      <c r="J6" s="51" t="n">
+      <c r="J6" s="53" t="n">
         <v>2500</v>
       </c>
-      <c r="K6" s="51" t="n">
+      <c r="K6" s="53" t="n">
         <v>2700</v>
       </c>
-      <c r="L6" s="51" t="n">
+      <c r="L6" s="53" t="n">
         <v>2800</v>
       </c>
-      <c r="M6" s="51" t="n">
+      <c r="M6" s="53" t="n">
         <v>2800</v>
       </c>
-      <c r="N6" s="51" t="n">
+      <c r="N6" s="53" t="n">
         <v>2800</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>TKタイアップ受注社数（月次）</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="49" t="n">
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="49" t="n">
+      <c r="G7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="49" t="n">
+      <c r="I7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M7" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="49" t="n">
+      <c r="L7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="51" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>TKタイアップ平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="54" t="n">
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="56" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="54" t="n">
+      <c r="G8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="56" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="54" t="n">
+      <c r="I8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="56" t="n">
         <v>100</v>
       </c>
-      <c r="K8" s="54" t="n">
+      <c r="K8" s="56" t="n">
         <v>100</v>
       </c>
-      <c r="L8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="55" t="n">
+      <c r="L8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="57" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>IGタイアップ受注社数（月次）</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="49" t="n">
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="49" t="n">
+      <c r="H9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M9" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="49" t="n">
+      <c r="K9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="51" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>IGタイアップ平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="54" t="n">
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="56" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="54" t="n">
+      <c r="H10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="56" t="n">
         <v>100</v>
       </c>
-      <c r="K10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M10" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="55" t="n">
+      <c r="K10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="57" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>EC注文件数（TikTok Shop）</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="49" t="n">
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="51" t="n">
         <v>20</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="51" t="n">
         <v>40</v>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="51" t="n">
         <v>80</v>
       </c>
-      <c r="H11" s="49" t="n">
+      <c r="H11" s="51" t="n">
         <v>100</v>
       </c>
-      <c r="I11" s="49" t="n">
+      <c r="I11" s="51" t="n">
         <v>130</v>
       </c>
-      <c r="J11" s="49" t="n">
-        <v>150</v>
-      </c>
-      <c r="K11" s="49" t="n">
+      <c r="J11" s="51" t="n">
+        <v>150</v>
+      </c>
+      <c r="K11" s="51" t="n">
         <v>180</v>
       </c>
-      <c r="L11" s="49" t="n">
+      <c r="L11" s="51" t="n">
         <v>200</v>
       </c>
-      <c r="M11" s="49" t="n">
+      <c r="M11" s="51" t="n">
         <v>250</v>
       </c>
-      <c r="N11" s="49" t="n">
+      <c r="N11" s="51" t="n">
         <v>1160</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>EC平均注文単価（円）</t>
         </is>
       </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="54" t="n">
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="n">
         <v>4000</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="56" t="n">
         <v>4000</v>
       </c>
-      <c r="F12" s="54" t="n">
+      <c r="F12" s="56" t="n">
         <v>4500</v>
       </c>
-      <c r="G12" s="54" t="n">
+      <c r="G12" s="56" t="n">
         <v>4500</v>
       </c>
-      <c r="H12" s="54" t="n">
+      <c r="H12" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="I12" s="54" t="n">
+      <c r="I12" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="J12" s="54" t="n">
+      <c r="J12" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="K12" s="54" t="n">
+      <c r="K12" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="L12" s="54" t="n">
+      <c r="L12" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="M12" s="54" t="n">
+      <c r="M12" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="N12" s="55" t="n">
+      <c r="N12" s="57" t="n">
         <v>4700</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="56" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>▌ 損益計算書（P/L）　単位：万円</t>
         </is>
@@ -6709,612 +6727,612 @@
       <c r="N13" s="2" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>【売上高】</t>
         </is>
       </c>
-      <c r="B14" s="58" t="n"/>
-      <c r="C14" s="58" t="n"/>
-      <c r="D14" s="58" t="n"/>
-      <c r="E14" s="58" t="n"/>
-      <c r="F14" s="58" t="n"/>
-      <c r="G14" s="58" t="n"/>
-      <c r="H14" s="58" t="n"/>
-      <c r="I14" s="58" t="n"/>
-      <c r="J14" s="58" t="n"/>
-      <c r="K14" s="58" t="n"/>
-      <c r="L14" s="58" t="n"/>
-      <c r="M14" s="58" t="n"/>
-      <c r="N14" s="58" t="n"/>
+      <c r="B14" s="60" t="n"/>
+      <c r="C14" s="60" t="n"/>
+      <c r="D14" s="60" t="n"/>
+      <c r="E14" s="60" t="n"/>
+      <c r="F14" s="60" t="n"/>
+      <c r="G14" s="60" t="n"/>
+      <c r="H14" s="60" t="n"/>
+      <c r="I14" s="60" t="n"/>
+      <c r="J14" s="60" t="n"/>
+      <c r="K14" s="60" t="n"/>
+      <c r="L14" s="60" t="n"/>
+      <c r="M14" s="60" t="n"/>
+      <c r="N14" s="60" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ① TikTokメディアタイアップ</t>
         </is>
       </c>
-      <c r="B15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="59" t="n">
+      <c r="B15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="G15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="59" t="n">
+      <c r="G15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="I15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="59" t="n">
+      <c r="I15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="K15" s="59" t="n">
+      <c r="K15" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="L15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="55" t="n">
+      <c r="L15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="57" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     受注社数（社）</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="62" t="n">
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="62" t="n">
+      <c r="G16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="62" t="n">
+      <c r="I16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="62" t="n">
+      <c r="K16" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="L16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="63" t="n">
+      <c r="L16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="65" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="62" t="n">
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="64" t="n">
         <v>100</v>
       </c>
-      <c r="G17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="62" t="n">
+      <c r="G17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="64" t="n">
         <v>100</v>
       </c>
-      <c r="I17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="62" t="n">
+      <c r="I17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="64" t="n">
         <v>100</v>
       </c>
-      <c r="K17" s="62" t="n">
+      <c r="K17" s="64" t="n">
         <v>100</v>
       </c>
-      <c r="L17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M17" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="63" t="n">
+      <c r="L17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="65" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ② IGメディアタイアップ</t>
         </is>
       </c>
-      <c r="B18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="59" t="n">
+      <c r="B18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="H18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="59" t="n">
+      <c r="H18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="K18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="55" t="n">
+      <c r="K18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="57" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     受注社数（社）</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="62" t="n">
+      <c r="B19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="62" t="n">
+      <c r="H19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M19" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="63" t="n">
+      <c r="K19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="65" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     平均単価（万円/社）</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="62" t="n">
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="64" t="n">
         <v>100</v>
       </c>
-      <c r="H20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="62" t="n">
+      <c r="H20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="64" t="n">
         <v>100</v>
       </c>
-      <c r="K20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="63" t="n">
+      <c r="K20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="65" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="64" t="inlineStr">
+      <c r="A21" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">  タイアップ売上合計</t>
         </is>
       </c>
-      <c r="B21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="65" t="n">
+      <c r="B21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="67" t="n">
         <v>100</v>
       </c>
-      <c r="G21" s="65" t="n">
+      <c r="G21" s="67" t="n">
         <v>100</v>
       </c>
-      <c r="H21" s="65" t="n">
+      <c r="H21" s="67" t="n">
         <v>100</v>
       </c>
-      <c r="I21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="65" t="n">
+      <c r="I21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="67" t="n">
         <v>200</v>
       </c>
-      <c r="K21" s="65" t="n">
+      <c r="K21" s="67" t="n">
         <v>100</v>
       </c>
-      <c r="L21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="65" t="n">
+      <c r="L21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="67" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ③ ECアフィリエイトコミッション（×20%）</t>
         </is>
       </c>
-      <c r="B22" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="59" t="n">
+      <c r="B22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="59" t="n">
+      <c r="E22" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="59" t="n">
+      <c r="F22" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="59" t="n">
+      <c r="G22" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="H22" s="59" t="n">
+      <c r="H22" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="I22" s="59" t="n">
+      <c r="I22" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="J22" s="59" t="n">
+      <c r="J22" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="K22" s="59" t="n">
+      <c r="K22" s="61" t="n">
         <v>18</v>
       </c>
-      <c r="L22" s="59" t="n">
+      <c r="L22" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="M22" s="59" t="n">
+      <c r="M22" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="N22" s="55" t="n">
+      <c r="N22" s="57" t="n">
         <v>115</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     EC実売上（ギャル協会側・参考値）</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="62" t="n">
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="62" t="n">
+      <c r="E23" s="64" t="n">
         <v>8</v>
       </c>
-      <c r="F23" s="62" t="n">
+      <c r="F23" s="64" t="n">
         <v>18</v>
       </c>
-      <c r="G23" s="62" t="n">
+      <c r="G23" s="64" t="n">
         <v>36</v>
       </c>
-      <c r="H23" s="62" t="n">
+      <c r="H23" s="64" t="n">
         <v>50</v>
       </c>
-      <c r="I23" s="62" t="n">
+      <c r="I23" s="64" t="n">
         <v>65</v>
       </c>
-      <c r="J23" s="62" t="n">
+      <c r="J23" s="64" t="n">
         <v>75</v>
       </c>
-      <c r="K23" s="62" t="n">
+      <c r="K23" s="64" t="n">
         <v>90</v>
       </c>
-      <c r="L23" s="62" t="n">
+      <c r="L23" s="64" t="n">
         <v>100</v>
       </c>
-      <c r="M23" s="62" t="n">
+      <c r="M23" s="64" t="n">
         <v>125</v>
       </c>
-      <c r="N23" s="63" t="n">
+      <c r="N23" s="65" t="n">
         <v>571</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     注文件数（件）</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="62" t="n">
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="64" t="n">
         <v>10</v>
       </c>
-      <c r="E24" s="62" t="n">
+      <c r="E24" s="64" t="n">
         <v>20</v>
       </c>
-      <c r="F24" s="62" t="n">
+      <c r="F24" s="64" t="n">
         <v>40</v>
       </c>
-      <c r="G24" s="62" t="n">
+      <c r="G24" s="64" t="n">
         <v>80</v>
       </c>
-      <c r="H24" s="62" t="n">
+      <c r="H24" s="64" t="n">
         <v>100</v>
       </c>
-      <c r="I24" s="62" t="n">
+      <c r="I24" s="64" t="n">
         <v>130</v>
       </c>
-      <c r="J24" s="62" t="n">
-        <v>150</v>
-      </c>
-      <c r="K24" s="62" t="n">
+      <c r="J24" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="K24" s="64" t="n">
         <v>180</v>
       </c>
-      <c r="L24" s="62" t="n">
+      <c r="L24" s="64" t="n">
         <v>200</v>
       </c>
-      <c r="M24" s="62" t="n">
+      <c r="M24" s="64" t="n">
         <v>250</v>
       </c>
-      <c r="N24" s="63" t="n">
+      <c r="N24" s="65" t="n">
         <v>1160</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="60" t="inlineStr">
+      <c r="A25" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     平均注文単価（円）</t>
         </is>
       </c>
-      <c r="B25" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="62" t="n">
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="64" t="n">
         <v>4000</v>
       </c>
-      <c r="E25" s="62" t="n">
+      <c r="E25" s="64" t="n">
         <v>4000</v>
       </c>
-      <c r="F25" s="62" t="n">
+      <c r="F25" s="64" t="n">
         <v>4500</v>
       </c>
-      <c r="G25" s="62" t="n">
+      <c r="G25" s="64" t="n">
         <v>4500</v>
       </c>
-      <c r="H25" s="62" t="n">
+      <c r="H25" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="I25" s="62" t="n">
+      <c r="I25" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="J25" s="62" t="n">
+      <c r="J25" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="K25" s="62" t="n">
+      <c r="K25" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="L25" s="62" t="n">
+      <c r="L25" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="M25" s="62" t="n">
+      <c r="M25" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="N25" s="63" t="n">
+      <c r="N25" s="65" t="n">
         <v>4700</v>
       </c>
     </row>
@@ -7324,277 +7342,277 @@
           <t>売上合計</t>
         </is>
       </c>
-      <c r="B26" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="66" t="n">
+      <c r="B26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="66" t="n">
+      <c r="E26" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="66" t="n">
+      <c r="F26" s="68" t="n">
         <v>104</v>
       </c>
-      <c r="G26" s="66" t="n">
+      <c r="G26" s="68" t="n">
         <v>107</v>
       </c>
-      <c r="H26" s="66" t="n">
+      <c r="H26" s="68" t="n">
         <v>110</v>
       </c>
-      <c r="I26" s="66" t="n">
+      <c r="I26" s="68" t="n">
         <v>13</v>
       </c>
-      <c r="J26" s="66" t="n">
+      <c r="J26" s="68" t="n">
         <v>215</v>
       </c>
-      <c r="K26" s="66" t="n">
+      <c r="K26" s="68" t="n">
         <v>118</v>
       </c>
-      <c r="L26" s="66" t="n">
+      <c r="L26" s="68" t="n">
         <v>20</v>
       </c>
-      <c r="M26" s="66" t="n">
+      <c r="M26" s="68" t="n">
         <v>25</v>
       </c>
-      <c r="N26" s="66" t="n">
+      <c r="N26" s="68" t="n">
         <v>715</v>
       </c>
     </row>
     <row r="27" ht="6" customHeight="1">
-      <c r="A27" s="67" t="inlineStr"/>
-      <c r="B27" s="68" t="n"/>
-      <c r="C27" s="68" t="n"/>
-      <c r="D27" s="68" t="n"/>
-      <c r="E27" s="68" t="n"/>
-      <c r="F27" s="68" t="n"/>
-      <c r="G27" s="68" t="n"/>
-      <c r="H27" s="68" t="n"/>
-      <c r="I27" s="68" t="n"/>
-      <c r="J27" s="68" t="n"/>
-      <c r="K27" s="68" t="n"/>
-      <c r="L27" s="68" t="n"/>
-      <c r="M27" s="68" t="n"/>
-      <c r="N27" s="68" t="n"/>
+      <c r="A27" s="69" t="inlineStr"/>
+      <c r="B27" s="70" t="n"/>
+      <c r="C27" s="70" t="n"/>
+      <c r="D27" s="70" t="n"/>
+      <c r="E27" s="70" t="n"/>
+      <c r="F27" s="70" t="n"/>
+      <c r="G27" s="70" t="n"/>
+      <c r="H27" s="70" t="n"/>
+      <c r="I27" s="70" t="n"/>
+      <c r="J27" s="70" t="n"/>
+      <c r="K27" s="70" t="n"/>
+      <c r="L27" s="70" t="n"/>
+      <c r="M27" s="70" t="n"/>
+      <c r="N27" s="70" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="57" t="inlineStr">
+      <c r="A28" s="59" t="inlineStr">
         <is>
           <t>【タイアップ原価】</t>
         </is>
       </c>
-      <c r="B28" s="58" t="n"/>
-      <c r="C28" s="58" t="n"/>
-      <c r="D28" s="58" t="n"/>
-      <c r="E28" s="58" t="n"/>
-      <c r="F28" s="58" t="n"/>
-      <c r="G28" s="58" t="n"/>
-      <c r="H28" s="58" t="n"/>
-      <c r="I28" s="58" t="n"/>
-      <c r="J28" s="58" t="n"/>
-      <c r="K28" s="58" t="n"/>
-      <c r="L28" s="58" t="n"/>
-      <c r="M28" s="58" t="n"/>
-      <c r="N28" s="58" t="n"/>
+      <c r="B28" s="60" t="n"/>
+      <c r="C28" s="60" t="n"/>
+      <c r="D28" s="60" t="n"/>
+      <c r="E28" s="60" t="n"/>
+      <c r="F28" s="60" t="n"/>
+      <c r="G28" s="60" t="n"/>
+      <c r="H28" s="60" t="n"/>
+      <c r="I28" s="60" t="n"/>
+      <c r="J28" s="60" t="n"/>
+      <c r="K28" s="60" t="n"/>
+      <c r="L28" s="60" t="n"/>
+      <c r="M28" s="60" t="n"/>
+      <c r="N28" s="60" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ギャル協会出演・監修料（件数×25万・最低保証10万）</t>
         </is>
       </c>
-      <c r="B29" s="59" t="n">
+      <c r="B29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="C29" s="59" t="n">
+      <c r="C29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="59" t="n">
+      <c r="D29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="E29" s="59" t="n">
+      <c r="E29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="F29" s="59" t="n">
+      <c r="F29" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="G29" s="59" t="n">
+      <c r="G29" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="H29" s="59" t="n">
+      <c r="H29" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="I29" s="59" t="n">
+      <c r="I29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="J29" s="59" t="n">
+      <c r="J29" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="K29" s="59" t="n">
+      <c r="K29" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="L29" s="59" t="n">
+      <c r="L29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="M29" s="59" t="n">
+      <c r="M29" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="N29" s="55" t="n">
+      <c r="N29" s="57" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">     タイアップ件数（社）</t>
         </is>
       </c>
-      <c r="B30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="62" t="n">
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="62" t="n">
+      <c r="G30" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="62" t="n">
+      <c r="H30" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="62" t="n">
+      <c r="I30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="K30" s="62" t="n">
+      <c r="K30" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M30" s="61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="63" t="n">
+      <c r="L30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="65" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  コンテンツ制作費（×10%）</t>
         </is>
       </c>
-      <c r="B31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="59" t="n">
+      <c r="B31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="G31" s="59" t="n">
+      <c r="G31" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="H31" s="59" t="n">
+      <c r="H31" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="I31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="59" t="n">
+      <c r="I31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="K31" s="59" t="n">
+      <c r="K31" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="L31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="55" t="n">
+      <c r="L31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="57" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="64" t="inlineStr">
+      <c r="A32" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">  タイアップ原価合計</t>
         </is>
       </c>
-      <c r="B32" s="65" t="n">
+      <c r="B32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="C32" s="65" t="n">
+      <c r="C32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="65" t="n">
+      <c r="D32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="E32" s="65" t="n">
+      <c r="E32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="F32" s="65" t="n">
+      <c r="F32" s="67" t="n">
         <v>35</v>
       </c>
-      <c r="G32" s="65" t="n">
+      <c r="G32" s="67" t="n">
         <v>35</v>
       </c>
-      <c r="H32" s="65" t="n">
+      <c r="H32" s="67" t="n">
         <v>35</v>
       </c>
-      <c r="I32" s="65" t="n">
+      <c r="I32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="J32" s="65" t="n">
+      <c r="J32" s="67" t="n">
         <v>70</v>
       </c>
-      <c r="K32" s="65" t="n">
+      <c r="K32" s="67" t="n">
         <v>35</v>
       </c>
-      <c r="L32" s="65" t="n">
+      <c r="L32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="M32" s="65" t="n">
+      <c r="M32" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="N32" s="65" t="n">
+      <c r="N32" s="67" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7604,658 +7622,658 @@
           <t xml:space="preserve">  タイアップ粗利</t>
         </is>
       </c>
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="C33" s="31" t="n">
+      <c r="C33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="D33" s="31" t="n">
+      <c r="D33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="E33" s="31" t="n">
+      <c r="E33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="F33" s="69" t="n">
+      <c r="F33" s="71" t="n">
         <v>65</v>
       </c>
-      <c r="G33" s="69" t="n">
+      <c r="G33" s="71" t="n">
         <v>65</v>
       </c>
-      <c r="H33" s="69" t="n">
+      <c r="H33" s="71" t="n">
         <v>65</v>
       </c>
-      <c r="I33" s="31" t="n">
+      <c r="I33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="J33" s="69" t="n">
+      <c r="J33" s="71" t="n">
         <v>130</v>
       </c>
-      <c r="K33" s="69" t="n">
+      <c r="K33" s="71" t="n">
         <v>65</v>
       </c>
-      <c r="L33" s="31" t="n">
+      <c r="L33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="M33" s="31" t="n">
+      <c r="M33" s="33" t="n">
         <v>-10</v>
       </c>
-      <c r="N33" s="69" t="n">
+      <c r="N33" s="71" t="n">
         <v>320</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="70" t="inlineStr">
+      <c r="A34" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">  タイアップ粗利率</t>
         </is>
       </c>
-      <c r="B34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="71" t="n">
+      <c r="B34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="73" t="n">
         <v>65</v>
       </c>
-      <c r="G34" s="71" t="n">
+      <c r="G34" s="73" t="n">
         <v>65</v>
       </c>
-      <c r="H34" s="71" t="n">
+      <c r="H34" s="73" t="n">
         <v>65</v>
       </c>
-      <c r="I34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="71" t="n">
+      <c r="I34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="73" t="n">
         <v>65</v>
       </c>
-      <c r="K34" s="71" t="n">
+      <c r="K34" s="73" t="n">
         <v>65</v>
       </c>
-      <c r="L34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="72" t="n">
+      <c r="L34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="74" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="35" ht="6" customHeight="1">
-      <c r="A35" s="67" t="inlineStr"/>
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="68" t="n"/>
-      <c r="D35" s="68" t="n"/>
-      <c r="E35" s="68" t="n"/>
-      <c r="F35" s="68" t="n"/>
-      <c r="G35" s="68" t="n"/>
-      <c r="H35" s="68" t="n"/>
-      <c r="I35" s="68" t="n"/>
-      <c r="J35" s="68" t="n"/>
-      <c r="K35" s="68" t="n"/>
-      <c r="L35" s="68" t="n"/>
-      <c r="M35" s="68" t="n"/>
-      <c r="N35" s="68" t="n"/>
+      <c r="A35" s="69" t="inlineStr"/>
+      <c r="B35" s="70" t="n"/>
+      <c r="C35" s="70" t="n"/>
+      <c r="D35" s="70" t="n"/>
+      <c r="E35" s="70" t="n"/>
+      <c r="F35" s="70" t="n"/>
+      <c r="G35" s="70" t="n"/>
+      <c r="H35" s="70" t="n"/>
+      <c r="I35" s="70" t="n"/>
+      <c r="J35" s="70" t="n"/>
+      <c r="K35" s="70" t="n"/>
+      <c r="L35" s="70" t="n"/>
+      <c r="M35" s="70" t="n"/>
+      <c r="N35" s="70" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  ※ECコミッション（原価ゼロ）→ ギャル協会がショップオーナー</t>
         </is>
       </c>
-      <c r="B36" s="73" t="n"/>
-      <c r="C36" s="73" t="n"/>
-      <c r="D36" s="73" t="n"/>
-      <c r="E36" s="73" t="n"/>
-      <c r="F36" s="73" t="n"/>
-      <c r="G36" s="73" t="n"/>
-      <c r="H36" s="73" t="n"/>
-      <c r="I36" s="73" t="n"/>
-      <c r="J36" s="73" t="n"/>
-      <c r="K36" s="73" t="n"/>
-      <c r="L36" s="73" t="n"/>
-      <c r="M36" s="73" t="n"/>
-      <c r="N36" s="73" t="n"/>
+      <c r="B36" s="75" t="n"/>
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="75" t="n"/>
+      <c r="E36" s="75" t="n"/>
+      <c r="F36" s="75" t="n"/>
+      <c r="G36" s="75" t="n"/>
+      <c r="H36" s="75" t="n"/>
+      <c r="I36" s="75" t="n"/>
+      <c r="J36" s="75" t="n"/>
+      <c r="K36" s="75" t="n"/>
+      <c r="L36" s="75" t="n"/>
+      <c r="M36" s="75" t="n"/>
+      <c r="N36" s="75" t="n"/>
     </row>
     <row r="37" ht="6" customHeight="1">
-      <c r="A37" s="67" t="inlineStr"/>
-      <c r="B37" s="68" t="n"/>
-      <c r="C37" s="68" t="n"/>
-      <c r="D37" s="68" t="n"/>
-      <c r="E37" s="68" t="n"/>
-      <c r="F37" s="68" t="n"/>
-      <c r="G37" s="68" t="n"/>
-      <c r="H37" s="68" t="n"/>
-      <c r="I37" s="68" t="n"/>
-      <c r="J37" s="68" t="n"/>
-      <c r="K37" s="68" t="n"/>
-      <c r="L37" s="68" t="n"/>
-      <c r="M37" s="68" t="n"/>
-      <c r="N37" s="68" t="n"/>
+      <c r="A37" s="69" t="inlineStr"/>
+      <c r="B37" s="70" t="n"/>
+      <c r="C37" s="70" t="n"/>
+      <c r="D37" s="70" t="n"/>
+      <c r="E37" s="70" t="n"/>
+      <c r="F37" s="70" t="n"/>
+      <c r="G37" s="70" t="n"/>
+      <c r="H37" s="70" t="n"/>
+      <c r="I37" s="70" t="n"/>
+      <c r="J37" s="70" t="n"/>
+      <c r="K37" s="70" t="n"/>
+      <c r="L37" s="70" t="n"/>
+      <c r="M37" s="70" t="n"/>
+      <c r="N37" s="70" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="74" t="inlineStr">
+      <c r="A38" s="76" t="inlineStr">
         <is>
           <t>売上原価合計</t>
         </is>
       </c>
-      <c r="B38" s="75" t="n">
+      <c r="B38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="C38" s="75" t="n">
+      <c r="C38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="75" t="n">
+      <c r="D38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="E38" s="75" t="n">
+      <c r="E38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="F38" s="75" t="n">
+      <c r="F38" s="77" t="n">
         <v>35</v>
       </c>
-      <c r="G38" s="75" t="n">
+      <c r="G38" s="77" t="n">
         <v>35</v>
       </c>
-      <c r="H38" s="75" t="n">
+      <c r="H38" s="77" t="n">
         <v>35</v>
       </c>
-      <c r="I38" s="75" t="n">
+      <c r="I38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="J38" s="75" t="n">
+      <c r="J38" s="77" t="n">
         <v>70</v>
       </c>
-      <c r="K38" s="75" t="n">
+      <c r="K38" s="77" t="n">
         <v>35</v>
       </c>
-      <c r="L38" s="75" t="n">
+      <c r="L38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="M38" s="75" t="n">
+      <c r="M38" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="N38" s="75" t="n">
+      <c r="N38" s="77" t="n">
         <v>280</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="76" t="inlineStr">
+      <c r="A39" s="78" t="inlineStr">
         <is>
           <t>粗利益合計</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n">
+      <c r="B39" s="79" t="n">
         <v>-10</v>
       </c>
-      <c r="C39" s="77" t="n">
+      <c r="C39" s="79" t="n">
         <v>-10</v>
       </c>
-      <c r="D39" s="77" t="n">
+      <c r="D39" s="79" t="n">
         <v>-9</v>
       </c>
-      <c r="E39" s="77" t="n">
+      <c r="E39" s="79" t="n">
         <v>-8</v>
       </c>
-      <c r="F39" s="78" t="n">
+      <c r="F39" s="80" t="n">
         <v>69</v>
       </c>
-      <c r="G39" s="78" t="n">
+      <c r="G39" s="80" t="n">
         <v>72</v>
       </c>
-      <c r="H39" s="78" t="n">
+      <c r="H39" s="80" t="n">
         <v>75</v>
       </c>
-      <c r="I39" s="78" t="n">
+      <c r="I39" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="J39" s="78" t="n">
+      <c r="J39" s="80" t="n">
         <v>145</v>
       </c>
-      <c r="K39" s="78" t="n">
+      <c r="K39" s="80" t="n">
         <v>83</v>
       </c>
-      <c r="L39" s="78" t="n">
+      <c r="L39" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="M39" s="78" t="n">
+      <c r="M39" s="80" t="n">
         <v>15</v>
       </c>
-      <c r="N39" s="78" t="n">
+      <c r="N39" s="80" t="n">
         <v>435</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="70" t="inlineStr">
+      <c r="A40" s="72" t="inlineStr">
         <is>
           <t>粗利率（合計）</t>
         </is>
       </c>
-      <c r="B40" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="71" t="n">
+      <c r="B40" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="73" t="n">
         <v>-900</v>
       </c>
-      <c r="E40" s="71" t="n">
+      <c r="E40" s="73" t="n">
         <v>-400</v>
       </c>
-      <c r="F40" s="71" t="n">
+      <c r="F40" s="73" t="n">
         <v>66.3</v>
       </c>
-      <c r="G40" s="71" t="n">
+      <c r="G40" s="73" t="n">
         <v>67.3</v>
       </c>
-      <c r="H40" s="71" t="n">
+      <c r="H40" s="73" t="n">
         <v>68.2</v>
       </c>
-      <c r="I40" s="71" t="n">
+      <c r="I40" s="73" t="n">
         <v>23.1</v>
       </c>
-      <c r="J40" s="71" t="n">
+      <c r="J40" s="73" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="K40" s="71" t="n">
+      <c r="K40" s="73" t="n">
         <v>70.3</v>
       </c>
-      <c r="L40" s="71" t="n">
+      <c r="L40" s="73" t="n">
         <v>50</v>
       </c>
-      <c r="M40" s="71" t="n">
+      <c r="M40" s="73" t="n">
         <v>60</v>
       </c>
-      <c r="N40" s="72" t="n">
+      <c r="N40" s="74" t="n">
         <v>-82.7</v>
       </c>
     </row>
     <row r="41" ht="6" customHeight="1">
-      <c r="A41" s="67" t="inlineStr"/>
-      <c r="B41" s="68" t="n"/>
-      <c r="C41" s="68" t="n"/>
-      <c r="D41" s="68" t="n"/>
-      <c r="E41" s="68" t="n"/>
-      <c r="F41" s="68" t="n"/>
-      <c r="G41" s="68" t="n"/>
-      <c r="H41" s="68" t="n"/>
-      <c r="I41" s="68" t="n"/>
-      <c r="J41" s="68" t="n"/>
-      <c r="K41" s="68" t="n"/>
-      <c r="L41" s="68" t="n"/>
-      <c r="M41" s="68" t="n"/>
-      <c r="N41" s="68" t="n"/>
+      <c r="A41" s="69" t="inlineStr"/>
+      <c r="B41" s="70" t="n"/>
+      <c r="C41" s="70" t="n"/>
+      <c r="D41" s="70" t="n"/>
+      <c r="E41" s="70" t="n"/>
+      <c r="F41" s="70" t="n"/>
+      <c r="G41" s="70" t="n"/>
+      <c r="H41" s="70" t="n"/>
+      <c r="I41" s="70" t="n"/>
+      <c r="J41" s="70" t="n"/>
+      <c r="K41" s="70" t="n"/>
+      <c r="L41" s="70" t="n"/>
+      <c r="M41" s="70" t="n"/>
+      <c r="N41" s="70" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="57" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>【販売管理費】</t>
         </is>
       </c>
-      <c r="B42" s="58" t="n"/>
-      <c r="C42" s="58" t="n"/>
-      <c r="D42" s="58" t="n"/>
-      <c r="E42" s="58" t="n"/>
-      <c r="F42" s="58" t="n"/>
-      <c r="G42" s="58" t="n"/>
-      <c r="H42" s="58" t="n"/>
-      <c r="I42" s="58" t="n"/>
-      <c r="J42" s="58" t="n"/>
-      <c r="K42" s="58" t="n"/>
-      <c r="L42" s="58" t="n"/>
-      <c r="M42" s="58" t="n"/>
-      <c r="N42" s="58" t="n"/>
+      <c r="B42" s="60" t="n"/>
+      <c r="C42" s="60" t="n"/>
+      <c r="D42" s="60" t="n"/>
+      <c r="E42" s="60" t="n"/>
+      <c r="F42" s="60" t="n"/>
+      <c r="G42" s="60" t="n"/>
+      <c r="H42" s="60" t="n"/>
+      <c r="I42" s="60" t="n"/>
+      <c r="J42" s="60" t="n"/>
+      <c r="K42" s="60" t="n"/>
+      <c r="L42" s="60" t="n"/>
+      <c r="M42" s="60" t="n"/>
+      <c r="N42" s="60" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
         </is>
       </c>
-      <c r="B43" s="59" t="n">
+      <c r="B43" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="C43" s="59" t="n">
+      <c r="C43" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="D43" s="59" t="n">
+      <c r="D43" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="E43" s="59" t="n">
+      <c r="E43" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="F43" s="59" t="n">
+      <c r="F43" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="G43" s="59" t="n">
+      <c r="G43" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="H43" s="59" t="n">
+      <c r="H43" s="61" t="n">
         <v>120</v>
       </c>
-      <c r="I43" s="59" t="n">
+      <c r="I43" s="61" t="n">
         <v>120</v>
       </c>
-      <c r="J43" s="59" t="n">
+      <c r="J43" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="K43" s="59" t="n">
+      <c r="K43" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="L43" s="59" t="n">
+      <c r="L43" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="M43" s="59" t="n">
+      <c r="M43" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="N43" s="55" t="n">
+      <c r="N43" s="57" t="n">
         <v>1040</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  人件費（バズ社員）</t>
         </is>
       </c>
-      <c r="B44" s="59" t="n">
+      <c r="B44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="C44" s="59" t="n">
+      <c r="C44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="D44" s="59" t="n">
+      <c r="D44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="E44" s="59" t="n">
+      <c r="E44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="F44" s="59" t="n">
+      <c r="F44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="G44" s="59" t="n">
+      <c r="G44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="H44" s="59" t="n">
+      <c r="H44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="I44" s="59" t="n">
+      <c r="I44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="59" t="n">
+      <c r="J44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="K44" s="59" t="n">
+      <c r="K44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="L44" s="59" t="n">
+      <c r="L44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="M44" s="59" t="n">
+      <c r="M44" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="N44" s="55" t="n">
+      <c r="N44" s="57" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  その他販管費</t>
         </is>
       </c>
-      <c r="B45" s="59" t="n">
+      <c r="B45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="C45" s="59" t="n">
+      <c r="C45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="D45" s="59" t="n">
+      <c r="D45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="E45" s="59" t="n">
+      <c r="E45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="F45" s="59" t="n">
+      <c r="F45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="G45" s="59" t="n">
+      <c r="G45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="H45" s="59" t="n">
+      <c r="H45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="I45" s="59" t="n">
+      <c r="I45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="J45" s="59" t="n">
+      <c r="J45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="K45" s="59" t="n">
+      <c r="K45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="L45" s="59" t="n">
+      <c r="L45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="M45" s="59" t="n">
+      <c r="M45" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="N45" s="55" t="n">
+      <c r="N45" s="57" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  ENTIAL業務委託費（TIE×5%）</t>
         </is>
       </c>
-      <c r="B46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="59" t="n">
+      <c r="B46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="G46" s="59" t="n">
+      <c r="G46" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="59" t="n">
+      <c r="H46" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="I46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="59" t="n">
+      <c r="I46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="K46" s="59" t="n">
+      <c r="K46" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="L46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="55" t="n">
+      <c r="L46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="57" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="74" t="inlineStr">
+      <c r="A47" s="76" t="inlineStr">
         <is>
           <t>販売管理費合計</t>
         </is>
       </c>
-      <c r="B47" s="75" t="n">
+      <c r="B47" s="77" t="n">
         <v>230</v>
       </c>
-      <c r="C47" s="75" t="n">
+      <c r="C47" s="77" t="n">
         <v>230</v>
       </c>
-      <c r="D47" s="75" t="n">
+      <c r="D47" s="77" t="n">
         <v>230</v>
       </c>
-      <c r="E47" s="75" t="n">
+      <c r="E47" s="77" t="n">
         <v>230</v>
       </c>
-      <c r="F47" s="75" t="n">
+      <c r="F47" s="77" t="n">
         <v>255</v>
       </c>
-      <c r="G47" s="75" t="n">
+      <c r="G47" s="77" t="n">
         <v>255</v>
       </c>
-      <c r="H47" s="75" t="n">
+      <c r="H47" s="77" t="n">
         <v>275</v>
       </c>
-      <c r="I47" s="75" t="n">
+      <c r="I47" s="77" t="n">
         <v>270</v>
       </c>
-      <c r="J47" s="75" t="n">
+      <c r="J47" s="77" t="n">
         <v>260</v>
       </c>
-      <c r="K47" s="75" t="n">
+      <c r="K47" s="77" t="n">
         <v>235</v>
       </c>
-      <c r="L47" s="75" t="n">
+      <c r="L47" s="77" t="n">
         <v>200</v>
       </c>
-      <c r="M47" s="75" t="n">
+      <c r="M47" s="77" t="n">
         <v>200</v>
       </c>
-      <c r="N47" s="75" t="n">
+      <c r="N47" s="77" t="n">
         <v>2870</v>
       </c>
     </row>
     <row r="48" ht="6" customHeight="1">
-      <c r="A48" s="67" t="inlineStr"/>
-      <c r="B48" s="68" t="n"/>
-      <c r="C48" s="68" t="n"/>
-      <c r="D48" s="68" t="n"/>
-      <c r="E48" s="68" t="n"/>
-      <c r="F48" s="68" t="n"/>
-      <c r="G48" s="68" t="n"/>
-      <c r="H48" s="68" t="n"/>
-      <c r="I48" s="68" t="n"/>
-      <c r="J48" s="68" t="n"/>
-      <c r="K48" s="68" t="n"/>
-      <c r="L48" s="68" t="n"/>
-      <c r="M48" s="68" t="n"/>
-      <c r="N48" s="68" t="n"/>
+      <c r="A48" s="69" t="inlineStr"/>
+      <c r="B48" s="70" t="n"/>
+      <c r="C48" s="70" t="n"/>
+      <c r="D48" s="70" t="n"/>
+      <c r="E48" s="70" t="n"/>
+      <c r="F48" s="70" t="n"/>
+      <c r="G48" s="70" t="n"/>
+      <c r="H48" s="70" t="n"/>
+      <c r="I48" s="70" t="n"/>
+      <c r="J48" s="70" t="n"/>
+      <c r="K48" s="70" t="n"/>
+      <c r="L48" s="70" t="n"/>
+      <c r="M48" s="70" t="n"/>
+      <c r="N48" s="70" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="56" t="inlineStr">
+      <c r="A49" s="58" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="B49" s="79" t="n">
+      <c r="B49" s="81" t="n">
         <v>-240</v>
       </c>
-      <c r="C49" s="79" t="n">
+      <c r="C49" s="81" t="n">
         <v>-240</v>
       </c>
-      <c r="D49" s="79" t="n">
+      <c r="D49" s="81" t="n">
         <v>-239</v>
       </c>
-      <c r="E49" s="79" t="n">
+      <c r="E49" s="81" t="n">
         <v>-238</v>
       </c>
-      <c r="F49" s="79" t="n">
+      <c r="F49" s="81" t="n">
         <v>-186</v>
       </c>
-      <c r="G49" s="79" t="n">
+      <c r="G49" s="81" t="n">
         <v>-183</v>
       </c>
-      <c r="H49" s="79" t="n">
+      <c r="H49" s="81" t="n">
         <v>-200</v>
       </c>
-      <c r="I49" s="79" t="n">
+      <c r="I49" s="81" t="n">
         <v>-267</v>
       </c>
-      <c r="J49" s="79" t="n">
+      <c r="J49" s="81" t="n">
         <v>-115</v>
       </c>
-      <c r="K49" s="79" t="n">
+      <c r="K49" s="81" t="n">
         <v>-152</v>
       </c>
-      <c r="L49" s="79" t="n">
+      <c r="L49" s="81" t="n">
         <v>-190</v>
       </c>
-      <c r="M49" s="79" t="n">
+      <c r="M49" s="81" t="n">
         <v>-185</v>
       </c>
-      <c r="N49" s="86" t="n">
+      <c r="N49" s="88" t="n">
         <v>-2435</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="70" t="inlineStr">
+      <c r="A50" s="72" t="inlineStr">
         <is>
           <t>営業利益率</t>
         </is>
       </c>
-      <c r="B50" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="71" t="n">
+      <c r="B50" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="73" t="n">
         <v>-23900</v>
       </c>
-      <c r="E50" s="71" t="n">
+      <c r="E50" s="73" t="n">
         <v>-11900</v>
       </c>
-      <c r="F50" s="71" t="n">
+      <c r="F50" s="73" t="n">
         <v>-178.8</v>
       </c>
-      <c r="G50" s="71" t="n">
+      <c r="G50" s="73" t="n">
         <v>-171</v>
       </c>
-      <c r="H50" s="71" t="n">
+      <c r="H50" s="73" t="n">
         <v>-181.8</v>
       </c>
-      <c r="I50" s="71" t="n">
+      <c r="I50" s="73" t="n">
         <v>-2053.8</v>
       </c>
-      <c r="J50" s="71" t="n">
+      <c r="J50" s="73" t="n">
         <v>-53.5</v>
       </c>
-      <c r="K50" s="71" t="n">
+      <c r="K50" s="73" t="n">
         <v>-128.8</v>
       </c>
-      <c r="L50" s="71" t="n">
+      <c r="L50" s="73" t="n">
         <v>-950</v>
       </c>
-      <c r="M50" s="71" t="n">
+      <c r="M50" s="73" t="n">
         <v>-740</v>
       </c>
-      <c r="N50" s="72" t="n">
+      <c r="N50" s="74" t="n">
         <v>-4025.8</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="37" t="inlineStr">
+      <c r="A51" s="39" t="inlineStr">
         <is>
           <t>★ 損益分岐：Year1内で達成せず　／　Year1通期営業利益：-2,435万円　／　Year1売上：715万円</t>
         </is>
@@ -8275,7 +8293,7 @@
       <c r="N51" s="2" t="n"/>
     </row>
     <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="83" t="inlineStr">
+      <c r="A52" s="85" t="inlineStr">
         <is>
           <t>【注記】単位：万円 ／ ギャル協会：出演・監修料=件数×25万（最低保証10万）、EC物販はギャル協会がショップオーナー（バズに原価なし） ／ バズEC収益=アフィリエイトコミッション（EC実売上×20%） ／ 制作費：TIE×10% ／ ENTIAL：TIE成功報酬×5%（EC運用除外）</t>
         </is>
